--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.1</v>
+        <v>-0.31</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>-491.9661613597635</v>
+        <v>-516.2292124438683</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>327.9774409065089</v>
+        <v>344.1528082959121</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>163.9887204532545</v>
+        <v>172.0764041479561</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>429.41</v>
+        <v>437.91</v>
       </c>
       <c r="C2" t="n">
-        <v>13.91</v>
+        <v>12.23</v>
       </c>
       <c r="D2" t="n">
-        <v>415.5</v>
+        <v>425.68</v>
       </c>
       <c r="E2" t="n">
-        <v>471.13</v>
+        <v>474.61</v>
       </c>
       <c r="F2" t="n">
-        <v>69.54000000000001</v>
+        <v>61.17</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56.95</v>
+        <v>58.74</v>
       </c>
       <c r="C3" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="D3" t="n">
-        <v>53.4</v>
+        <v>55.94</v>
       </c>
       <c r="E3" t="n">
-        <v>67.59</v>
+        <v>67.13</v>
       </c>
       <c r="F3" t="n">
-        <v>177.39</v>
+        <v>139.86</v>
       </c>
     </row>
   </sheetData>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>56.95000076293945</v>
+        <v>58.7400016784668</v>
       </c>
       <c r="F2" t="n">
-        <v>2847.500038146973</v>
+        <v>2937.00008392334</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3279.774409065089</v>
+        <v>3441.528082959121</v>
       </c>
     </row>
     <row r="3">
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>429.4100036621094</v>
+        <v>437.9100036621094</v>
       </c>
       <c r="F3" t="n">
-        <v>2147.050018310547</v>
+        <v>2189.550018310547</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2147.050018310547</v>
+        <v>2189.550018310547</v>
       </c>
     </row>
   </sheetData>
@@ -934,13 +934,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4702.7001953125</v>
+        <v>4787.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04690565345336162</v>
+        <v>0.02932385302456186</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.07158502425452595</v>
+        <v>-0.06409553048641625</v>
       </c>
     </row>
     <row r="3">
@@ -950,13 +950,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73.16999816894531</v>
+        <v>75.76000213623047</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0521245250620872</v>
+        <v>0.04158935176317846</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1042638199482613</v>
+        <v>-0.1052320328971353</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>-516.2292124438683</v>
+        <v>-516.6686245315942</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>344.1528082959121</v>
+        <v>344.4457496877294</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>172.0764041479561</v>
+        <v>172.2228748438647</v>
       </c>
     </row>
   </sheetData>
@@ -740,16 +740,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58.74</v>
+        <v>58.79</v>
       </c>
       <c r="C3" t="n">
         <v>2.8</v>
       </c>
       <c r="D3" t="n">
-        <v>55.94</v>
+        <v>55.99</v>
       </c>
       <c r="E3" t="n">
-        <v>67.13</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="F3" t="n">
         <v>139.86</v>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>58.7400016784668</v>
+        <v>58.79000091552734</v>
       </c>
       <c r="F2" t="n">
-        <v>2937.00008392334</v>
+        <v>2939.500045776367</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3441.528082959121</v>
+        <v>3444.457496877294</v>
       </c>
     </row>
     <row r="3">
@@ -934,13 +934,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4787.89990234375</v>
+        <v>4787.5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02932385302456186</v>
+        <v>0.02923788025368168</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.06409553048641625</v>
+        <v>-0.06417370053978377</v>
       </c>
     </row>
     <row r="3">

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.31</v>
+        <v>-0.64</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,11 +600,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+15.0%</t>
+          <t>-85.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>-516.6686245315942</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>344.4457496877294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>172.2228748438647</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>437.91</v>
+        <v>437.13</v>
       </c>
       <c r="C2" t="n">
-        <v>12.23</v>
+        <v>11.3</v>
       </c>
       <c r="D2" t="n">
-        <v>425.68</v>
+        <v>425.83</v>
       </c>
       <c r="E2" t="n">
-        <v>474.61</v>
+        <v>471.04</v>
       </c>
       <c r="F2" t="n">
-        <v>61.17</v>
+        <v>56.51</v>
       </c>
     </row>
     <row r="3">
@@ -739,20 +739,12 @@
           <t>PHAG.MI</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>58.79</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="D3" t="n">
-        <v>55.99</v>
-      </c>
-      <c r="E3" t="n">
-        <v>67.18000000000001</v>
-      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>139.86</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -838,20 +830,14 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>58.79000091552734</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2939.500045776367</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Layer 1</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>3444.457496877294</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -871,10 +857,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>437.9100036621094</v>
+        <v>437.1300048828125</v>
       </c>
       <c r="F3" t="n">
-        <v>2189.550018310547</v>
+        <v>2185.650024414062</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -882,7 +868,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2189.550018310547</v>
+        <v>2185.650024414062</v>
       </c>
     </row>
   </sheetData>
@@ -934,13 +920,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4787.5</v>
+        <v>4771</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02923788025368168</v>
+        <v>0.02569063742878641</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.06417370053978377</v>
+        <v>-0.06739900266847176</v>
       </c>
     </row>
     <row r="3">
@@ -950,13 +936,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.76000213623047</v>
+        <v>76.02500152587891</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04158935176317846</v>
+        <v>0.04523270623385556</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1052320328971353</v>
+        <v>-0.1021022419985969</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.64</v>
+        <v>-0.63</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>437.13</v>
+        <v>435.36</v>
       </c>
       <c r="C2" t="n">
-        <v>11.3</v>
+        <v>10.63</v>
       </c>
       <c r="D2" t="n">
-        <v>425.83</v>
+        <v>424.73</v>
       </c>
       <c r="E2" t="n">
-        <v>471.04</v>
+        <v>467.25</v>
       </c>
       <c r="F2" t="n">
-        <v>56.51</v>
+        <v>53.16</v>
       </c>
     </row>
     <row r="3">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>437.1300048828125</v>
+        <v>435.3599853515625</v>
       </c>
       <c r="F3" t="n">
-        <v>2185.650024414062</v>
+        <v>2176.799926757812</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2185.650024414062</v>
+        <v>2176.799926757812</v>
       </c>
     </row>
   </sheetData>
@@ -920,13 +920,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4771</v>
+        <v>4773</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02569063742878641</v>
+        <v>0.02495280024611191</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.06739900266847176</v>
+        <v>-0.05531914893617018</v>
       </c>
     </row>
     <row r="3">
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>76.02500152587891</v>
+        <v>75.87999725341797</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04523270623385556</v>
+        <v>0.04430153731332465</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1021022419985969</v>
+        <v>-0.06221425365562971</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.63</v>
+        <v>-0.29</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LIGERAMENTE ALCISTA (Parcial)</t>
+          <t>HOLD / CASH (Sin Tendencia)</t>
         </is>
       </c>
     </row>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>435.36</v>
+        <v>445.09</v>
       </c>
       <c r="C2" t="n">
-        <v>10.63</v>
+        <v>10.76</v>
       </c>
       <c r="D2" t="n">
-        <v>424.73</v>
+        <v>434.33</v>
       </c>
       <c r="E2" t="n">
-        <v>467.25</v>
+        <v>477.36</v>
       </c>
       <c r="F2" t="n">
-        <v>53.16</v>
+        <v>53.78</v>
       </c>
     </row>
     <row r="3">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>435.3599853515625</v>
+        <v>445.0899963378906</v>
       </c>
       <c r="F3" t="n">
-        <v>2176.799926757812</v>
+        <v>2225.449981689453</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2176.799926757812</v>
+        <v>2225.449981689453</v>
       </c>
     </row>
   </sheetData>
@@ -920,13 +920,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4773</v>
+        <v>4864</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02495280024611191</v>
+        <v>0.04442676730265593</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.05531914893617018</v>
+        <v>-0.02603123748498193</v>
       </c>
     </row>
     <row r="3">
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.87999725341797</v>
+        <v>79.55000305175781</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04430153731332465</v>
+        <v>0.1075377584730248</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.06221425365562971</v>
+        <v>-0.008883264171360428</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.29</v>
+        <v>0.06</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>445.09</v>
+        <v>440.46</v>
       </c>
       <c r="C2" t="n">
-        <v>10.76</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>434.33</v>
+        <v>430.49</v>
       </c>
       <c r="E2" t="n">
-        <v>477.36</v>
+        <v>470.36</v>
       </c>
       <c r="F2" t="n">
-        <v>53.78</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="3">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>445.0899963378906</v>
+        <v>440.4599914550781</v>
       </c>
       <c r="F3" t="n">
-        <v>2225.449981689453</v>
+        <v>2202.299957275391</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2225.449981689453</v>
+        <v>2202.299957275391</v>
       </c>
     </row>
   </sheetData>
@@ -920,13 +920,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4864</v>
+        <v>4823.7001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04442676730265593</v>
+        <v>0.01562273824876304</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02603123748498193</v>
+        <v>-0.03545287036342737</v>
       </c>
     </row>
     <row r="3">
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79.55000305175781</v>
+        <v>79.43499755859375</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1075377584730248</v>
+        <v>0.0559794558893929</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.008883264171360428</v>
+        <v>-0.001194533159327271</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>440.46</v>
+        <v>440.08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.970000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="D2" t="n">
-        <v>430.49</v>
+        <v>430.91</v>
       </c>
       <c r="E2" t="n">
-        <v>470.36</v>
+        <v>467.57</v>
       </c>
       <c r="F2" t="n">
-        <v>49.84</v>
+        <v>45.82</v>
       </c>
     </row>
     <row r="3">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>440.4599914550781</v>
+        <v>440.0799865722656</v>
       </c>
       <c r="F3" t="n">
-        <v>2202.299957275391</v>
+        <v>2200.399932861328</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2202.299957275391</v>
+        <v>2200.399932861328</v>
       </c>
     </row>
   </sheetData>
@@ -920,13 +920,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4823.7001953125</v>
+        <v>4815.7001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01562273824876304</v>
+        <v>0.004903801811741104</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.03545287036342737</v>
+        <v>-0.01517407483038369</v>
       </c>
     </row>
     <row r="3">
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79.43499755859375</v>
+        <v>78.88999938964844</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0559794558893929</v>
+        <v>0.034256708414939</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.001194533159327271</v>
+        <v>0.02138844156294439</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.06</v>
+        <v>-0.13</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HOLD / CASH (Sin Tendencia)</t>
+          <t>LIGERAMENTE ALCISTA (Parcial)</t>
         </is>
       </c>
     </row>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>440.08</v>
+        <v>445.93</v>
       </c>
       <c r="C2" t="n">
-        <v>9.16</v>
+        <v>8.51</v>
       </c>
       <c r="D2" t="n">
-        <v>430.91</v>
+        <v>437.42</v>
       </c>
       <c r="E2" t="n">
-        <v>467.57</v>
+        <v>471.47</v>
       </c>
       <c r="F2" t="n">
-        <v>45.82</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="3">
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>440.0799865722656</v>
+        <v>445.9299926757812</v>
       </c>
       <c r="F3" t="n">
-        <v>2200.399932861328</v>
+        <v>2229.649963378906</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2200.399932861328</v>
+        <v>2229.649963378906</v>
       </c>
     </row>
   </sheetData>
@@ -920,13 +920,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4815.7001953125</v>
+        <v>4849.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004903801811741104</v>
+        <v>0.02256241611912979</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01517407483038369</v>
+        <v>0.06104498642600742</v>
       </c>
     </row>
     <row r="3">
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.88999938964844</v>
+        <v>80.93000030517578</v>
       </c>
       <c r="C3" t="n">
-        <v>0.034256708414939</v>
+        <v>0.07159405072315228</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02138844156294439</v>
+        <v>0.1668108361160749</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,11 +600,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-85.0%</t>
+          <t>-54.4%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>100265.7995353147</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>+32.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-60091.99173325991</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>+21.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-40173.80780205476</v>
       </c>
     </row>
   </sheetData>
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -714,37 +714,111 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>PAAS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>445.93</v>
+        <v>59.06</v>
       </c>
       <c r="C2" t="n">
-        <v>8.51</v>
+        <v>2.4</v>
       </c>
       <c r="D2" t="n">
-        <v>437.42</v>
+        <v>56.66</v>
       </c>
       <c r="E2" t="n">
-        <v>471.47</v>
+        <v>66.25</v>
       </c>
       <c r="F2" t="n">
-        <v>42.56</v>
+        <v>1322.43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="E3" t="n">
+        <v>22.54</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>PHAG.MI</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>0</v>
+      <c r="B4" t="n">
+        <v>63.54</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="D4" t="n">
+        <v>61.18</v>
+      </c>
+      <c r="E4" t="n">
+        <v>70.63</v>
+      </c>
+      <c r="F4" t="n">
+        <v>351.96</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FNV</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>253.64</v>
+      </c>
+      <c r="E5" t="n">
+        <v>289.09</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1550.88</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SGLE.MI</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="D6" t="n">
+        <v>107.81</v>
+      </c>
+      <c r="E6" t="n">
+        <v>117.16</v>
+      </c>
+      <c r="F6" t="n">
+        <v>820.09</v>
       </c>
     </row>
   </sheetData>
@@ -758,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -820,55 +894,189 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="C2" t="n">
-        <v>31.24</v>
+        <v>71.27120805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>63.54000091552734</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9467.460136413574</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Layer 1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>11119.87266184867</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>GLDA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>176.337108</v>
       </c>
       <c r="C3" t="n">
-        <v>210.5</v>
+        <v>180.0585271439185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SGLE.MI</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>351</v>
+      </c>
+      <c r="C4" t="n">
+        <v>121.1489</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>110.1500015258789</v>
+      </c>
+      <c r="F4" t="n">
+        <v>38662.6505355835</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Layer 1</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>45410.67451360885</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PAAS</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>552</v>
+      </c>
+      <c r="C5" t="n">
+        <v>63.24086956521739</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>445.9299926757812</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2229.649963378906</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>🚨 NO CLASIFICADO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2229.649963378906</v>
+      <c r="E5" t="n">
+        <v>59.06000137329102</v>
+      </c>
+      <c r="F5" t="n">
+        <v>32601.12075805664</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Layer 2</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>32601.12075805664</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FNV</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>175</v>
+      </c>
+      <c r="C6" t="n">
+        <v>153.3512571428571</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>45937.5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Layer 2</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>45937.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2528</v>
+      </c>
+      <c r="C7" t="n">
+        <v>26.52362341772152</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>19.54000091552734</v>
+      </c>
+      <c r="F7" t="n">
+        <v>49397.12231445312</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Layer 3</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>49397.12231445312</v>
       </c>
     </row>
   </sheetData>
@@ -920,13 +1128,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4849.39990234375</v>
+        <v>4879.60009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02256241611912979</v>
+        <v>0.02893054110529447</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06104498642600742</v>
+        <v>0.06765276604218795</v>
       </c>
     </row>
     <row r="3">
@@ -936,13 +1144,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80.93000030517578</v>
+        <v>81.84200286865234</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07159405072315228</v>
+        <v>0.08366987572723605</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1668108361160749</v>
+        <v>0.1799596618867088</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,11 +600,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-54.4%</t>
+          <t>-43.6%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100265.7995353147</v>
+        <v>95189.504916698</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+32.6%</t>
+          <t>+26.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-60091.99173325991</v>
+        <v>-56707.79532084877</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+21.8%</t>
+          <t>+17.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-40173.80780205476</v>
+        <v>-38481.7095958492</v>
       </c>
     </row>
   </sheetData>
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -802,22 +802,44 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>GLDA.DE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="D6" t="n">
+        <v>160.52</v>
+      </c>
+      <c r="E6" t="n">
+        <v>172.45</v>
+      </c>
+      <c r="F6" t="n">
+        <v>525.86</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>SGLE.MI</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
         <v>110.15</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" t="n">
         <v>2.34</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>107.81</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>117.16</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>820.09</v>
       </c>
     </row>
@@ -916,13 +938,13 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>11119.87266184867</v>
+        <v>11117.26218877667</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GLDA</t>
+          <t>GLDA.DE</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -937,10 +959,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>163.5</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>28831.117158</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -948,7 +970,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>33855.2350918314</v>
       </c>
     </row>
     <row r="4">
@@ -980,7 +1002,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>45410.67451360885</v>
+        <v>45400.01401896077</v>
       </c>
     </row>
     <row r="5">

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>95189.504916698</v>
+        <v>95191.09715000888</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-56707.79532084877</v>
+        <v>-56708.85680972273</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-38481.7095958492</v>
+        <v>-38482.24034028617</v>
       </c>
     </row>
   </sheetData>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>11117.26218877667</v>
+        <v>11115.95638793608</v>
       </c>
     </row>
     <row r="3">
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>33855.2350918314</v>
+        <v>33851.25855573008</v>
       </c>
     </row>
     <row r="4">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>45400.01401896077</v>
+        <v>45394.68146716319</v>
       </c>
     </row>
     <row r="5">

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LIGERAMENTE ALCISTA (Parcial)</t>
+          <t>HOLD / CASH (Sin Tendencia)</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,11 +600,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-43.6%</t>
+          <t>-85.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>95191.09715000888</v>
+        <v>107475.1824203491</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+26.0%</t>
+          <t>+51.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-56708.85680972273</v>
+        <v>-64931.0121673584</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+17.6%</t>
+          <t>+33.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-38482.24034028617</v>
+        <v>-42544.17025299072</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59.06</v>
+        <v>58.7</v>
       </c>
       <c r="C2" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="D2" t="n">
-        <v>56.66</v>
+        <v>56.39</v>
       </c>
       <c r="E2" t="n">
-        <v>66.25</v>
+        <v>65.63</v>
       </c>
       <c r="F2" t="n">
-        <v>1322.43</v>
+        <v>1275.51</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.54</v>
+        <v>19.33</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="D3" t="n">
-        <v>18.54</v>
+        <v>18.4</v>
       </c>
       <c r="E3" t="n">
-        <v>22.54</v>
+        <v>22.12</v>
       </c>
       <c r="F3" t="n">
-        <v>2528</v>
+        <v>2349.23</v>
       </c>
     </row>
     <row r="4">
@@ -761,20 +761,12 @@
           <t>PHAG.MI</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>63.54</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="D4" t="n">
-        <v>61.18</v>
-      </c>
-      <c r="E4" t="n">
-        <v>70.63</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>351.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -784,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>262.5</v>
+        <v>258.13</v>
       </c>
       <c r="C5" t="n">
-        <v>8.859999999999999</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>253.64</v>
+        <v>249.5</v>
       </c>
       <c r="E5" t="n">
-        <v>289.09</v>
+        <v>284.02</v>
       </c>
       <c r="F5" t="n">
-        <v>1550.88</v>
+        <v>1510.38</v>
       </c>
     </row>
     <row r="6">
@@ -805,20 +797,12 @@
           <t>GLDA.DE</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>163.5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="D6" t="n">
-        <v>160.52</v>
-      </c>
-      <c r="E6" t="n">
-        <v>172.45</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>525.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -827,20 +811,12 @@
           <t>SGLE.MI</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>110.15</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="D7" t="n">
-        <v>107.81</v>
-      </c>
-      <c r="E7" t="n">
-        <v>117.16</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>820.09</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -926,20 +902,14 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>63.54000091552734</v>
-      </c>
-      <c r="F2" t="n">
-        <v>9467.460136413574</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Layer 1</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>11115.95638793608</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -958,20 +928,14 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>163.5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>28831.117158</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Layer 1</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>33851.25855573008</v>
-      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -990,20 +954,14 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>110.1500015258789</v>
-      </c>
-      <c r="F4" t="n">
-        <v>38662.6505355835</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Layer 1</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>45394.68146716319</v>
-      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1023,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>59.06000137329102</v>
+        <v>58.70000076293945</v>
       </c>
       <c r="F5" t="n">
-        <v>32601.12075805664</v>
+        <v>32402.40042114258</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1034,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>32601.12075805664</v>
+        <v>32402.40042114258</v>
       </c>
     </row>
     <row r="6">
@@ -1055,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>262.5</v>
+        <v>258.1300048828125</v>
       </c>
       <c r="F6" t="n">
-        <v>45937.5</v>
+        <v>45172.75085449219</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1066,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>45937.5</v>
+        <v>45172.75085449219</v>
       </c>
     </row>
     <row r="7">
@@ -1087,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>19.54000091552734</v>
+        <v>19.32999992370605</v>
       </c>
       <c r="F7" t="n">
-        <v>49397.12231445312</v>
+        <v>48866.23980712891</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1098,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>49397.12231445312</v>
+        <v>48866.23980712891</v>
       </c>
     </row>
   </sheetData>
@@ -1150,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4879.60009765625</v>
+        <v>4850.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02893054110529447</v>
+        <v>0.02287871167220157</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06765276604218795</v>
+        <v>0.06137318527776014</v>
       </c>
     </row>
     <row r="3">
@@ -1166,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81.84200286865234</v>
+        <v>80.18499755859375</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08366987572723605</v>
+        <v>0.06172947012264229</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1799596618867088</v>
+        <v>0.1560697354813261</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.15</v>
+        <v>0.34</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>107475.1824203491</v>
+        <v>101779.6296142578</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.4%</t>
+          <t>+51.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-64931.0121673584</v>
+        <v>-62035.14626464844</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.6%</t>
+          <t>+33.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-42544.17025299072</v>
+        <v>-39744.48334960938</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>58.7</v>
+        <v>55.61</v>
       </c>
       <c r="C2" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="D2" t="n">
-        <v>56.39</v>
+        <v>53.33</v>
       </c>
       <c r="E2" t="n">
-        <v>65.63</v>
+        <v>62.45</v>
       </c>
       <c r="F2" t="n">
-        <v>1275.51</v>
+        <v>1258.95</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.33</v>
+        <v>18.09</v>
       </c>
       <c r="C3" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="D3" t="n">
-        <v>18.4</v>
+        <v>17.18</v>
       </c>
       <c r="E3" t="n">
-        <v>22.12</v>
+        <v>20.83</v>
       </c>
       <c r="F3" t="n">
-        <v>2349.23</v>
+        <v>2312.22</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>258.13</v>
+        <v>247.5</v>
       </c>
       <c r="C5" t="n">
-        <v>8.630000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="D5" t="n">
-        <v>249.5</v>
+        <v>239.08</v>
       </c>
       <c r="E5" t="n">
-        <v>284.02</v>
+        <v>272.76</v>
       </c>
       <c r="F5" t="n">
-        <v>1510.38</v>
+        <v>1473.63</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>58.70000076293945</v>
+        <v>55.61000061035156</v>
       </c>
       <c r="F5" t="n">
-        <v>32402.40042114258</v>
+        <v>30696.72033691406</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>32402.40042114258</v>
+        <v>30696.72033691406</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>258.1300048828125</v>
+        <v>247.5</v>
       </c>
       <c r="F6" t="n">
-        <v>45172.75085449219</v>
+        <v>43312.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>45172.75085449219</v>
+        <v>43312.5</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>19.32999992370605</v>
+        <v>18.09000015258789</v>
       </c>
       <c r="F7" t="n">
-        <v>48866.23980712891</v>
+        <v>45731.52038574219</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>48866.23980712891</v>
+        <v>45731.52038574219</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4850.89990234375</v>
+        <v>4736.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02287871167220157</v>
+        <v>-0.01836271454015548</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06137318527776014</v>
+        <v>0.07545237331557053</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80.18499755859375</v>
+        <v>76.86000061035156</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06172947012264229</v>
+        <v>-0.03188016610133237</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1560697354813261</v>
+        <v>0.1131225159222402</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101779.6296142578</v>
+        <v>104024.1020584106</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.8%</t>
+          <t>+50.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-62035.14626464844</v>
+        <v>-62212.2891998291</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.2%</t>
+          <t>+34.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-39744.48334960938</v>
+        <v>-41811.81285858154</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55.61</v>
+        <v>56.46</v>
       </c>
       <c r="C2" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="D2" t="n">
-        <v>53.33</v>
+        <v>54.22</v>
       </c>
       <c r="E2" t="n">
-        <v>62.45</v>
+        <v>63.19</v>
       </c>
       <c r="F2" t="n">
-        <v>1258.95</v>
+        <v>1238.45</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.09</v>
+        <v>18.96</v>
       </c>
       <c r="C3" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>17.18</v>
+        <v>18.06</v>
       </c>
       <c r="E3" t="n">
-        <v>20.83</v>
+        <v>21.66</v>
       </c>
       <c r="F3" t="n">
-        <v>2312.22</v>
+        <v>2271.59</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>247.5</v>
+        <v>247.34</v>
       </c>
       <c r="C5" t="n">
-        <v>8.42</v>
+        <v>7.99</v>
       </c>
       <c r="D5" t="n">
-        <v>239.08</v>
+        <v>239.35</v>
       </c>
       <c r="E5" t="n">
-        <v>272.76</v>
+        <v>271.32</v>
       </c>
       <c r="F5" t="n">
-        <v>1473.63</v>
+        <v>1398.63</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>55.61000061035156</v>
+        <v>56.45999908447266</v>
       </c>
       <c r="F5" t="n">
-        <v>30696.72033691406</v>
+        <v>31165.91949462891</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>30696.72033691406</v>
+        <v>31165.91949462891</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>247.5</v>
+        <v>247.3399963378906</v>
       </c>
       <c r="F6" t="n">
-        <v>43312.5</v>
+        <v>43284.49935913086</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>43312.5</v>
+        <v>43284.49935913086</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.09000015258789</v>
+        <v>18.95999908447266</v>
       </c>
       <c r="F7" t="n">
-        <v>45731.52038574219</v>
+        <v>47930.87768554688</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>45731.52038574219</v>
+        <v>47930.87768554688</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4736.39990234375</v>
+        <v>4747.7998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01836271454015548</v>
+        <v>-0.01087504069010414</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07545237331557053</v>
+        <v>0.07921715169961119</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>76.86000061035156</v>
+        <v>77.55000305175781</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03188016610133237</v>
+        <v>-0.02441778727491695</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1131225159222402</v>
+        <v>0.1194676318480792</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HOLD / CASH (Sin Tendencia)</t>
+          <t>LIGERAMENTE ALCISTA (Parcial)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>104024.1020584106</v>
+        <v>101765.6371559143</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+50.8%</t>
+          <t>+51.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-62212.2891998291</v>
+        <v>-61160.81033477784</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+34.2%</t>
+          <t>+33.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-41811.81285858154</v>
+        <v>-40604.82682113648</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56.46</v>
+        <v>55.12</v>
       </c>
       <c r="C2" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="D2" t="n">
-        <v>54.22</v>
+        <v>52.95</v>
       </c>
       <c r="E2" t="n">
-        <v>63.19</v>
+        <v>61.64</v>
       </c>
       <c r="F2" t="n">
-        <v>1238.45</v>
+        <v>1200.21</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.96</v>
+        <v>18.43</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="D3" t="n">
-        <v>18.06</v>
+        <v>17.54</v>
       </c>
       <c r="E3" t="n">
-        <v>21.66</v>
+        <v>21.1</v>
       </c>
       <c r="F3" t="n">
-        <v>2271.59</v>
+        <v>2246.31</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>247.34</v>
+        <v>244.04</v>
       </c>
       <c r="C5" t="n">
-        <v>7.99</v>
+        <v>7.53</v>
       </c>
       <c r="D5" t="n">
-        <v>239.35</v>
+        <v>236.51</v>
       </c>
       <c r="E5" t="n">
-        <v>271.32</v>
+        <v>266.64</v>
       </c>
       <c r="F5" t="n">
-        <v>1398.63</v>
+        <v>1318.24</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.45999908447266</v>
+        <v>55.11999893188477</v>
       </c>
       <c r="F5" t="n">
-        <v>31165.91949462891</v>
+        <v>30426.23941040039</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>31165.91949462891</v>
+        <v>30426.23941040039</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>247.3399963378906</v>
+        <v>244.0399932861328</v>
       </c>
       <c r="F6" t="n">
-        <v>43284.49935913086</v>
+        <v>42706.99882507324</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>43284.49935913086</v>
+        <v>42706.99882507324</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.95999908447266</v>
+        <v>18.43000030517578</v>
       </c>
       <c r="F7" t="n">
-        <v>47930.87768554688</v>
+        <v>46591.04077148438</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>47930.87768554688</v>
+        <v>46591.04077148438</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4747.7998046875</v>
+        <v>4708.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01087504069010414</v>
+        <v>-0.01598612478813577</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07921715169961119</v>
+        <v>0.03496859301201227</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77.55000305175781</v>
+        <v>75.45500183105469</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.02441778727491695</v>
+        <v>-0.04008600951602082</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1194676318480792</v>
+        <v>0.04275786359240197</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.67</v>
+        <v>0.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LIGERAMENTE ALCISTA (Parcial)</t>
+          <t>HOLD / CASH (Sin Tendencia)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101765.6371559143</v>
+        <v>102714.5349205017</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.1%</t>
+          <t>+50.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-61160.81033477784</v>
+        <v>-61230.16831512452</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.9%</t>
+          <t>+34.3%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-40604.82682113648</v>
+        <v>-41484.3666053772</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55.12</v>
+        <v>55.99</v>
       </c>
       <c r="C2" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="D2" t="n">
-        <v>52.95</v>
+        <v>53.77</v>
       </c>
       <c r="E2" t="n">
-        <v>61.64</v>
+        <v>62.64</v>
       </c>
       <c r="F2" t="n">
-        <v>1200.21</v>
+        <v>1223.63</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.43</v>
+        <v>18.8</v>
       </c>
       <c r="C3" t="n">
         <v>0.89</v>
       </c>
       <c r="D3" t="n">
-        <v>17.54</v>
+        <v>17.91</v>
       </c>
       <c r="E3" t="n">
-        <v>21.1</v>
+        <v>21.48</v>
       </c>
       <c r="F3" t="n">
-        <v>2246.31</v>
+        <v>2258.05</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>244.04</v>
+        <v>242.33</v>
       </c>
       <c r="C5" t="n">
-        <v>7.53</v>
+        <v>7.65</v>
       </c>
       <c r="D5" t="n">
-        <v>236.51</v>
+        <v>234.68</v>
       </c>
       <c r="E5" t="n">
-        <v>266.64</v>
+        <v>265.28</v>
       </c>
       <c r="F5" t="n">
-        <v>1318.24</v>
+        <v>1338.75</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>55.11999893188477</v>
+        <v>55.9900016784668</v>
       </c>
       <c r="F5" t="n">
-        <v>30426.23941040039</v>
+        <v>30906.48092651367</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>30426.23941040039</v>
+        <v>30906.48092651367</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>244.0399932861328</v>
+        <v>242.3300018310547</v>
       </c>
       <c r="F6" t="n">
-        <v>42706.99882507324</v>
+        <v>42407.75032043457</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>42706.99882507324</v>
+        <v>42407.75032043457</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.43000030517578</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="F7" t="n">
-        <v>46591.04077148438</v>
+        <v>47526.39807128906</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>46591.04077148438</v>
+        <v>47526.39807128906</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4708.89990234375</v>
+        <v>4725.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01598612478813577</v>
+        <v>-0.02721512529948389</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03496859301201227</v>
+        <v>0.0799679813378471</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.45500183105469</v>
+        <v>75.68499755859375</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.04008600951602082</v>
+        <v>-0.07405370183570115</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04275786359240197</v>
+        <v>0.118425916875212</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102714.5349205017</v>
+        <v>101774.8102714539</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-61230.16831512452</v>
+        <v>-60690.20169525146</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-41484.3666053772</v>
+        <v>-41084.60857620239</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55.99</v>
+        <v>55.23</v>
       </c>
       <c r="C2" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="D2" t="n">
-        <v>53.77</v>
+        <v>53.05</v>
       </c>
       <c r="E2" t="n">
-        <v>62.64</v>
+        <v>61.77</v>
       </c>
       <c r="F2" t="n">
-        <v>1223.63</v>
+        <v>1202.97</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.8</v>
+        <v>18.62</v>
       </c>
       <c r="C3" t="n">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="D3" t="n">
-        <v>17.91</v>
+        <v>17.76</v>
       </c>
       <c r="E3" t="n">
-        <v>21.48</v>
+        <v>21.21</v>
       </c>
       <c r="F3" t="n">
-        <v>2258.05</v>
+        <v>2181.3</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>242.33</v>
+        <v>241.01</v>
       </c>
       <c r="C5" t="n">
-        <v>7.65</v>
+        <v>7.32</v>
       </c>
       <c r="D5" t="n">
-        <v>234.68</v>
+        <v>233.69</v>
       </c>
       <c r="E5" t="n">
-        <v>265.28</v>
+        <v>262.97</v>
       </c>
       <c r="F5" t="n">
-        <v>1338.75</v>
+        <v>1280.81</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>55.9900016784668</v>
+        <v>55.22999954223633</v>
       </c>
       <c r="F5" t="n">
-        <v>30906.48092651367</v>
+        <v>30486.95974731445</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>30906.48092651367</v>
+        <v>30486.95974731445</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>242.3300018310547</v>
+        <v>241.0099945068359</v>
       </c>
       <c r="F6" t="n">
-        <v>42407.75032043457</v>
+        <v>42176.74903869629</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>42407.75032043457</v>
+        <v>42176.74903869629</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.79999923706055</v>
+        <v>18.6200008392334</v>
       </c>
       <c r="F7" t="n">
-        <v>47526.39807128906</v>
+        <v>47071.36212158203</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>47526.39807128906</v>
+        <v>47071.36212158203</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4725.39990234375</v>
+        <v>4702</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02721512529948389</v>
+        <v>-0.02176176414327757</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0799679813378471</v>
+        <v>0.04674977738201247</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.68499755859375</v>
+        <v>75.83499908447266</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.07405370183570115</v>
+        <v>-0.05148150116748795</v>
       </c>
       <c r="D3" t="n">
-        <v>0.118425916875212</v>
+        <v>0.09044505113433288</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.46</v>
+        <v>0.82</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HOLD / CASH (Sin Tendencia)</t>
+          <t>LIGERAMENTE ALCISTA (Parcial)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101774.8102714539</v>
+        <v>97489.94145202637</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-60690.20169525146</v>
+        <v>-58125.12350463868</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-41084.60857620239</v>
+        <v>-39364.8179473877</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55.23</v>
+        <v>52.39</v>
       </c>
       <c r="C2" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="D2" t="n">
-        <v>53.05</v>
+        <v>50.25</v>
       </c>
       <c r="E2" t="n">
-        <v>61.77</v>
+        <v>58.81</v>
       </c>
       <c r="F2" t="n">
-        <v>1202.97</v>
+        <v>1181.67</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.62</v>
+        <v>17.84</v>
       </c>
       <c r="C3" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>17.76</v>
+        <v>17.03</v>
       </c>
       <c r="E3" t="n">
-        <v>21.21</v>
+        <v>20.27</v>
       </c>
       <c r="F3" t="n">
-        <v>2181.3</v>
+        <v>2047.68</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>241.01</v>
+        <v>232.43</v>
       </c>
       <c r="C5" t="n">
-        <v>7.32</v>
+        <v>7.18</v>
       </c>
       <c r="D5" t="n">
-        <v>233.69</v>
+        <v>225.25</v>
       </c>
       <c r="E5" t="n">
-        <v>262.97</v>
+        <v>253.96</v>
       </c>
       <c r="F5" t="n">
-        <v>1280.81</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>55.22999954223633</v>
+        <v>52.38999938964844</v>
       </c>
       <c r="F5" t="n">
-        <v>30486.95974731445</v>
+        <v>28919.27966308594</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>30486.95974731445</v>
+        <v>28919.27966308594</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>241.0099945068359</v>
+        <v>232.4299926757812</v>
       </c>
       <c r="F6" t="n">
-        <v>42176.74903869629</v>
+        <v>40675.24871826172</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>42176.74903869629</v>
+        <v>40675.24871826172</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.6200008392334</v>
+        <v>17.84000015258789</v>
       </c>
       <c r="F7" t="n">
-        <v>47071.36212158203</v>
+        <v>45099.52038574219</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>47071.36212158203</v>
+        <v>45099.52038574219</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4702</v>
+        <v>4606.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02176176414327757</v>
+        <v>-0.02653990441759113</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04674977738201247</v>
+        <v>-0.008757249861713556</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.83499908447266</v>
+        <v>73.65499877929688</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.05148150116748795</v>
+        <v>-0.05440795816404398</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09044505113433288</v>
+        <v>-0.01385732532170325</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.82</v>
+        <v>1.02</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CERRAR ARBITRAJE (Media alcanzada)</t>
+          <t>MANTENER</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>97489.94145202637</v>
+        <v>95590.97163467408</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-58125.12350463868</v>
+        <v>-57049.81170196534</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-39364.8179473877</v>
+        <v>-38541.15993270874</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.39</v>
+        <v>51.28</v>
       </c>
       <c r="C2" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="D2" t="n">
-        <v>50.25</v>
+        <v>49.19</v>
       </c>
       <c r="E2" t="n">
-        <v>58.81</v>
+        <v>57.56</v>
       </c>
       <c r="F2" t="n">
-        <v>1181.67</v>
+        <v>1156.04</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.84</v>
+        <v>17.47</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="D3" t="n">
-        <v>17.03</v>
+        <v>16.68</v>
       </c>
       <c r="E3" t="n">
-        <v>20.27</v>
+        <v>19.84</v>
       </c>
       <c r="F3" t="n">
-        <v>2047.68</v>
+        <v>1998.93</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>232.43</v>
+        <v>228.51</v>
       </c>
       <c r="C5" t="n">
-        <v>7.18</v>
+        <v>6.74</v>
       </c>
       <c r="D5" t="n">
-        <v>225.25</v>
+        <v>221.77</v>
       </c>
       <c r="E5" t="n">
-        <v>253.96</v>
+        <v>248.71</v>
       </c>
       <c r="F5" t="n">
-        <v>1256</v>
+        <v>1178.63</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.38999938964844</v>
+        <v>51.27999877929688</v>
       </c>
       <c r="F5" t="n">
-        <v>28919.27966308594</v>
+        <v>28306.55932617188</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28919.27966308594</v>
+        <v>28306.55932617188</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232.4299926757812</v>
+        <v>228.5099945068359</v>
       </c>
       <c r="F6" t="n">
-        <v>40675.24871826172</v>
+        <v>39989.24903869629</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>40675.24871826172</v>
+        <v>39989.24903869629</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.84000015258789</v>
+        <v>17.46999931335449</v>
       </c>
       <c r="F7" t="n">
-        <v>45099.52038574219</v>
+        <v>44164.15826416016</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>45099.52038574219</v>
+        <v>44164.15826416016</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4606.89990234375</v>
+        <v>4563</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02653990441759113</v>
+        <v>-0.03020129108986103</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.008757249861713556</v>
+        <v>-0.04603616539577304</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73.65499877929688</v>
+        <v>72.01000213623047</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.05440795816404398</v>
+        <v>-0.04578273861156235</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01385732532170325</v>
+        <v>-0.05083889956586052</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LIGERAMENTE ALCISTA (Parcial)</t>
+          <t>HOLD / CASH (Sin Tendencia)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>95590.97163467408</v>
+        <v>97518.91986846924</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+50.7%</t>
+          <t>+50.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-57049.81170196534</v>
+        <v>-57700.76576232911</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+34.3%</t>
+          <t>+34.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-38541.15993270874</v>
+        <v>-39818.15410614014</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51.28</v>
+        <v>52.29</v>
       </c>
       <c r="C2" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="D2" t="n">
-        <v>49.19</v>
+        <v>50.12</v>
       </c>
       <c r="E2" t="n">
-        <v>57.56</v>
+        <v>58.8</v>
       </c>
       <c r="F2" t="n">
-        <v>1156.04</v>
+        <v>1197.05</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.47</v>
+        <v>18.02</v>
       </c>
       <c r="C3" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>16.68</v>
+        <v>17.21</v>
       </c>
       <c r="E3" t="n">
-        <v>19.84</v>
+        <v>20.46</v>
       </c>
       <c r="F3" t="n">
-        <v>1998.93</v>
+        <v>2058.51</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>228.51</v>
+        <v>230.34</v>
       </c>
       <c r="C5" t="n">
-        <v>6.74</v>
+        <v>6.77</v>
       </c>
       <c r="D5" t="n">
-        <v>221.77</v>
+        <v>223.57</v>
       </c>
       <c r="E5" t="n">
-        <v>248.71</v>
+        <v>250.66</v>
       </c>
       <c r="F5" t="n">
-        <v>1178.63</v>
+        <v>1185.56</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>51.27999877929688</v>
+        <v>52.29000091552734</v>
       </c>
       <c r="F5" t="n">
-        <v>28306.55932617188</v>
+        <v>28864.08050537109</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28306.55932617188</v>
+        <v>28864.08050537109</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228.5099945068359</v>
+        <v>230.3399963378906</v>
       </c>
       <c r="F6" t="n">
-        <v>39989.24903869629</v>
+        <v>40309.49935913086</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39989.24903869629</v>
+        <v>40309.49935913086</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.46999931335449</v>
+        <v>18.02000045776367</v>
       </c>
       <c r="F7" t="n">
-        <v>44164.15826416016</v>
+        <v>45554.56115722656</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>44164.15826416016</v>
+        <v>45554.56115722656</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4563</v>
+        <v>4642.7001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.03020129108986103</v>
+        <v>-0.01326218381088917</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04603616539577304</v>
+        <v>-0.02937363987768882</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72.01000213623047</v>
+        <v>74.60500335693359</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.04578273861156235</v>
+        <v>-0.01139591893845004</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.05083889956586052</v>
+        <v>-0.01663428713423187</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.03</v>
+        <v>1.29</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,11 +600,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-85.0%</t>
+          <t>-42.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>97518.91986846924</v>
+        <v>84013.27502821552</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+50.3%</t>
+          <t>+24.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-57700.76576232911</v>
+        <v>-48313.77131397635</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+34.7%</t>
+          <t>+17.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-39818.15410614014</v>
+        <v>-35699.50371423915</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.29</v>
+        <v>51.81</v>
       </c>
       <c r="C2" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="D2" t="n">
-        <v>50.12</v>
+        <v>49.62</v>
       </c>
       <c r="E2" t="n">
-        <v>58.8</v>
+        <v>58.38</v>
       </c>
       <c r="F2" t="n">
-        <v>1197.05</v>
+        <v>1209.67</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.02</v>
+        <v>18.06</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="D3" t="n">
         <v>17.21</v>
       </c>
       <c r="E3" t="n">
-        <v>20.46</v>
+        <v>20.62</v>
       </c>
       <c r="F3" t="n">
-        <v>2058.51</v>
+        <v>2157.83</v>
       </c>
     </row>
     <row r="4">
@@ -761,12 +761,20 @@
           <t>PHAG.MI</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>56.93</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D4" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="E4" t="n">
+        <v>62.91</v>
+      </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>297.15</v>
       </c>
     </row>
     <row r="5">
@@ -776,19 +784,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>230.34</v>
+        <v>226.44</v>
       </c>
       <c r="C5" t="n">
-        <v>6.77</v>
+        <v>6.99</v>
       </c>
       <c r="D5" t="n">
-        <v>223.57</v>
+        <v>219.45</v>
       </c>
       <c r="E5" t="n">
-        <v>250.66</v>
+        <v>247.42</v>
       </c>
       <c r="F5" t="n">
-        <v>1185.56</v>
+        <v>1224.12</v>
       </c>
     </row>
     <row r="6">
@@ -797,12 +805,20 @@
           <t>GLDA.DE</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>156.17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>153.97</v>
+      </c>
+      <c r="E6" t="n">
+        <v>162.78</v>
+      </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>388.32</v>
       </c>
     </row>
     <row r="7">
@@ -811,12 +827,20 @@
           <t>SGLE.MI</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>104.53</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="D7" t="n">
+        <v>102.79</v>
+      </c>
+      <c r="E7" t="n">
+        <v>109.74</v>
+      </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>609.74</v>
       </c>
     </row>
   </sheetData>
@@ -902,14 +926,20 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>56.93000030517578</v>
+      </c>
+      <c r="F2" t="n">
+        <v>8482.570045471191</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Layer 1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>9944.396806849802</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -928,14 +958,20 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>156.1699981689453</v>
+      </c>
+      <c r="F3" t="n">
+        <v>27538.56583347712</v>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Layer 1</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>32284.36955682584</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -954,14 +990,20 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>104.5299987792969</v>
+      </c>
+      <c r="F4" t="n">
+        <v>36690.0295715332</v>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Layer 1</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>43012.93251438306</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -981,10 +1023,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.29000091552734</v>
+        <v>51.81000137329102</v>
       </c>
       <c r="F5" t="n">
-        <v>28864.08050537109</v>
+        <v>28599.12075805664</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +1034,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28864.08050537109</v>
+        <v>28599.12075805664</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1055,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230.3399963378906</v>
+        <v>226.4400024414062</v>
       </c>
       <c r="F6" t="n">
-        <v>40309.49935913086</v>
+        <v>39627.00042724609</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1066,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>40309.49935913086</v>
+        <v>39627.00042724609</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1087,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.02000045776367</v>
+        <v>18.05999946594238</v>
       </c>
       <c r="F7" t="n">
-        <v>45554.56115722656</v>
+        <v>45655.67864990234</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1098,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>45554.56115722656</v>
+        <v>45655.67864990234</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1150,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4642.7001953125</v>
+        <v>4625.60009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01326218381088917</v>
+        <v>-0.0204772485929976</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02937363987768882</v>
+        <v>-0.005568075318445609</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1166,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.60500335693359</v>
+        <v>75.83999633789062</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.01139591893845004</v>
+        <v>-0.007109001662359504</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01663428713423187</v>
+        <v>0.04268915517266336</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MANTENER</t>
+          <t>CERRAR ARBITRAJE (Media alcanzada)</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>84013.27502821552</v>
+        <v>82516.70963438707</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+24.3%</t>
+          <t>+24.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-48313.77131397635</v>
+        <v>-47850.96981912424</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+17.9%</t>
+          <t>+17.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-35699.50371423915</v>
+        <v>-34665.73981526281</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51.81</v>
+        <v>51.11</v>
       </c>
       <c r="C2" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="D2" t="n">
-        <v>49.62</v>
+        <v>48.96</v>
       </c>
       <c r="E2" t="n">
-        <v>58.38</v>
+        <v>57.56</v>
       </c>
       <c r="F2" t="n">
-        <v>1209.67</v>
+        <v>1186.36</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.06</v>
+        <v>17.58</v>
       </c>
       <c r="C3" t="n">
         <v>0.85</v>
       </c>
       <c r="D3" t="n">
-        <v>17.21</v>
+        <v>16.73</v>
       </c>
       <c r="E3" t="n">
-        <v>20.62</v>
+        <v>20.12</v>
       </c>
       <c r="F3" t="n">
-        <v>2157.83</v>
+        <v>2140.67</v>
       </c>
     </row>
     <row r="4">
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56.93</v>
+        <v>57</v>
       </c>
       <c r="C4" t="n">
         <v>1.99</v>
       </c>
       <c r="D4" t="n">
-        <v>54.94</v>
+        <v>55.01</v>
       </c>
       <c r="E4" t="n">
-        <v>62.91</v>
+        <v>62.97</v>
       </c>
       <c r="F4" t="n">
-        <v>297.15</v>
+        <v>296.4</v>
       </c>
     </row>
     <row r="5">
@@ -784,19 +784,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>226.44</v>
+        <v>223.95</v>
       </c>
       <c r="C5" t="n">
-        <v>6.99</v>
+        <v>6.64</v>
       </c>
       <c r="D5" t="n">
-        <v>219.45</v>
+        <v>217.31</v>
       </c>
       <c r="E5" t="n">
-        <v>247.42</v>
+        <v>243.87</v>
       </c>
       <c r="F5" t="n">
-        <v>1224.12</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="6">
@@ -806,19 +806,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>156.17</v>
+        <v>153.56</v>
       </c>
       <c r="C6" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="D6" t="n">
-        <v>153.97</v>
+        <v>151.27</v>
       </c>
       <c r="E6" t="n">
-        <v>162.78</v>
+        <v>160.43</v>
       </c>
       <c r="F6" t="n">
-        <v>388.32</v>
+        <v>404.06</v>
       </c>
     </row>
     <row r="7">
@@ -828,19 +828,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>104.53</v>
+        <v>102.55</v>
       </c>
       <c r="C7" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="D7" t="n">
-        <v>102.79</v>
+        <v>100.79</v>
       </c>
       <c r="E7" t="n">
-        <v>109.74</v>
+        <v>107.84</v>
       </c>
       <c r="F7" t="n">
-        <v>609.74</v>
+        <v>618.76</v>
       </c>
     </row>
   </sheetData>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>56.93000030517578</v>
+        <v>57</v>
       </c>
       <c r="F2" t="n">
-        <v>8482.570045471191</v>
+        <v>8493</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>9944.396806849802</v>
+        <v>9931.010353446007</v>
       </c>
     </row>
     <row r="3">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>156.1699981689453</v>
+        <v>153.5599975585938</v>
       </c>
       <c r="F3" t="n">
-        <v>27538.56583347712</v>
+        <v>27078.32587396949</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>32284.36955682584</v>
+        <v>31663.15019526385</v>
       </c>
     </row>
     <row r="4">
@@ -991,10 +991,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>104.5299987792969</v>
+        <v>102.5500030517578</v>
       </c>
       <c r="F4" t="n">
-        <v>36690.0295715332</v>
+        <v>35995.05107116699</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>43012.93251438306</v>
+        <v>42089.62967862677</v>
       </c>
     </row>
     <row r="5">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>51.81000137329102</v>
+        <v>51.11000061035156</v>
       </c>
       <c r="F5" t="n">
-        <v>28599.12075805664</v>
+        <v>28212.72033691406</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28599.12075805664</v>
+        <v>28212.72033691406</v>
       </c>
     </row>
     <row r="6">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>226.4400024414062</v>
+        <v>223.9499969482422</v>
       </c>
       <c r="F6" t="n">
-        <v>39627.00042724609</v>
+        <v>39191.24946594238</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39627.00042724609</v>
+        <v>39191.24946594238</v>
       </c>
     </row>
     <row r="7">
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.05999946594238</v>
+        <v>17.57999992370605</v>
       </c>
       <c r="F7" t="n">
-        <v>45655.67864990234</v>
+        <v>44442.23980712891</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>45655.67864990234</v>
+        <v>44442.23980712891</v>
       </c>
     </row>
   </sheetData>
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4625.60009765625</v>
+        <v>4527</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0204772485929976</v>
+        <v>-0.01404769683110096</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.005568075318445609</v>
+        <v>-0.02787317688788005</v>
       </c>
     </row>
     <row r="3">
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.83999633789062</v>
+        <v>73.13500213623047</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.007109001662359504</v>
+        <v>-0.000956214644810327</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04268915517266336</v>
+        <v>0.006523430769345362</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CERRAR ARBITRAJE (Media alcanzada)</t>
+          <t>MANTENER</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -600,11 +600,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-42.2%</t>
+          <t>-85.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>82516.70963438707</v>
+        <v>93820.18616485596</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+24.5%</t>
+          <t>+50.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-47850.96981912424</v>
+        <v>-56236.62257385254</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+17.7%</t>
+          <t>+34.1%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-34665.73981526281</v>
+        <v>-37583.56359100342</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51.11</v>
+        <v>50.52</v>
       </c>
       <c r="C2" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="D2" t="n">
-        <v>48.96</v>
+        <v>48.39</v>
       </c>
       <c r="E2" t="n">
-        <v>57.56</v>
+        <v>56.9</v>
       </c>
       <c r="F2" t="n">
-        <v>1186.36</v>
+        <v>1174.43</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.58</v>
+        <v>17.05</v>
       </c>
       <c r="C3" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="D3" t="n">
-        <v>16.73</v>
+        <v>16.19</v>
       </c>
       <c r="E3" t="n">
-        <v>20.12</v>
+        <v>19.64</v>
       </c>
       <c r="F3" t="n">
-        <v>2140.67</v>
+        <v>2179.48</v>
       </c>
     </row>
     <row r="4">
@@ -761,20 +761,12 @@
           <t>PHAG.MI</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>57</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="D4" t="n">
-        <v>55.01</v>
-      </c>
-      <c r="E4" t="n">
-        <v>62.97</v>
-      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>296.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -784,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>223.95</v>
+        <v>225.07</v>
       </c>
       <c r="C5" t="n">
-        <v>6.64</v>
+        <v>6.42</v>
       </c>
       <c r="D5" t="n">
-        <v>217.31</v>
+        <v>218.65</v>
       </c>
       <c r="E5" t="n">
-        <v>243.87</v>
+        <v>244.34</v>
       </c>
       <c r="F5" t="n">
-        <v>1162</v>
+        <v>1124.06</v>
       </c>
     </row>
     <row r="6">
@@ -805,20 +797,12 @@
           <t>GLDA.DE</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>153.56</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="D6" t="n">
-        <v>151.27</v>
-      </c>
-      <c r="E6" t="n">
-        <v>160.43</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>404.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -827,20 +811,12 @@
           <t>SGLE.MI</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>102.55</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="D7" t="n">
-        <v>100.79</v>
-      </c>
-      <c r="E7" t="n">
-        <v>107.84</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>618.76</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -926,20 +902,14 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>57</v>
-      </c>
-      <c r="F2" t="n">
-        <v>8493</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Layer 1</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>9931.010353446007</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -958,20 +928,14 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>153.5599975585938</v>
-      </c>
-      <c r="F3" t="n">
-        <v>27078.32587396949</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Layer 1</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>31663.15019526385</v>
-      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -990,20 +954,14 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>102.5500030517578</v>
-      </c>
-      <c r="F4" t="n">
-        <v>35995.05107116699</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Layer 1</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>42089.62967862677</v>
-      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1023,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>51.11000061035156</v>
+        <v>50.52000045776367</v>
       </c>
       <c r="F5" t="n">
-        <v>28212.72033691406</v>
+        <v>27887.04025268555</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1034,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28212.72033691406</v>
+        <v>27887.04025268555</v>
       </c>
     </row>
     <row r="6">
@@ -1055,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223.9499969482422</v>
+        <v>225.0700073242188</v>
       </c>
       <c r="F6" t="n">
-        <v>39191.24946594238</v>
+        <v>39387.25128173828</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1066,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39191.24946594238</v>
+        <v>39387.25128173828</v>
       </c>
     </row>
     <row r="7">
@@ -1087,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.57999992370605</v>
+        <v>17.04999923706055</v>
       </c>
       <c r="F7" t="n">
-        <v>44442.23980712891</v>
+        <v>43102.39807128906</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1098,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>44442.23980712891</v>
+        <v>43102.39807128906</v>
       </c>
     </row>
   </sheetData>
@@ -1150,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4527</v>
+        <v>4558.2001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01404769683110096</v>
+        <v>0.002860160046065152</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02787317688788005</v>
+        <v>-0.02123637033129755</v>
       </c>
     </row>
     <row r="3">
@@ -1166,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73.13500213623047</v>
+        <v>73.12000274658203</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.000956214644810327</v>
+        <v>0.02167142893082952</v>
       </c>
       <c r="D3" t="n">
-        <v>0.006523430769345362</v>
+        <v>0.01801584958834779</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.19</v>
+        <v>0.55</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MANTENER</t>
+          <t>CERRAR ARBITRAJE (Media alcanzada)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>93820.18616485596</v>
+        <v>100434.6222518921</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+50.9%</t>
+          <t>+51.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-56236.62257385254</v>
+        <v>-60459.34217224121</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+34.1%</t>
+          <t>+33.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-37583.56359100342</v>
+        <v>-39975.28007965088</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50.52</v>
+        <v>56.59</v>
       </c>
       <c r="C2" t="n">
-        <v>2.13</v>
+        <v>2.46</v>
       </c>
       <c r="D2" t="n">
-        <v>48.39</v>
+        <v>54.13</v>
       </c>
       <c r="E2" t="n">
-        <v>56.9</v>
+        <v>63.98</v>
       </c>
       <c r="F2" t="n">
-        <v>1174.43</v>
+        <v>1360.09</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.05</v>
+        <v>18.15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.86</v>
+        <v>1.01</v>
       </c>
       <c r="D3" t="n">
-        <v>16.19</v>
+        <v>17.14</v>
       </c>
       <c r="E3" t="n">
-        <v>19.64</v>
+        <v>21.17</v>
       </c>
       <c r="F3" t="n">
-        <v>2179.48</v>
+        <v>2547.86</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>225.07</v>
+        <v>234.5</v>
       </c>
       <c r="C5" t="n">
-        <v>6.42</v>
+        <v>6.99</v>
       </c>
       <c r="D5" t="n">
-        <v>218.65</v>
+        <v>227.51</v>
       </c>
       <c r="E5" t="n">
-        <v>244.34</v>
+        <v>255.48</v>
       </c>
       <c r="F5" t="n">
-        <v>1124.06</v>
+        <v>1223.78</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>50.52000045776367</v>
+        <v>56.59000015258789</v>
       </c>
       <c r="F5" t="n">
-        <v>27887.04025268555</v>
+        <v>31237.68008422852</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>27887.04025268555</v>
+        <v>31237.68008422852</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>225.0700073242188</v>
+        <v>234.5</v>
       </c>
       <c r="F6" t="n">
-        <v>39387.25128173828</v>
+        <v>41037.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39387.25128173828</v>
+        <v>41037.5</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.04999923706055</v>
+        <v>18.14999961853027</v>
       </c>
       <c r="F7" t="n">
-        <v>43102.39807128906</v>
+        <v>45883.19903564453</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>43102.39807128906</v>
+        <v>45883.19903564453</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4558.2001953125</v>
+        <v>4705.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.002860160046065152</v>
+        <v>0.03524590780323944</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02123637033129755</v>
+        <v>0.01037121892909432</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73.12000274658203</v>
+        <v>77.91999816894531</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02167142893082952</v>
+        <v>0.08873950876971559</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01801584958834779</v>
+        <v>0.08484395727938243</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.55</v>
+        <v>0.79</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100434.6222518921</v>
+        <v>99875.70594253539</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.2%</t>
+          <t>+51.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-60459.34217224121</v>
+        <v>-60069.78824005127</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.8%</t>
+          <t>+33.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-39975.28007965088</v>
+        <v>-39805.91770248413</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56.59</v>
+        <v>57.81</v>
       </c>
       <c r="C2" t="n">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="D2" t="n">
-        <v>54.13</v>
+        <v>55.3</v>
       </c>
       <c r="E2" t="n">
-        <v>63.98</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1360.09</v>
+        <v>1387.89</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.15</v>
+        <v>18.07</v>
       </c>
       <c r="C3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="D3" t="n">
-        <v>17.14</v>
+        <v>17.03</v>
       </c>
       <c r="E3" t="n">
-        <v>21.17</v>
+        <v>21.2</v>
       </c>
       <c r="F3" t="n">
-        <v>2547.86</v>
+        <v>2639.95</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>234.5</v>
+        <v>228.05</v>
       </c>
       <c r="C5" t="n">
-        <v>6.99</v>
+        <v>7.23</v>
       </c>
       <c r="D5" t="n">
-        <v>227.51</v>
+        <v>220.82</v>
       </c>
       <c r="E5" t="n">
-        <v>255.48</v>
+        <v>249.73</v>
       </c>
       <c r="F5" t="n">
-        <v>1223.78</v>
+        <v>1264.56</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.59000015258789</v>
+        <v>57.81000137329102</v>
       </c>
       <c r="F5" t="n">
-        <v>31237.68008422852</v>
+        <v>31911.12075805664</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>31237.68008422852</v>
+        <v>31911.12075805664</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>234.5</v>
+        <v>228.0500030517578</v>
       </c>
       <c r="F6" t="n">
-        <v>41037.5</v>
+        <v>39908.75053405762</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>41037.5</v>
+        <v>39908.75053405762</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.14999961853027</v>
+        <v>18.06999969482422</v>
       </c>
       <c r="F7" t="n">
-        <v>45883.19903564453</v>
+        <v>45680.95922851562</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>45883.19903564453</v>
+        <v>45680.95922851562</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4705.39990234375</v>
+        <v>4695.10009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03524590780323944</v>
+        <v>0.01408242007121885</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01037121892909432</v>
+        <v>-0.0202621121194454</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77.91999816894531</v>
+        <v>78.98000335693359</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08873950876971559</v>
+        <v>0.03988106939503755</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08484395727938243</v>
+        <v>0.0354366704845146</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.79</v>
+        <v>0.21</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>99875.70594253539</v>
+        <v>102264.0196159363</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.1%</t>
+          <t>+50.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-60069.78824005127</v>
+        <v>-61233.46863861084</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.9%</t>
+          <t>+34.1%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-39805.91770248413</v>
+        <v>-41030.55097732544</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57.81</v>
+        <v>59.14</v>
       </c>
       <c r="C2" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="D2" t="n">
-        <v>55.3</v>
+        <v>56.55</v>
       </c>
       <c r="E2" t="n">
-        <v>65.34999999999999</v>
+        <v>66.92</v>
       </c>
       <c r="F2" t="n">
-        <v>1387.89</v>
+        <v>1431.26</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.07</v>
+        <v>18.61</v>
       </c>
       <c r="C3" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="D3" t="n">
-        <v>17.03</v>
+        <v>17.53</v>
       </c>
       <c r="E3" t="n">
-        <v>21.2</v>
+        <v>21.86</v>
       </c>
       <c r="F3" t="n">
-        <v>2639.95</v>
+        <v>2737.46</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>228.05</v>
+        <v>232.11</v>
       </c>
       <c r="C5" t="n">
-        <v>7.23</v>
+        <v>7.17</v>
       </c>
       <c r="D5" t="n">
-        <v>220.82</v>
+        <v>224.94</v>
       </c>
       <c r="E5" t="n">
-        <v>249.73</v>
+        <v>253.62</v>
       </c>
       <c r="F5" t="n">
-        <v>1264.56</v>
+        <v>1254.75</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>57.81000137329102</v>
+        <v>59.13999938964844</v>
       </c>
       <c r="F5" t="n">
-        <v>31911.12075805664</v>
+        <v>32645.27966308594</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>31911.12075805664</v>
+        <v>32645.27966308594</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228.0500030517578</v>
+        <v>232.1100006103516</v>
       </c>
       <c r="F6" t="n">
-        <v>39908.75053405762</v>
+        <v>40619.25010681152</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39908.75053405762</v>
+        <v>40619.25010681152</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.06999969482422</v>
+        <v>18.61000061035156</v>
       </c>
       <c r="F7" t="n">
-        <v>45680.95922851562</v>
+        <v>47046.08154296875</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>45680.95922851562</v>
+        <v>47046.08154296875</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4695.10009765625</v>
+        <v>4723.7001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01408242007121885</v>
+        <v>0.02025968054325888</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0202621121194454</v>
+        <v>-0.01429406060018179</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.98000335693359</v>
+        <v>80.83499908447266</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03988106939503755</v>
+        <v>0.06430465585854983</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0354366704845146</v>
+        <v>0.05975587177912223</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.21</v>
+        <v>-0.52</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102264.0196159363</v>
+        <v>108985.1655014038</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+50.9%</t>
+          <t>+49.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-61233.46863861084</v>
+        <v>-63142.2973968506</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+34.1%</t>
+          <t>+35.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-41030.55097732544</v>
+        <v>-45842.86810455323</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59.14</v>
+        <v>62.29</v>
       </c>
       <c r="C2" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="D2" t="n">
-        <v>56.55</v>
+        <v>62.17</v>
       </c>
       <c r="E2" t="n">
-        <v>66.92</v>
+        <v>70.17</v>
       </c>
       <c r="F2" t="n">
-        <v>1431.26</v>
+        <v>68.42</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.61</v>
+        <v>20.67</v>
       </c>
       <c r="C3" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="D3" t="n">
-        <v>17.53</v>
+        <v>19.52</v>
       </c>
       <c r="E3" t="n">
-        <v>21.86</v>
+        <v>24.13</v>
       </c>
       <c r="F3" t="n">
-        <v>2737.46</v>
+        <v>2911.71</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>232.11</v>
+        <v>237.6</v>
       </c>
       <c r="C5" t="n">
-        <v>7.17</v>
+        <v>6.86</v>
       </c>
       <c r="D5" t="n">
-        <v>224.94</v>
+        <v>230.74</v>
       </c>
       <c r="E5" t="n">
-        <v>253.62</v>
+        <v>258.18</v>
       </c>
       <c r="F5" t="n">
-        <v>1254.75</v>
+        <v>1200.25</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>59.13999938964844</v>
+        <v>62.29000091552734</v>
       </c>
       <c r="F5" t="n">
-        <v>32645.27966308594</v>
+        <v>34384.08050537109</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>32645.27966308594</v>
+        <v>34384.08050537109</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232.1100006103516</v>
+        <v>237.6000061035156</v>
       </c>
       <c r="F6" t="n">
-        <v>40619.25010681152</v>
+        <v>41580.00106811523</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>40619.25010681152</v>
+        <v>41580.00106811523</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.61000061035156</v>
+        <v>20.67000007629395</v>
       </c>
       <c r="F7" t="n">
-        <v>47046.08154296875</v>
+        <v>52253.76019287109</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>47046.08154296875</v>
+        <v>52253.76019287109</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4723.7001953125</v>
+        <v>4763.2001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02025968054325888</v>
+        <v>0.04552447419037242</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01429406060018179</v>
+        <v>0.004386026779072294</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80.83499908447266</v>
+        <v>87.72499847412109</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06430465585854983</v>
+        <v>0.1999370304679031</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05975587177912223</v>
+        <v>0.1615666144826862</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.52</v>
+        <v>-0.54</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>108985.1655014038</v>
+        <v>109380.1407714844</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+49.2%</t>
+          <t>+49.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-63142.2973968506</v>
+        <v>-63813.30747070313</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+35.8%</t>
+          <t>+35.4%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-45842.86810455323</v>
+        <v>-45566.83330078125</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>62.29</v>
+        <v>63.78</v>
       </c>
       <c r="C2" t="n">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="D2" t="n">
-        <v>62.17</v>
+        <v>61.78</v>
       </c>
       <c r="E2" t="n">
-        <v>70.17</v>
+        <v>72.12</v>
       </c>
       <c r="F2" t="n">
-        <v>68.42</v>
+        <v>1105.29</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.67</v>
+        <v>20.57</v>
       </c>
       <c r="C3" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="D3" t="n">
-        <v>19.52</v>
+        <v>19.38</v>
       </c>
       <c r="E3" t="n">
-        <v>24.13</v>
+        <v>24.15</v>
       </c>
       <c r="F3" t="n">
-        <v>2911.71</v>
+        <v>3018.25</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>237.6</v>
+        <v>237</v>
       </c>
       <c r="C5" t="n">
-        <v>6.86</v>
+        <v>6.99</v>
       </c>
       <c r="D5" t="n">
-        <v>230.74</v>
+        <v>230.01</v>
       </c>
       <c r="E5" t="n">
-        <v>258.18</v>
+        <v>257.97</v>
       </c>
       <c r="F5" t="n">
-        <v>1200.25</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>62.29000091552734</v>
+        <v>63.77999877929688</v>
       </c>
       <c r="F5" t="n">
-        <v>34384.08050537109</v>
+        <v>35206.55932617188</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>34384.08050537109</v>
+        <v>35206.55932617188</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>237.6000061035156</v>
+        <v>237</v>
       </c>
       <c r="F6" t="n">
-        <v>41580.00106811523</v>
+        <v>41475</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>41580.00106811523</v>
+        <v>41475</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20.67000007629395</v>
+        <v>20.56999969482422</v>
       </c>
       <c r="F7" t="n">
-        <v>52253.76019287109</v>
+        <v>52000.95922851562</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>52253.76019287109</v>
+        <v>52000.95922851562</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4763.2001953125</v>
+        <v>4725.2001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04552447419037242</v>
+        <v>0.00924844483477183</v>
       </c>
       <c r="D2" t="n">
-        <v>0.004386026779072294</v>
+        <v>-0.02068389734455955</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>87.72499847412109</v>
+        <v>87.48000335693359</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1999370304679031</v>
+        <v>0.1388994644395467</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1615666144826862</v>
+        <v>0.1018881817178021</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.54</v>
+        <v>-0.51</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>109380.1407714844</v>
+        <v>110919.0217903137</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+49.6%</t>
+          <t>+49.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-63813.30747070313</v>
+        <v>-64229.27205963134</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+35.4%</t>
+          <t>+35.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-45566.83330078125</v>
+        <v>-46689.74973068237</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63.78</v>
+        <v>63.66</v>
       </c>
       <c r="C2" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="D2" t="n">
-        <v>61.78</v>
+        <v>61.77</v>
       </c>
       <c r="E2" t="n">
-        <v>72.12</v>
+        <v>72.02</v>
       </c>
       <c r="F2" t="n">
-        <v>1105.29</v>
+        <v>1045.19</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.57</v>
+        <v>21.05</v>
       </c>
       <c r="C3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="D3" t="n">
-        <v>19.38</v>
+        <v>19.83</v>
       </c>
       <c r="E3" t="n">
-        <v>24.15</v>
+        <v>24.7</v>
       </c>
       <c r="F3" t="n">
-        <v>3018.25</v>
+        <v>3077.84</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>237</v>
+        <v>240.79</v>
       </c>
       <c r="C5" t="n">
-        <v>6.99</v>
+        <v>7.31</v>
       </c>
       <c r="D5" t="n">
-        <v>230.01</v>
+        <v>233.48</v>
       </c>
       <c r="E5" t="n">
-        <v>257.97</v>
+        <v>262.73</v>
       </c>
       <c r="F5" t="n">
-        <v>1223</v>
+        <v>1280.06</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>63.77999877929688</v>
+        <v>63.65999984741211</v>
       </c>
       <c r="F5" t="n">
-        <v>35206.55932617188</v>
+        <v>35140.31991577148</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>35206.55932617188</v>
+        <v>35140.31991577148</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>237</v>
+        <v>240.7899932861328</v>
       </c>
       <c r="F6" t="n">
-        <v>41475</v>
+        <v>42138.24882507324</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>41475</v>
+        <v>42138.24882507324</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20.56999969482422</v>
+        <v>21.04999923706055</v>
       </c>
       <c r="F7" t="n">
-        <v>52000.95922851562</v>
+        <v>53214.39807128906</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>52000.95922851562</v>
+        <v>53214.39807128906</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4725.2001953125</v>
+        <v>4707.5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00924844483477183</v>
+        <v>0.001638409215818148</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02068389734455955</v>
+        <v>-0.01927083333333335</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>87.48000335693359</v>
+        <v>88.57499694824219</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1388994644395467</v>
+        <v>0.1113411494242751</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1018881817178021</v>
+        <v>0.114277087226045</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.51</v>
+        <v>-0.19</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>110919.0217903137</v>
+        <v>105860.0897109985</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+49.2%</t>
+          <t>+50.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-64229.27205963134</v>
+        <v>-62917.55188293457</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+35.8%</t>
+          <t>+34.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-46689.74973068237</v>
+        <v>-42942.53782806396</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63.66</v>
+        <v>61.09</v>
       </c>
       <c r="C2" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="D2" t="n">
-        <v>61.77</v>
+        <v>58.21</v>
       </c>
       <c r="E2" t="n">
-        <v>72.02</v>
+        <v>69.72</v>
       </c>
       <c r="F2" t="n">
-        <v>1045.19</v>
+        <v>1587.79</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.05</v>
+        <v>19.45</v>
       </c>
       <c r="C3" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="D3" t="n">
-        <v>19.83</v>
+        <v>18.16</v>
       </c>
       <c r="E3" t="n">
-        <v>24.7</v>
+        <v>23.32</v>
       </c>
       <c r="F3" t="n">
-        <v>3077.84</v>
+        <v>3259.31</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>240.79</v>
+        <v>238</v>
       </c>
       <c r="C5" t="n">
         <v>7.31</v>
       </c>
       <c r="D5" t="n">
-        <v>233.48</v>
+        <v>230.69</v>
       </c>
       <c r="E5" t="n">
-        <v>262.73</v>
+        <v>259.93</v>
       </c>
       <c r="F5" t="n">
-        <v>1280.06</v>
+        <v>1279.37</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>63.65999984741211</v>
+        <v>61.09000015258789</v>
       </c>
       <c r="F5" t="n">
-        <v>35140.31991577148</v>
+        <v>33721.68008422852</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>35140.31991577148</v>
+        <v>33721.68008422852</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>240.7899932861328</v>
+        <v>238</v>
       </c>
       <c r="F6" t="n">
-        <v>42138.24882507324</v>
+        <v>41650</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>42138.24882507324</v>
+        <v>41650</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>21.04999923706055</v>
+        <v>19.45000076293945</v>
       </c>
       <c r="F7" t="n">
-        <v>53214.39807128906</v>
+        <v>49169.60192871094</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>53214.39807128906</v>
+        <v>49169.60192871094</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4707.5</v>
+        <v>4665.60009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001638409215818148</v>
+        <v>-0.01160914452614303</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01927083333333335</v>
+        <v>-0.02503443957292384</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>88.57499694824219</v>
+        <v>84.23500061035156</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1113411494242751</v>
+        <v>0.04776421577991741</v>
       </c>
       <c r="D3" t="n">
-        <v>0.114277087226045</v>
+        <v>0.07161027913492757</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.19</v>
+        <v>0.71</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105860.0897109985</v>
+        <v>97892.9871307373</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+50.5%</t>
+          <t>+51.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-62917.55188293457</v>
+        <v>-59057.47968139649</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+34.5%</t>
+          <t>+33.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-42942.53782806396</v>
+        <v>-38835.50744934082</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>61.09</v>
+        <v>56.4</v>
       </c>
       <c r="C2" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="D2" t="n">
-        <v>58.21</v>
+        <v>53.26</v>
       </c>
       <c r="E2" t="n">
-        <v>69.72</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1587.79</v>
+        <v>1733.87</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.45</v>
+        <v>17.64</v>
       </c>
       <c r="C3" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="D3" t="n">
-        <v>18.16</v>
+        <v>16.24</v>
       </c>
       <c r="E3" t="n">
-        <v>23.32</v>
+        <v>21.84</v>
       </c>
       <c r="F3" t="n">
-        <v>3259.31</v>
+        <v>3536.49</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>238</v>
+        <v>225.38</v>
       </c>
       <c r="C5" t="n">
-        <v>7.31</v>
+        <v>8.07</v>
       </c>
       <c r="D5" t="n">
-        <v>230.69</v>
+        <v>217.31</v>
       </c>
       <c r="E5" t="n">
-        <v>259.93</v>
+        <v>249.6</v>
       </c>
       <c r="F5" t="n">
-        <v>1279.37</v>
+        <v>1412.62</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>61.09000015258789</v>
+        <v>56.40000152587891</v>
       </c>
       <c r="F5" t="n">
-        <v>33721.68008422852</v>
+        <v>31132.80084228516</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>33721.68008422852</v>
+        <v>31132.80084228516</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>238</v>
+        <v>225.3800048828125</v>
       </c>
       <c r="F6" t="n">
-        <v>41650</v>
+        <v>39441.50085449219</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>41650</v>
+        <v>39441.50085449219</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>19.45000076293945</v>
+        <v>17.63999938964844</v>
       </c>
       <c r="F7" t="n">
-        <v>49169.60192871094</v>
+        <v>44593.91845703125</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>49169.60192871094</v>
+        <v>44593.91845703125</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4665.60009765625</v>
+        <v>4543.60009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01160914452614303</v>
+        <v>-0.03710769712180328</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02503443957292384</v>
+        <v>-0.0646409736675323</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>84.23500061035156</v>
+        <v>76.29499816894531</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04776421577991741</v>
+        <v>-0.1075042683019343</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07161027913492757</v>
+        <v>-0.0665908251064562</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>97892.9871307373</v>
+        <v>96513.17389221191</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.3%</t>
+          <t>+51.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-59057.47968139649</v>
+        <v>-58557.13883666992</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.7%</t>
+          <t>+33.4%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-38835.50744934082</v>
+        <v>-37956.03505554199</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56.4</v>
+        <v>55.19</v>
       </c>
       <c r="C2" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="D2" t="n">
-        <v>53.26</v>
+        <v>52.09</v>
       </c>
       <c r="E2" t="n">
-        <v>65.81999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1733.87</v>
+        <v>1712.38</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.64</v>
+        <v>17.26</v>
       </c>
       <c r="C3" t="n">
         <v>1.4</v>
       </c>
       <c r="D3" t="n">
-        <v>16.24</v>
+        <v>15.86</v>
       </c>
       <c r="E3" t="n">
-        <v>21.84</v>
+        <v>21.46</v>
       </c>
       <c r="F3" t="n">
-        <v>3536.49</v>
+        <v>3540.1</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>225.38</v>
+        <v>225.41</v>
       </c>
       <c r="C5" t="n">
-        <v>8.07</v>
+        <v>7.85</v>
       </c>
       <c r="D5" t="n">
-        <v>217.31</v>
+        <v>217.56</v>
       </c>
       <c r="E5" t="n">
-        <v>249.6</v>
+        <v>248.97</v>
       </c>
       <c r="F5" t="n">
-        <v>1412.62</v>
+        <v>1374.62</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.40000152587891</v>
+        <v>55.18999862670898</v>
       </c>
       <c r="F5" t="n">
-        <v>31132.80084228516</v>
+        <v>30464.87924194336</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>31132.80084228516</v>
+        <v>30464.87924194336</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>225.3800048828125</v>
+        <v>225.4100036621094</v>
       </c>
       <c r="F6" t="n">
-        <v>39441.50085449219</v>
+        <v>39446.75064086914</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39441.50085449219</v>
+        <v>39446.75064086914</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.63999938964844</v>
+        <v>17.26000022888184</v>
       </c>
       <c r="F7" t="n">
-        <v>44593.91845703125</v>
+        <v>43633.28057861328</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>44593.91845703125</v>
+        <v>43633.28057861328</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4543.60009765625</v>
+        <v>4583.10009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.03710769712180328</v>
+        <v>-0.02020266761310996</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0646409736675323</v>
+        <v>-0.04649856352913173</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>76.29499816894531</v>
+        <v>78.93000030517578</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1075042683019343</v>
+        <v>-0.07282975623487709</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0665908251064562</v>
+        <v>-0.01277027353925153</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.86</v>
+        <v>1.15</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CERRAR ARBITRAJE (Media alcanzada)</t>
+          <t>MANTENER</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HOLD / CASH (Sin Tendencia)</t>
+          <t>LIGERAMENTE ALCISTA (Parcial)</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>96513.17389221191</v>
+        <v>93093.54862747192</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.6%</t>
+          <t>+52.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-58557.13883666992</v>
+        <v>-57211.55818023681</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.4%</t>
+          <t>+32.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-37956.03505554199</v>
+        <v>-35881.9904472351</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55.19</v>
+        <v>52.87</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="D2" t="n">
-        <v>52.09</v>
+        <v>49.72</v>
       </c>
       <c r="E2" t="n">
-        <v>64.5</v>
+        <v>62.32</v>
       </c>
       <c r="F2" t="n">
-        <v>1712.38</v>
+        <v>1738.01</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.26</v>
+        <v>16.36</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="D3" t="n">
-        <v>15.86</v>
+        <v>14.94</v>
       </c>
       <c r="E3" t="n">
-        <v>21.46</v>
+        <v>20.62</v>
       </c>
       <c r="F3" t="n">
-        <v>3540.1</v>
+        <v>3591.2</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>225.41</v>
+        <v>222.74</v>
       </c>
       <c r="C5" t="n">
         <v>7.85</v>
       </c>
       <c r="D5" t="n">
-        <v>217.56</v>
+        <v>214.89</v>
       </c>
       <c r="E5" t="n">
-        <v>248.97</v>
+        <v>246.3</v>
       </c>
       <c r="F5" t="n">
-        <v>1374.62</v>
+        <v>1374.37</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>55.18999862670898</v>
+        <v>52.86999893188477</v>
       </c>
       <c r="F5" t="n">
-        <v>30464.87924194336</v>
+        <v>29184.23941040039</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>30464.87924194336</v>
+        <v>29184.23941040039</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>225.4100036621094</v>
+        <v>222.7400054931641</v>
       </c>
       <c r="F6" t="n">
-        <v>39446.75064086914</v>
+        <v>38979.50096130371</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39446.75064086914</v>
+        <v>38979.50096130371</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.26000022888184</v>
+        <v>16.36000061035156</v>
       </c>
       <c r="F7" t="n">
-        <v>43633.28057861328</v>
+        <v>41358.08154296875</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>43633.28057861328</v>
+        <v>41358.08154296875</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4583.10009765625</v>
+        <v>4484</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02020266761310996</v>
+        <v>-0.04549038602457778</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04649856352913173</v>
+        <v>-0.04563253592713523</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.93000030517578</v>
+        <v>74.25499725341797</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.07282975623487709</v>
+        <v>-0.1646229317172283</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01277027353925153</v>
+        <v>-0.0282159083318464</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.15</v>
+        <v>0.97</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MANTENER</t>
+          <t>CERRAR ARBITRAJE (Media alcanzada)</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LIGERAMENTE ALCISTA (Parcial)</t>
+          <t>HOLD / CASH (Sin Tendencia)</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>93093.54862747192</v>
+        <v>96139.63437805175</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+52.2%</t>
+          <t>+51.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-57211.55818023681</v>
+        <v>-58363.86621704102</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+32.8%</t>
+          <t>+33.4%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-35881.9904472351</v>
+        <v>-37775.76816101075</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.87</v>
+        <v>54.83</v>
       </c>
       <c r="C2" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="D2" t="n">
-        <v>49.72</v>
+        <v>51.71</v>
       </c>
       <c r="E2" t="n">
-        <v>62.32</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1738.01</v>
+        <v>1720.76</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.36</v>
+        <v>17.18</v>
       </c>
       <c r="C3" t="n">
         <v>1.42</v>
       </c>
       <c r="D3" t="n">
-        <v>14.94</v>
+        <v>15.76</v>
       </c>
       <c r="E3" t="n">
-        <v>20.62</v>
+        <v>21.45</v>
       </c>
       <c r="F3" t="n">
-        <v>3591.2</v>
+        <v>3596.98</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>222.74</v>
+        <v>225.19</v>
       </c>
       <c r="C5" t="n">
-        <v>7.85</v>
+        <v>7.84</v>
       </c>
       <c r="D5" t="n">
-        <v>214.89</v>
+        <v>217.35</v>
       </c>
       <c r="E5" t="n">
-        <v>246.3</v>
+        <v>248.71</v>
       </c>
       <c r="F5" t="n">
-        <v>1374.37</v>
+        <v>1372.09</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.86999893188477</v>
+        <v>54.83000183105469</v>
       </c>
       <c r="F5" t="n">
-        <v>29184.23941040039</v>
+        <v>30266.16101074219</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>29184.23941040039</v>
+        <v>30266.16101074219</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222.7400054931641</v>
+        <v>225.1900024414062</v>
       </c>
       <c r="F6" t="n">
-        <v>38979.50096130371</v>
+        <v>39408.25042724609</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>38979.50096130371</v>
+        <v>39408.25042724609</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.36000061035156</v>
+        <v>17.18000030517578</v>
       </c>
       <c r="F7" t="n">
-        <v>41358.08154296875</v>
+        <v>43431.04077148438</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>41358.08154296875</v>
+        <v>43431.04077148438</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4484</v>
+        <v>4540.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.04549038602457778</v>
+        <v>-0.02943506817681996</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04563253592713523</v>
+        <v>-0.04059167409535125</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.25499725341797</v>
+        <v>75.91999816894531</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1646229317172283</v>
+        <v>-0.1058979192936736</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0282159083318464</v>
+        <v>-0.02532961408542223</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.97</v>
+        <v>1.03</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CERRAR ARBITRAJE (Media alcanzada)</t>
+          <t>MANTENER</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>96139.63437805175</v>
+        <v>96480.09745788574</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.6%</t>
+          <t>+51.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-58363.86621704102</v>
+        <v>-58420.99923706055</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.4%</t>
+          <t>+33.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-37775.76816101075</v>
+        <v>-38059.0982208252</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54.83</v>
+        <v>54.8</v>
       </c>
       <c r="C2" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="D2" t="n">
-        <v>51.71</v>
+        <v>51.65</v>
       </c>
       <c r="E2" t="n">
-        <v>64.18000000000001</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1720.76</v>
+        <v>1741.48</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.18</v>
+        <v>17.3</v>
       </c>
       <c r="C3" t="n">
         <v>1.42</v>
       </c>
       <c r="D3" t="n">
-        <v>15.76</v>
+        <v>15.88</v>
       </c>
       <c r="E3" t="n">
-        <v>21.45</v>
+        <v>21.56</v>
       </c>
       <c r="F3" t="n">
-        <v>3596.98</v>
+        <v>3589.76</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>225.19</v>
+        <v>225.84</v>
       </c>
       <c r="C5" t="n">
-        <v>7.84</v>
+        <v>7.93</v>
       </c>
       <c r="D5" t="n">
-        <v>217.35</v>
+        <v>217.91</v>
       </c>
       <c r="E5" t="n">
-        <v>248.71</v>
+        <v>249.64</v>
       </c>
       <c r="F5" t="n">
-        <v>1372.09</v>
+        <v>1388.12</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54.83000183105469</v>
+        <v>54.79999923706055</v>
       </c>
       <c r="F5" t="n">
-        <v>30266.16101074219</v>
+        <v>30249.59957885742</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>30266.16101074219</v>
+        <v>30249.59957885742</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>225.1900024414062</v>
+        <v>225.8399963378906</v>
       </c>
       <c r="F6" t="n">
-        <v>39408.25042724609</v>
+        <v>39521.99935913086</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39408.25042724609</v>
+        <v>39521.99935913086</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.18000030517578</v>
+        <v>17.29999923706055</v>
       </c>
       <c r="F7" t="n">
-        <v>43431.04077148438</v>
+        <v>43734.39807128906</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>43431.04077148438</v>
+        <v>43734.39807128906</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4540.39990234375</v>
+        <v>4543.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02943506817681996</v>
+        <v>-0.002721783852528303</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04059167409535125</v>
+        <v>-0.03436700430518957</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.91999816894531</v>
+        <v>77.03500366210938</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1058979192936736</v>
+        <v>-0.001632942102883339</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02532961408542223</v>
+        <v>0.02080444444983631</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>96480.09745788574</v>
+        <v>95441.03323516845</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.5%</t>
+          <t>+51.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-58420.99923706055</v>
+        <v>-58129.77281799317</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.5%</t>
+          <t>+33.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-38059.0982208252</v>
+        <v>-37311.2604171753</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54.8</v>
+        <v>53.94</v>
       </c>
       <c r="C2" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="D2" t="n">
-        <v>51.65</v>
+        <v>50.75</v>
       </c>
       <c r="E2" t="n">
-        <v>64.26000000000001</v>
+        <v>63.51</v>
       </c>
       <c r="F2" t="n">
-        <v>1741.48</v>
+        <v>1760.96</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.3</v>
+        <v>16.98</v>
       </c>
       <c r="C3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="D3" t="n">
-        <v>15.88</v>
+        <v>15.57</v>
       </c>
       <c r="E3" t="n">
-        <v>21.56</v>
+        <v>21.22</v>
       </c>
       <c r="F3" t="n">
-        <v>3589.76</v>
+        <v>3576.22</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>225.84</v>
+        <v>226.19</v>
       </c>
       <c r="C5" t="n">
-        <v>7.93</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>217.91</v>
+        <v>218.14</v>
       </c>
       <c r="E5" t="n">
-        <v>249.64</v>
+        <v>250.35</v>
       </c>
       <c r="F5" t="n">
-        <v>1388.12</v>
+        <v>1409.62</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54.79999923706055</v>
+        <v>53.93999862670898</v>
       </c>
       <c r="F5" t="n">
-        <v>30249.59957885742</v>
+        <v>29774.87924194336</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>30249.59957885742</v>
+        <v>29774.87924194336</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>225.8399963378906</v>
+        <v>226.1900024414062</v>
       </c>
       <c r="F6" t="n">
-        <v>39521.99935913086</v>
+        <v>39583.25042724609</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39521.99935913086</v>
+        <v>39583.25042724609</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.29999923706055</v>
+        <v>16.97999954223633</v>
       </c>
       <c r="F7" t="n">
-        <v>43734.39807128906</v>
+        <v>42925.43884277344</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>43734.39807128906</v>
+        <v>42925.43884277344</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4543.39990234375</v>
+        <v>4510.5</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.002721783852528303</v>
+        <v>-0.009943326447507728</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.03436700430518957</v>
+        <v>-0.04135939589323212</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77.03500366210938</v>
+        <v>75.91500091552734</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.001632942102883339</v>
+        <v>-0.01614808189370265</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02080444444983631</v>
+        <v>0.005963090167285579</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -752,7 +752,7 @@
         <v>21.22</v>
       </c>
       <c r="F3" t="n">
-        <v>3576.22</v>
+        <v>3573.79</v>
       </c>
     </row>
     <row r="4">
@@ -779,16 +779,16 @@
         <v>226.19</v>
       </c>
       <c r="C5" t="n">
-        <v>8.050000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="D5" t="n">
-        <v>218.14</v>
+        <v>218.13</v>
       </c>
       <c r="E5" t="n">
-        <v>250.35</v>
+        <v>250.37</v>
       </c>
       <c r="F5" t="n">
-        <v>1409.62</v>
+        <v>1410.25</v>
       </c>
     </row>
     <row r="6">
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4510.5</v>
+        <v>4576.10009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.009943326447507728</v>
+        <v>0.01548949159932578</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04135939589323212</v>
+        <v>-0.02123878315472472</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.91500091552734</v>
+        <v>78.54000091552734</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.01614808189370265</v>
+        <v>0.0496070700874891</v>
       </c>
       <c r="D3" t="n">
-        <v>0.005963090167285579</v>
+        <v>0.04715814888992176</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.01</v>
+        <v>0.08</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MANTENER</t>
+          <t>CERRAR ARBITRAJE (Media alcanzada)</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>95441.03323516845</v>
+        <v>97838.13598327637</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.8%</t>
+          <t>+51.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-58129.77281799317</v>
+        <v>-59151.08064575196</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.2%</t>
+          <t>+33.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-37311.2604171753</v>
+        <v>-38687.05533752442</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53.94</v>
+        <v>55.35</v>
       </c>
       <c r="C2" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="D2" t="n">
-        <v>50.75</v>
+        <v>52.13</v>
       </c>
       <c r="E2" t="n">
-        <v>63.51</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
-        <v>1760.96</v>
+        <v>1774.97</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.98</v>
+        <v>17.58</v>
       </c>
       <c r="C3" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="D3" t="n">
-        <v>15.57</v>
+        <v>16.19</v>
       </c>
       <c r="E3" t="n">
-        <v>21.22</v>
+        <v>21.75</v>
       </c>
       <c r="F3" t="n">
-        <v>3573.79</v>
+        <v>3516.05</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>226.19</v>
+        <v>229.19</v>
       </c>
       <c r="C5" t="n">
-        <v>8.06</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>218.13</v>
+        <v>221.05</v>
       </c>
       <c r="E5" t="n">
-        <v>250.37</v>
+        <v>253.6</v>
       </c>
       <c r="F5" t="n">
-        <v>1410.25</v>
+        <v>1423.75</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53.93999862670898</v>
+        <v>55.34999847412109</v>
       </c>
       <c r="F5" t="n">
-        <v>29774.87924194336</v>
+        <v>30553.19915771484</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>29774.87924194336</v>
+        <v>30553.19915771484</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>226.1900024414062</v>
+        <v>229.1900024414062</v>
       </c>
       <c r="F6" t="n">
-        <v>39583.25042724609</v>
+        <v>40108.25042724609</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39583.25042724609</v>
+        <v>40108.25042724609</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.97999954223633</v>
+        <v>17.57999992370605</v>
       </c>
       <c r="F7" t="n">
-        <v>42925.43884277344</v>
+        <v>44442.23980712891</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>42925.43884277344</v>
+        <v>44442.23980712891</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4576.10009765625</v>
+        <v>4510.7998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01548949159932578</v>
+        <v>-0.004524088205065002</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02123878315472472</v>
+        <v>-0.01757599810791677</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.54000091552734</v>
+        <v>77.51499938964844</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0496070700874891</v>
+        <v>0.02193776628348876</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04715814888992176</v>
+        <v>0.05887572502956195</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.08</v>
+        <v>0.42</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HOLD / CASH (Sin Tendencia)</t>
+          <t>LIGERAMENTE ALCISTA (Parcial)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>97838.13598327637</v>
+        <v>94622.39218597412</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.4%</t>
+          <t>+51.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-59151.08064575196</v>
+        <v>-57364.09390563965</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.6%</t>
+          <t>+33.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-38687.05533752442</v>
+        <v>-37258.29828033447</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55.35</v>
+        <v>53.32</v>
       </c>
       <c r="C2" t="n">
-        <v>3.22</v>
+        <v>2.93</v>
       </c>
       <c r="D2" t="n">
-        <v>52.13</v>
+        <v>50.39</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>62.11</v>
       </c>
       <c r="F2" t="n">
-        <v>1774.97</v>
+        <v>1616.51</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.58</v>
+        <v>16.94</v>
       </c>
       <c r="C3" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="D3" t="n">
-        <v>16.19</v>
+        <v>15.68</v>
       </c>
       <c r="E3" t="n">
-        <v>21.75</v>
+        <v>20.71</v>
       </c>
       <c r="F3" t="n">
-        <v>3516.05</v>
+        <v>3174.87</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>229.19</v>
+        <v>223.22</v>
       </c>
       <c r="C5" t="n">
-        <v>8.140000000000001</v>
+        <v>7.78</v>
       </c>
       <c r="D5" t="n">
-        <v>221.05</v>
+        <v>215.44</v>
       </c>
       <c r="E5" t="n">
-        <v>253.6</v>
+        <v>246.55</v>
       </c>
       <c r="F5" t="n">
-        <v>1423.75</v>
+        <v>1360.81</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>55.34999847412109</v>
+        <v>53.31999969482422</v>
       </c>
       <c r="F5" t="n">
-        <v>30553.19915771484</v>
+        <v>29432.63983154297</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>30553.19915771484</v>
+        <v>29432.63983154297</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229.1900024414062</v>
+        <v>223.2200012207031</v>
       </c>
       <c r="F6" t="n">
-        <v>40108.25042724609</v>
+        <v>39063.50021362305</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>40108.25042724609</v>
+        <v>39063.50021362305</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.57999992370605</v>
+        <v>16.94000053405762</v>
       </c>
       <c r="F7" t="n">
-        <v>44442.23980712891</v>
+        <v>42824.32135009766</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>44442.23980712891</v>
+        <v>42824.32135009766</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4510.7998046875</v>
+        <v>4482.7998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.004524088205065002</v>
+        <v>-0.01255561973044395</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01757599810791677</v>
+        <v>-0.0137288541634214</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77.51499938964844</v>
+        <v>74.875</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02193776628348876</v>
+        <v>-0.02014030721257032</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05887572502956195</v>
+        <v>0.04619318063102384</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.42</v>
+        <v>0.33</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LIGERAMENTE ALCISTA (Parcial)</t>
+          <t>HOLD / CASH (Sin Tendencia)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>94622.39218597412</v>
+        <v>97230.51389312744</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.5%</t>
+          <t>+51.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-57364.09390563965</v>
+        <v>-58482.43550109864</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.5%</t>
+          <t>+33.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-37258.29828033447</v>
+        <v>-38748.07839202881</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53.32</v>
+        <v>55.16</v>
       </c>
       <c r="C2" t="n">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="D2" t="n">
-        <v>50.39</v>
+        <v>52.31</v>
       </c>
       <c r="E2" t="n">
-        <v>62.11</v>
+        <v>63.71</v>
       </c>
       <c r="F2" t="n">
-        <v>1616.51</v>
+        <v>1572.76</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.94</v>
+        <v>17.59</v>
       </c>
       <c r="C3" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="D3" t="n">
-        <v>15.68</v>
+        <v>16.36</v>
       </c>
       <c r="E3" t="n">
-        <v>20.71</v>
+        <v>21.28</v>
       </c>
       <c r="F3" t="n">
-        <v>3174.87</v>
+        <v>3112.65</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>223.22</v>
+        <v>225.56</v>
       </c>
       <c r="C5" t="n">
-        <v>7.78</v>
+        <v>7.51</v>
       </c>
       <c r="D5" t="n">
-        <v>215.44</v>
+        <v>218.05</v>
       </c>
       <c r="E5" t="n">
-        <v>246.55</v>
+        <v>248.1</v>
       </c>
       <c r="F5" t="n">
-        <v>1360.81</v>
+        <v>1315.06</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53.31999969482422</v>
+        <v>55.15999984741211</v>
       </c>
       <c r="F5" t="n">
-        <v>29432.63983154297</v>
+        <v>30448.31991577148</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>29432.63983154297</v>
+        <v>30448.31991577148</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223.2200012207031</v>
+        <v>225.5599975585938</v>
       </c>
       <c r="F6" t="n">
-        <v>39063.50021362305</v>
+        <v>39472.99957275391</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39063.50021362305</v>
+        <v>39472.99957275391</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.94000053405762</v>
+        <v>17.59000015258789</v>
       </c>
       <c r="F7" t="n">
-        <v>42824.32135009766</v>
+        <v>44467.52038574219</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>42824.32135009766</v>
+        <v>44467.52038574219</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4482.7998046875</v>
+        <v>4525.7998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01255561973044395</v>
+        <v>0.001061668809444916</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0137288541634214</v>
+        <v>-0.01926460807037966</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.875</v>
+        <v>76.00499725341797</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.02014030721257032</v>
+        <v>0.001475755538079326</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04619318063102384</v>
+        <v>0.03360351383363458</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.33</v>
+        <v>0.08</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>97230.51389312744</v>
+        <v>99240.51031723022</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.1%</t>
+          <t>+51.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-58482.43550109864</v>
+        <v>-60155.6262374878</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.9%</t>
+          <t>+33.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-38748.07839202881</v>
+        <v>-39084.88407974243</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55.16</v>
+        <v>56.99</v>
       </c>
       <c r="C2" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="D2" t="n">
-        <v>52.31</v>
+        <v>54.13</v>
       </c>
       <c r="E2" t="n">
-        <v>63.71</v>
+        <v>65.56</v>
       </c>
       <c r="F2" t="n">
-        <v>1572.76</v>
+        <v>1576.42</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.59</v>
+        <v>17.77</v>
       </c>
       <c r="C3" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="D3" t="n">
-        <v>16.36</v>
+        <v>16.57</v>
       </c>
       <c r="E3" t="n">
-        <v>21.28</v>
+        <v>21.38</v>
       </c>
       <c r="F3" t="n">
-        <v>3112.65</v>
+        <v>3040.61</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>225.56</v>
+        <v>230.7</v>
       </c>
       <c r="C5" t="n">
-        <v>7.51</v>
+        <v>7.67</v>
       </c>
       <c r="D5" t="n">
-        <v>218.05</v>
+        <v>223.03</v>
       </c>
       <c r="E5" t="n">
-        <v>248.1</v>
+        <v>253.72</v>
       </c>
       <c r="F5" t="n">
-        <v>1315.06</v>
+        <v>1342.87</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>55.15999984741211</v>
+        <v>56.9900016784668</v>
       </c>
       <c r="F5" t="n">
-        <v>30448.31991577148</v>
+        <v>31458.48092651367</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>30448.31991577148</v>
+        <v>31458.48092651367</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>225.5599975585938</v>
+        <v>230.6999969482422</v>
       </c>
       <c r="F6" t="n">
-        <v>39472.99957275391</v>
+        <v>40372.49946594238</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39472.99957275391</v>
+        <v>40372.49946594238</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.59000015258789</v>
+        <v>17.77000045776367</v>
       </c>
       <c r="F7" t="n">
-        <v>44467.52038574219</v>
+        <v>44922.56115722656</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>44467.52038574219</v>
+        <v>44922.56115722656</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4525.7998046875</v>
+        <v>4569.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001061668809444916</v>
+        <v>0.01081616950757569</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01926460807037966</v>
+        <v>-0.009708169777585374</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>76.00499725341797</v>
+        <v>75.58499908447266</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001475755538079326</v>
+        <v>-0.004058327729718036</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03360351383363458</v>
+        <v>0.02789189487550026</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.08</v>
+        <v>0.33</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HOLD / CASH (Sin Tendencia)</t>
+          <t>LIGERAMENTE ALCISTA (Parcial)</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>99240.51031723022</v>
+        <v>97672.32787780762</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.5%</t>
+          <t>+51.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-60155.6262374878</v>
+        <v>-59076.63661499023</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.5%</t>
+          <t>+33.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-39084.88407974243</v>
+        <v>-38595.69126281739</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56.99</v>
+        <v>55.5</v>
       </c>
       <c r="C2" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
       <c r="D2" t="n">
-        <v>54.13</v>
+        <v>52.69</v>
       </c>
       <c r="E2" t="n">
-        <v>65.56</v>
+        <v>63.92</v>
       </c>
       <c r="F2" t="n">
-        <v>1576.42</v>
+        <v>1550.07</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.77</v>
+        <v>17.54</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="D3" t="n">
-        <v>16.57</v>
+        <v>16.42</v>
       </c>
       <c r="E3" t="n">
-        <v>21.38</v>
+        <v>20.89</v>
       </c>
       <c r="F3" t="n">
-        <v>3040.61</v>
+        <v>2819.36</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>230.7</v>
+        <v>228.18</v>
       </c>
       <c r="C5" t="n">
-        <v>7.67</v>
+        <v>7.86</v>
       </c>
       <c r="D5" t="n">
-        <v>223.03</v>
+        <v>220.32</v>
       </c>
       <c r="E5" t="n">
-        <v>253.72</v>
+        <v>251.77</v>
       </c>
       <c r="F5" t="n">
-        <v>1342.87</v>
+        <v>1376.19</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56.9900016784668</v>
+        <v>55.5</v>
       </c>
       <c r="F5" t="n">
-        <v>31458.48092651367</v>
+        <v>30636</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>31458.48092651367</v>
+        <v>30636</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230.6999969482422</v>
+        <v>228.1799926757812</v>
       </c>
       <c r="F6" t="n">
-        <v>40372.49946594238</v>
+        <v>39931.49871826172</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>40372.49946594238</v>
+        <v>39931.49871826172</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.77000045776367</v>
+        <v>17.54000091552734</v>
       </c>
       <c r="F7" t="n">
-        <v>44922.56115722656</v>
+        <v>44341.12231445312</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>44922.56115722656</v>
+        <v>44341.12231445312</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4569.89990234375</v>
+        <v>4517.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01081616950757569</v>
+        <v>0.003777442087123495</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.009708169777585374</v>
+        <v>-0.0004646747773536797</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.58499908447266</v>
+        <v>75.40000152587891</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.004058327729718036</v>
+        <v>-0.01186028144521856</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02789189487550026</v>
+        <v>0.03185902910022276</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.33</v>
+        <v>0.02</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>97672.32787780762</v>
+        <v>99241.57844619751</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.4%</t>
+          <t>+51.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-59076.63661499023</v>
+        <v>-60080.9202835083</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.6%</t>
+          <t>+33.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-38595.69126281739</v>
+        <v>-39160.65816268921</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55.5</v>
+        <v>55.2</v>
       </c>
       <c r="C2" t="n">
-        <v>2.81</v>
+        <v>2.66</v>
       </c>
       <c r="D2" t="n">
-        <v>52.69</v>
+        <v>52.54</v>
       </c>
       <c r="E2" t="n">
-        <v>63.92</v>
+        <v>63.18</v>
       </c>
       <c r="F2" t="n">
-        <v>1550.07</v>
+        <v>1468.13</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.54</v>
+        <v>17.8</v>
       </c>
       <c r="C3" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="D3" t="n">
-        <v>16.42</v>
+        <v>16.75</v>
       </c>
       <c r="E3" t="n">
-        <v>20.89</v>
+        <v>20.95</v>
       </c>
       <c r="F3" t="n">
-        <v>2819.36</v>
+        <v>2651.51</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>228.18</v>
+        <v>235.92</v>
       </c>
       <c r="C5" t="n">
-        <v>7.86</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>220.32</v>
+        <v>227.92</v>
       </c>
       <c r="E5" t="n">
-        <v>251.77</v>
+        <v>259.92</v>
       </c>
       <c r="F5" t="n">
-        <v>1376.19</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>55.5</v>
+        <v>55.20000076293945</v>
       </c>
       <c r="F5" t="n">
-        <v>30636</v>
+        <v>30470.40042114258</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>30636</v>
+        <v>30470.40042114258</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228.1799926757812</v>
+        <v>235.9199981689453</v>
       </c>
       <c r="F6" t="n">
-        <v>39931.49871826172</v>
+        <v>41285.99967956543</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39931.49871826172</v>
+        <v>41285.99967956543</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.54000091552734</v>
+        <v>17.79999923706055</v>
       </c>
       <c r="F7" t="n">
-        <v>44341.12231445312</v>
+        <v>44998.39807128906</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>44341.12231445312</v>
+        <v>44998.39807128906</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4517.39990234375</v>
+        <v>4499.2001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003777442087123495</v>
+        <v>0.01162455206576718</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0004646747773536797</v>
+        <v>-0.01242363839534044</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.40000152587891</v>
+        <v>74.90000152587891</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.01186028144521856</v>
+        <v>0.004034940232198414</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03185902910022276</v>
+        <v>0.02451167827056477</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.02</v>
+        <v>0.49</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>99241.57844619751</v>
+        <v>94577.32350921631</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.5%</t>
+          <t>+52.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-60080.9202835083</v>
+        <v>-57998.93528747559</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.5%</t>
+          <t>+32.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-39160.65816268921</v>
+        <v>-36578.38822174072</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55.2</v>
+        <v>52.59</v>
       </c>
       <c r="C2" t="n">
         <v>2.66</v>
       </c>
       <c r="D2" t="n">
-        <v>52.54</v>
+        <v>49.93</v>
       </c>
       <c r="E2" t="n">
-        <v>63.18</v>
+        <v>60.56</v>
       </c>
       <c r="F2" t="n">
-        <v>1468.13</v>
+        <v>1467.34</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.8</v>
+        <v>16.67</v>
       </c>
       <c r="C3" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="D3" t="n">
-        <v>16.75</v>
+        <v>15.65</v>
       </c>
       <c r="E3" t="n">
-        <v>20.95</v>
+        <v>19.74</v>
       </c>
       <c r="F3" t="n">
-        <v>2651.51</v>
+        <v>2586.55</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>235.92</v>
+        <v>229.12</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>7.67</v>
       </c>
       <c r="D5" t="n">
-        <v>227.92</v>
+        <v>221.45</v>
       </c>
       <c r="E5" t="n">
-        <v>259.92</v>
+        <v>252.12</v>
       </c>
       <c r="F5" t="n">
-        <v>1400</v>
+        <v>1341.81</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>55.20000076293945</v>
+        <v>52.59000015258789</v>
       </c>
       <c r="F5" t="n">
-        <v>30470.40042114258</v>
+        <v>29029.68008422852</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>30470.40042114258</v>
+        <v>29029.68008422852</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>235.9199981689453</v>
+        <v>229.1199951171875</v>
       </c>
       <c r="F6" t="n">
-        <v>41285.99967956543</v>
+        <v>40095.99914550781</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>41285.99967956543</v>
+        <v>40095.99914550781</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.79999923706055</v>
+        <v>16.67000007629395</v>
       </c>
       <c r="F7" t="n">
-        <v>44998.39807128906</v>
+        <v>42141.76019287109</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>44998.39807128906</v>
+        <v>42141.76019287109</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4499.2001953125</v>
+        <v>4474.60009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01162455206576718</v>
+        <v>-0.005489677972896345</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01242363839534044</v>
+        <v>-0.0442768553389461</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.90000152587891</v>
+        <v>73.30999755859375</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004034940232198414</v>
+        <v>-0.03086785892119781</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02451167827056477</v>
+        <v>-0.04557940382235548</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>94577.32350921631</v>
+        <v>96157.38784255981</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+52.1%</t>
+          <t>+52.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-57998.93528747559</v>
+        <v>-59267.46496734619</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+32.9%</t>
+          <t>+32.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-36578.38822174072</v>
+        <v>-36889.92287521362</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.59</v>
+        <v>53.05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="D2" t="n">
-        <v>49.93</v>
+        <v>50.47</v>
       </c>
       <c r="E2" t="n">
-        <v>60.56</v>
+        <v>60.8</v>
       </c>
       <c r="F2" t="n">
-        <v>1467.34</v>
+        <v>1426.69</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.67</v>
+        <v>16.83</v>
       </c>
       <c r="C3" t="n">
-        <v>1.02</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>15.65</v>
+        <v>15.89</v>
       </c>
       <c r="E3" t="n">
-        <v>19.74</v>
+        <v>19.65</v>
       </c>
       <c r="F3" t="n">
-        <v>2586.55</v>
+        <v>2378.06</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>229.12</v>
+        <v>235.98</v>
       </c>
       <c r="C5" t="n">
-        <v>7.67</v>
+        <v>7.97</v>
       </c>
       <c r="D5" t="n">
-        <v>221.45</v>
+        <v>228.01</v>
       </c>
       <c r="E5" t="n">
-        <v>252.12</v>
+        <v>259.88</v>
       </c>
       <c r="F5" t="n">
-        <v>1341.81</v>
+        <v>1394.22</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.59000015258789</v>
+        <v>53.04999923706055</v>
       </c>
       <c r="F5" t="n">
-        <v>29029.68008422852</v>
+        <v>29283.59957885742</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>29029.68008422852</v>
+        <v>29283.59957885742</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229.1199951171875</v>
+        <v>235.9799957275391</v>
       </c>
       <c r="F6" t="n">
-        <v>40095.99914550781</v>
+        <v>41296.49925231934</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>40095.99914550781</v>
+        <v>41296.49925231934</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.67000007629395</v>
+        <v>16.82999992370605</v>
       </c>
       <c r="F7" t="n">
-        <v>42141.76019287109</v>
+        <v>42546.23980712891</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>42141.76019287109</v>
+        <v>42546.23980712891</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4474.60009765625</v>
+        <v>4497.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.005489677972896345</v>
+        <v>-0.01383622358431091</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0442768553389461</v>
+        <v>-0.04306564337950736</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73.30999755859375</v>
+        <v>74.20999908447266</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03086785892119781</v>
+        <v>-0.0185939256230867</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04557940382235548</v>
+        <v>-0.06889496446153753</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.41</v>
+        <v>1.15</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CERRAR ARBITRAJE (Media alcanzada)</t>
+          <t>MANTENER</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>96157.38784255981</v>
+        <v>86621.37610244751</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+52.4%</t>
+          <t>+53.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-59267.46496734619</v>
+        <v>-54352.91184234619</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+32.6%</t>
+          <t>+31.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-36889.92287521362</v>
+        <v>-32268.46426010132</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53.05</v>
+        <v>47.58</v>
       </c>
       <c r="C2" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="D2" t="n">
-        <v>50.47</v>
+        <v>44.95</v>
       </c>
       <c r="E2" t="n">
-        <v>60.8</v>
+        <v>55.48</v>
       </c>
       <c r="F2" t="n">
-        <v>1426.69</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.83</v>
+        <v>14.78</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="D3" t="n">
-        <v>15.89</v>
+        <v>13.82</v>
       </c>
       <c r="E3" t="n">
-        <v>19.65</v>
+        <v>17.67</v>
       </c>
       <c r="F3" t="n">
-        <v>2378.06</v>
+        <v>2433.2</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>235.98</v>
+        <v>218.74</v>
       </c>
       <c r="C5" t="n">
-        <v>7.97</v>
+        <v>8.19</v>
       </c>
       <c r="D5" t="n">
-        <v>228.01</v>
+        <v>210.55</v>
       </c>
       <c r="E5" t="n">
-        <v>259.88</v>
+        <v>243.31</v>
       </c>
       <c r="F5" t="n">
-        <v>1394.22</v>
+        <v>1433.25</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53.04999923706055</v>
+        <v>47.58000183105469</v>
       </c>
       <c r="F5" t="n">
-        <v>29283.59957885742</v>
+        <v>26264.16101074219</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>29283.59957885742</v>
+        <v>26264.16101074219</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>235.9799957275391</v>
+        <v>218.7400054931641</v>
       </c>
       <c r="F6" t="n">
-        <v>41296.49925231934</v>
+        <v>38279.50096130371</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>41296.49925231934</v>
+        <v>38279.50096130371</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.82999992370605</v>
+        <v>14.77999973297119</v>
       </c>
       <c r="F7" t="n">
-        <v>42546.23980712891</v>
+        <v>37363.83932495117</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>42546.23980712891</v>
+        <v>37363.83932495117</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4497.39990234375</v>
+        <v>4353.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01383622358431091</v>
+        <v>-0.04530207162728872</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04306564337950736</v>
+        <v>-0.07359885882772188</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.20999908447266</v>
+        <v>67.99500274658203</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0185939256230867</v>
+        <v>-0.1007854797732652</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.06889496446153753</v>
+        <v>-0.1468738683485459</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86621.37610244751</v>
+        <v>86123.47066497803</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+53.3%</t>
+          <t>+52.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-54352.91184234619</v>
+        <v>-53547.6363067627</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+31.7%</t>
+          <t>+32.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-32268.46426010132</v>
+        <v>-32575.83435821533</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47.58</v>
+        <v>47.28</v>
       </c>
       <c r="C2" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="D2" t="n">
-        <v>44.95</v>
+        <v>44.71</v>
       </c>
       <c r="E2" t="n">
-        <v>55.48</v>
+        <v>54.98</v>
       </c>
       <c r="F2" t="n">
-        <v>1453</v>
+        <v>1417.06</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.78</v>
+        <v>14.89</v>
       </c>
       <c r="C3" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="D3" t="n">
-        <v>13.82</v>
+        <v>13.97</v>
       </c>
       <c r="E3" t="n">
-        <v>17.67</v>
+        <v>17.66</v>
       </c>
       <c r="F3" t="n">
-        <v>2433.2</v>
+        <v>2332.11</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>218.74</v>
+        <v>214.75</v>
       </c>
       <c r="C5" t="n">
-        <v>8.19</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>210.55</v>
+        <v>206.47</v>
       </c>
       <c r="E5" t="n">
-        <v>243.31</v>
+        <v>239.58</v>
       </c>
       <c r="F5" t="n">
-        <v>1433.25</v>
+        <v>1448.34</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>47.58000183105469</v>
+        <v>47.27999877929688</v>
       </c>
       <c r="F5" t="n">
-        <v>26264.16101074219</v>
+        <v>26098.55932617188</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>26264.16101074219</v>
+        <v>26098.55932617188</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>218.7400054931641</v>
+        <v>214.75</v>
       </c>
       <c r="F6" t="n">
-        <v>38279.50096130371</v>
+        <v>37581.25</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>38279.50096130371</v>
+        <v>37581.25</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.77999973297119</v>
+        <v>14.89000034332275</v>
       </c>
       <c r="F7" t="n">
-        <v>37363.83932495117</v>
+        <v>37641.92086791992</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>37363.83932495117</v>
+        <v>37641.92086791992</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4353.89990234375</v>
+        <v>4349.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.04530207162728872</v>
+        <v>-0.03111986640383391</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.07359885882772188</v>
+        <v>-0.0782631397806558</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67.99500274658203</v>
+        <v>68.23000335693359</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1007854797732652</v>
+        <v>-0.09402336887760843</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1468738683485459</v>
+        <v>-0.2018482439050077</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86123.47066497803</v>
+        <v>84382.08553771973</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+52.8%</t>
+          <t>+53.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-53547.6363067627</v>
+        <v>-52664.45704956054</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+32.2%</t>
+          <t>+31.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-32575.83435821533</v>
+        <v>-31717.62848815918</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47.28</v>
+        <v>46.13</v>
       </c>
       <c r="C2" t="n">
-        <v>2.57</v>
+        <v>2.67</v>
       </c>
       <c r="D2" t="n">
-        <v>44.71</v>
+        <v>43.46</v>
       </c>
       <c r="E2" t="n">
-        <v>54.98</v>
+        <v>54.15</v>
       </c>
       <c r="F2" t="n">
-        <v>1417.06</v>
+        <v>1476.21</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.89</v>
+        <v>14.51</v>
       </c>
       <c r="C3" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>13.97</v>
+        <v>13.57</v>
       </c>
       <c r="E3" t="n">
-        <v>17.66</v>
+        <v>17.34</v>
       </c>
       <c r="F3" t="n">
-        <v>2332.11</v>
+        <v>2387.53</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>214.75</v>
+        <v>212.16</v>
       </c>
       <c r="C5" t="n">
-        <v>8.279999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="D5" t="n">
-        <v>206.47</v>
+        <v>203.43</v>
       </c>
       <c r="E5" t="n">
-        <v>239.58</v>
+        <v>238.36</v>
       </c>
       <c r="F5" t="n">
-        <v>1448.34</v>
+        <v>1528.5</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>47.27999877929688</v>
+        <v>46.13000106811523</v>
       </c>
       <c r="F5" t="n">
-        <v>26098.55932617188</v>
+        <v>25463.76058959961</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>26098.55932617188</v>
+        <v>25463.76058959961</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>214.75</v>
+        <v>212.1600036621094</v>
       </c>
       <c r="F6" t="n">
-        <v>37581.25</v>
+        <v>37128.00064086914</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>37581.25</v>
+        <v>37128.00064086914</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.89000034332275</v>
+        <v>14.51000022888184</v>
       </c>
       <c r="F7" t="n">
-        <v>37641.92086791992</v>
+        <v>36681.28057861328</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>37641.92086791992</v>
+        <v>36681.28057861328</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4349.39990234375</v>
+        <v>4264.10009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.03111986640383391</v>
+        <v>-0.0389028084067089</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0782631397806558</v>
+        <v>-0.08840003236001037</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>68.23000335693359</v>
+        <v>65.07499694824219</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.09402336887760843</v>
+        <v>-0.1143366706657061</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2018482439050077</v>
+        <v>-0.2355808874922826</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MANTENER</t>
+          <t>CERRAR ARBITRAJE (Media alcanzada)</t>
         </is>
       </c>
     </row>
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LIGERAMENTE ALCISTA (Parcial)</t>
+          <t>HOLD / CASH (Sin Tendencia)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>84382.08553771973</v>
+        <v>81923.62954940795</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-52664.45704956054</v>
+        <v>-51224.26609954834</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-31717.62848815918</v>
+        <v>-30699.36344985962</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46.13</v>
+        <v>44.17</v>
       </c>
       <c r="C2" t="n">
         <v>2.67</v>
       </c>
       <c r="D2" t="n">
-        <v>43.46</v>
+        <v>41.5</v>
       </c>
       <c r="E2" t="n">
-        <v>54.15</v>
+        <v>52.17</v>
       </c>
       <c r="F2" t="n">
-        <v>1476.21</v>
+        <v>1471.47</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.51</v>
+        <v>14.05</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="D3" t="n">
-        <v>13.57</v>
+        <v>13.13</v>
       </c>
       <c r="E3" t="n">
-        <v>17.34</v>
+        <v>16.81</v>
       </c>
       <c r="F3" t="n">
-        <v>2387.53</v>
+        <v>2327.7</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>212.16</v>
+        <v>208.46</v>
       </c>
       <c r="C5" t="n">
-        <v>8.73</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>203.43</v>
+        <v>199.67</v>
       </c>
       <c r="E5" t="n">
-        <v>238.36</v>
+        <v>234.84</v>
       </c>
       <c r="F5" t="n">
-        <v>1528.5</v>
+        <v>1538.56</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46.13000106811523</v>
+        <v>44.16999816894531</v>
       </c>
       <c r="F5" t="n">
-        <v>25463.76058959961</v>
+        <v>24381.83898925781</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>25463.76058959961</v>
+        <v>24381.83898925781</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>212.1600036621094</v>
+        <v>208.4600067138672</v>
       </c>
       <c r="F6" t="n">
-        <v>37128.00064086914</v>
+        <v>36480.50117492676</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>37128.00064086914</v>
+        <v>36480.50117492676</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.51000022888184</v>
+        <v>14.05000019073486</v>
       </c>
       <c r="F7" t="n">
-        <v>36681.28057861328</v>
+        <v>35518.40048217773</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>36681.28057861328</v>
+        <v>35518.40048217773</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4264.10009765625</v>
+        <v>4085.199951171875</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0389028084067089</v>
+        <v>-0.08726928606291784</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.08840003236001037</v>
+        <v>-0.1303829999095718</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.07499694824219</v>
+        <v>62.93000030517578</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1143366706657061</v>
+        <v>-0.1470472508730543</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2355808874922826</v>
+        <v>-0.2920304207599731</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>81923.62954940795</v>
+        <v>84968.99998016357</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+53.1%</t>
+          <t>+52.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-51224.26609954834</v>
+        <v>-52072.45702819825</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+31.9%</t>
+          <t>+32.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-30699.36344985962</v>
+        <v>-32896.54295196533</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.17</v>
+        <v>46.53</v>
       </c>
       <c r="C2" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="D2" t="n">
-        <v>41.5</v>
+        <v>43.83</v>
       </c>
       <c r="E2" t="n">
-        <v>52.17</v>
+        <v>54.64</v>
       </c>
       <c r="F2" t="n">
-        <v>1471.47</v>
+        <v>1492.77</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.05</v>
+        <v>14.99</v>
       </c>
       <c r="C3" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="D3" t="n">
-        <v>13.13</v>
+        <v>14.06</v>
       </c>
       <c r="E3" t="n">
-        <v>16.81</v>
+        <v>17.78</v>
       </c>
       <c r="F3" t="n">
-        <v>2327.7</v>
+        <v>2350.32</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>208.46</v>
+        <v>207.91</v>
       </c>
       <c r="C5" t="n">
-        <v>8.789999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>199.67</v>
+        <v>199.27</v>
       </c>
       <c r="E5" t="n">
-        <v>234.84</v>
+        <v>233.84</v>
       </c>
       <c r="F5" t="n">
-        <v>1538.56</v>
+        <v>1512.75</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.16999816894531</v>
+        <v>46.52999877929688</v>
       </c>
       <c r="F5" t="n">
-        <v>24381.83898925781</v>
+        <v>25684.55932617188</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24381.83898925781</v>
+        <v>25684.55932617188</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208.4600067138672</v>
+        <v>207.9100036621094</v>
       </c>
       <c r="F6" t="n">
-        <v>36480.50117492676</v>
+        <v>36384.25064086914</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>36480.50117492676</v>
+        <v>36384.25064086914</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.05000019073486</v>
+        <v>14.98999977111816</v>
       </c>
       <c r="F7" t="n">
-        <v>35518.40048217773</v>
+        <v>37894.71942138672</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>35518.40048217773</v>
+        <v>37894.71942138672</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4085.199951171875</v>
+        <v>4236.5</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.08726928606291784</v>
+        <v>-0.0231952446083995</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1303829999095718</v>
+        <v>-0.09439731695298559</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62.93000030517578</v>
+        <v>67.52999877929688</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1470472508730543</v>
+        <v>-0.02049522065906728</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2920304207599731</v>
+        <v>-0.2047060870009001</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.58</v>
+        <v>-0.04</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>84968.99998016357</v>
+        <v>86599.61563034057</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-52072.45702819825</v>
+        <v>-53040.59076385498</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-32896.54295196533</v>
+        <v>-33559.0248664856</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46.53</v>
+        <v>48.14</v>
       </c>
       <c r="C2" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="D2" t="n">
-        <v>43.83</v>
+        <v>45.38</v>
       </c>
       <c r="E2" t="n">
-        <v>54.64</v>
+        <v>56.41</v>
       </c>
       <c r="F2" t="n">
-        <v>1492.77</v>
+        <v>1521.5</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.99</v>
+        <v>15.29</v>
       </c>
       <c r="C3" t="n">
         <v>0.93</v>
       </c>
       <c r="D3" t="n">
-        <v>14.06</v>
+        <v>14.36</v>
       </c>
       <c r="E3" t="n">
-        <v>17.78</v>
+        <v>18.09</v>
       </c>
       <c r="F3" t="n">
-        <v>2350.32</v>
+        <v>2355.55</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>207.91</v>
+        <v>209.46</v>
       </c>
       <c r="C5" t="n">
-        <v>8.640000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="D5" t="n">
-        <v>199.27</v>
+        <v>200.61</v>
       </c>
       <c r="E5" t="n">
-        <v>233.84</v>
+        <v>236.02</v>
       </c>
       <c r="F5" t="n">
-        <v>1512.75</v>
+        <v>1549.21</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46.52999877929688</v>
+        <v>48.13999938964844</v>
       </c>
       <c r="F5" t="n">
-        <v>25684.55932617188</v>
+        <v>26573.27966308594</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>25684.55932617188</v>
+        <v>26573.27966308594</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>207.9100036621094</v>
+        <v>209.4600067138672</v>
       </c>
       <c r="F6" t="n">
-        <v>36384.25064086914</v>
+        <v>36655.50117492676</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>36384.25064086914</v>
+        <v>36655.50117492676</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.98999977111816</v>
+        <v>15.28999996185303</v>
       </c>
       <c r="F7" t="n">
-        <v>37894.71942138672</v>
+        <v>38653.11990356445</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>37894.71942138672</v>
+        <v>38653.11990356445</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4236.5</v>
+        <v>4239.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0231952446083995</v>
+        <v>-0.02214073252662219</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.09439731695298559</v>
+        <v>-0.06934016328345205</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67.52999877929688</v>
+        <v>68.12000274658203</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.02049522065906728</v>
+        <v>-0.004457439409174313</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2047060870009001</v>
+        <v>-0.1171705913801421</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.04</v>
+        <v>-0.59</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HOLD / CASH (Sin Tendencia)</t>
+          <t>LIGERAMENTE ALCISTA (Parcial)</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86599.61563034057</v>
+        <v>92788.695652771</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+52.1%</t>
+          <t>+51.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-53040.59076385498</v>
+        <v>-56130.37460632324</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+32.9%</t>
+          <t>+33.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-33559.0248664856</v>
+        <v>-36658.32104644775</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.14</v>
+        <v>50.97</v>
       </c>
       <c r="C2" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="D2" t="n">
-        <v>45.38</v>
+        <v>48.03</v>
       </c>
       <c r="E2" t="n">
-        <v>56.41</v>
+        <v>59.8</v>
       </c>
       <c r="F2" t="n">
-        <v>1521.5</v>
+        <v>1625.44</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.29</v>
+        <v>16.66</v>
       </c>
       <c r="C3" t="n">
-        <v>0.93</v>
+        <v>1.02</v>
       </c>
       <c r="D3" t="n">
-        <v>14.36</v>
+        <v>15.64</v>
       </c>
       <c r="E3" t="n">
-        <v>18.09</v>
+        <v>19.72</v>
       </c>
       <c r="F3" t="n">
-        <v>2355.55</v>
+        <v>2579.46</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>209.46</v>
+        <v>222.35</v>
       </c>
       <c r="C5" t="n">
-        <v>8.85</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>200.61</v>
+        <v>212.9</v>
       </c>
       <c r="E5" t="n">
-        <v>236.02</v>
+        <v>250.69</v>
       </c>
       <c r="F5" t="n">
-        <v>1549.21</v>
+        <v>1653.37</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>48.13999938964844</v>
+        <v>50.97000122070312</v>
       </c>
       <c r="F5" t="n">
-        <v>26573.27966308594</v>
+        <v>28135.44067382812</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>26573.27966308594</v>
+        <v>28135.44067382812</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>209.4600067138672</v>
+        <v>222.3500061035156</v>
       </c>
       <c r="F6" t="n">
-        <v>36655.50117492676</v>
+        <v>38911.25106811523</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>36655.50117492676</v>
+        <v>38911.25106811523</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.28999996185303</v>
+        <v>16.65999984741211</v>
       </c>
       <c r="F7" t="n">
-        <v>38653.11990356445</v>
+        <v>42116.47961425781</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>38653.11990356445</v>
+        <v>42116.47961425781</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4239.89990234375</v>
+        <v>4335</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02214073252662219</v>
+        <v>0.01760563380281699</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.06934016328345205</v>
+        <v>-0.0477759472817133</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>68.12000274658203</v>
+        <v>69.93499755859375</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.004457439409174313</v>
+        <v>0.07436930680153453</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1171705913801421</v>
+        <v>-0.09261350497796894</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.59</v>
+        <v>-1.03</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CERRAR ARBITRAJE (Media alcanzada)</t>
+          <t>MANTENER</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>92788.695652771</v>
+        <v>94526.58489303589</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.4%</t>
+          <t>+52.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-56130.37460632324</v>
+        <v>-57818.81397552491</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.6%</t>
+          <t>+33.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-36658.32104644775</v>
+        <v>-36707.77091751099</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50.97</v>
+        <v>51.92</v>
       </c>
       <c r="C2" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="D2" t="n">
-        <v>48.03</v>
+        <v>49.04</v>
       </c>
       <c r="E2" t="n">
-        <v>59.8</v>
+        <v>60.56</v>
       </c>
       <c r="F2" t="n">
-        <v>1625.44</v>
+        <v>1589.56</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.66</v>
+        <v>16.72</v>
       </c>
       <c r="C3" t="n">
         <v>1.02</v>
       </c>
       <c r="D3" t="n">
-        <v>15.64</v>
+        <v>15.7</v>
       </c>
       <c r="E3" t="n">
-        <v>19.72</v>
+        <v>19.78</v>
       </c>
       <c r="F3" t="n">
-        <v>2579.46</v>
+        <v>2574.95</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>222.35</v>
+        <v>230.17</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>212.9</v>
+        <v>220.38</v>
       </c>
       <c r="E5" t="n">
-        <v>250.69</v>
+        <v>259.53</v>
       </c>
       <c r="F5" t="n">
-        <v>1653.37</v>
+        <v>1712.53</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>50.97000122070312</v>
+        <v>51.91999816894531</v>
       </c>
       <c r="F5" t="n">
-        <v>28135.44067382812</v>
+        <v>28659.83898925781</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28135.44067382812</v>
+        <v>28659.83898925781</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222.3500061035156</v>
+        <v>230.1699981689453</v>
       </c>
       <c r="F6" t="n">
-        <v>38911.25106811523</v>
+        <v>40279.74967956543</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>38911.25106811523</v>
+        <v>40279.74967956543</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.65999984741211</v>
+        <v>16.71999931335449</v>
       </c>
       <c r="F7" t="n">
-        <v>42116.47961425781</v>
+        <v>42268.15826416016</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>42116.47961425781</v>
+        <v>42268.15826416016</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4335</v>
+        <v>4356.10009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01760563380281699</v>
+        <v>0.06034270253591978</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0477759472817133</v>
+        <v>-0.03333105064936215</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69.93499755859375</v>
+        <v>70.15499877929688</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07436930680153453</v>
+        <v>0.08600752085715091</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09261350497796894</v>
+        <v>-0.06244993809044508</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LIGERAMENTE ALCISTA (Parcial)</t>
+          <t>HOLD / CASH (Sin Tendencia)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>94526.58489303589</v>
+        <v>91941.39483337403</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+52.0%</t>
+          <t>+52.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-57818.81397552491</v>
+        <v>-56750.03352661133</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.0%</t>
+          <t>+32.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-36707.77091751099</v>
+        <v>-35191.3613067627</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51.92</v>
+        <v>50.46</v>
       </c>
       <c r="C2" t="n">
         <v>2.88</v>
       </c>
       <c r="D2" t="n">
-        <v>49.04</v>
+        <v>47.58</v>
       </c>
       <c r="E2" t="n">
-        <v>60.56</v>
+        <v>59.1</v>
       </c>
       <c r="F2" t="n">
-        <v>1589.56</v>
+        <v>1590.15</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.72</v>
+        <v>16.06</v>
       </c>
       <c r="C3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="D3" t="n">
-        <v>15.7</v>
+        <v>15.04</v>
       </c>
       <c r="E3" t="n">
-        <v>19.78</v>
+        <v>19.1</v>
       </c>
       <c r="F3" t="n">
-        <v>2574.95</v>
+        <v>2565.92</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>230.17</v>
+        <v>226.93</v>
       </c>
       <c r="C5" t="n">
-        <v>9.789999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="D5" t="n">
-        <v>220.38</v>
+        <v>217.03</v>
       </c>
       <c r="E5" t="n">
-        <v>259.53</v>
+        <v>256.63</v>
       </c>
       <c r="F5" t="n">
-        <v>1712.53</v>
+        <v>1732.21</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>51.91999816894531</v>
+        <v>50.45999908447266</v>
       </c>
       <c r="F5" t="n">
-        <v>28659.83898925781</v>
+        <v>27853.91949462891</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28659.83898925781</v>
+        <v>27853.91949462891</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230.1699981689453</v>
+        <v>226.9299926757812</v>
       </c>
       <c r="F6" t="n">
-        <v>40279.74967956543</v>
+        <v>39712.74871826172</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>40279.74967956543</v>
+        <v>39712.74871826172</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.71999931335449</v>
+        <v>16.05999946594238</v>
       </c>
       <c r="F7" t="n">
-        <v>42268.15826416016</v>
+        <v>40599.67864990234</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>42268.15826416016</v>
+        <v>40599.67864990234</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4356.10009765625</v>
+        <v>4297.7001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06034270253591978</v>
+        <v>0.0507053624449374</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.03333105064936215</v>
+        <v>-0.05155245060884028</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70.15499877929688</v>
+        <v>68.38500213623047</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08600752085715091</v>
+        <v>0.07043913176687822</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.06244993809044508</v>
+        <v>-0.09842976352105048</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.03</v>
+        <v>-0.65</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MANTENER</t>
+          <t>CERRAR ARBITRAJE (Media alcanzada)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>91941.39483337403</v>
+        <v>89900.57226486206</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+52.5%</t>
+          <t>+51.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-56750.03352661133</v>
+        <v>-54841.96112518311</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+32.5%</t>
+          <t>+33.1%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-35191.3613067627</v>
+        <v>-35058.61113967896</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50.46</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="D2" t="n">
-        <v>47.58</v>
+        <v>46.08</v>
       </c>
       <c r="E2" t="n">
-        <v>59.1</v>
+        <v>57.75</v>
       </c>
       <c r="F2" t="n">
-        <v>1590.15</v>
+        <v>1610.66</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.06</v>
+        <v>15.96</v>
       </c>
       <c r="C3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="D3" t="n">
-        <v>15.04</v>
+        <v>14.94</v>
       </c>
       <c r="E3" t="n">
-        <v>19.1</v>
+        <v>19.02</v>
       </c>
       <c r="F3" t="n">
-        <v>2565.92</v>
+        <v>2579.46</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>226.93</v>
+        <v>219.26</v>
       </c>
       <c r="C5" t="n">
-        <v>9.9</v>
+        <v>10.38</v>
       </c>
       <c r="D5" t="n">
-        <v>217.03</v>
+        <v>208.88</v>
       </c>
       <c r="E5" t="n">
-        <v>256.63</v>
+        <v>250.41</v>
       </c>
       <c r="F5" t="n">
-        <v>1732.21</v>
+        <v>1816.96</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>50.45999908447266</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>27853.91949462891</v>
+        <v>27048</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>27853.91949462891</v>
+        <v>27048</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>226.9299926757812</v>
+        <v>219.2599945068359</v>
       </c>
       <c r="F6" t="n">
-        <v>39712.74871826172</v>
+        <v>38370.49903869629</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39712.74871826172</v>
+        <v>38370.49903869629</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.05999946594238</v>
+        <v>15.96000003814697</v>
       </c>
       <c r="F7" t="n">
-        <v>40599.67864990234</v>
+        <v>40346.88009643555</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>40599.67864990234</v>
+        <v>40346.88009643555</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4297.7001953125</v>
+        <v>4215</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0507053624449374</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.05155245060884028</v>
+        <v>-0.07154496203822314</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>68.38500213623047</v>
+        <v>65.63500213623047</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07043913176687822</v>
+        <v>-0.03277382492271841</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09842976352105048</v>
+        <v>-0.1410605271544697</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.65</v>
+        <v>-0.64</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         <v>19.02</v>
       </c>
       <c r="F3" t="n">
-        <v>2579.46</v>
+        <v>2578.56</v>
       </c>
     </row>
     <row r="4">
@@ -779,16 +779,16 @@
         <v>219.26</v>
       </c>
       <c r="C5" t="n">
-        <v>10.38</v>
+        <v>10.42</v>
       </c>
       <c r="D5" t="n">
-        <v>208.88</v>
+        <v>208.84</v>
       </c>
       <c r="E5" t="n">
-        <v>250.41</v>
+        <v>250.51</v>
       </c>
       <c r="F5" t="n">
-        <v>1816.96</v>
+        <v>1823.09</v>
       </c>
     </row>
     <row r="6">
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4215</v>
+        <v>4172.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0.03583643661188773</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.07154496203822314</v>
+        <v>-0.0769962613705486</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.63500213623047</v>
+        <v>64.91000366210938</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03277382492271841</v>
+        <v>-0.07358773286252773</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1410605271544697</v>
+        <v>-0.1447168303585835</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.64</v>
+        <v>-0.57</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>89900.57226486206</v>
+        <v>90119.98180923461</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-54841.96112518311</v>
+        <v>-55023.71836700439</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-35058.61113967896</v>
+        <v>-35096.26344223023</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>48.91</v>
       </c>
       <c r="C2" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="D2" t="n">
-        <v>46.08</v>
+        <v>46.13</v>
       </c>
       <c r="E2" t="n">
-        <v>57.75</v>
+        <v>57.26</v>
       </c>
       <c r="F2" t="n">
-        <v>1610.66</v>
+        <v>1536.53</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.96</v>
+        <v>15.98</v>
       </c>
       <c r="C3" t="n">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="D3" t="n">
-        <v>14.94</v>
+        <v>14.99</v>
       </c>
       <c r="E3" t="n">
-        <v>19.02</v>
+        <v>18.95</v>
       </c>
       <c r="F3" t="n">
-        <v>2578.56</v>
+        <v>2500.9</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>219.26</v>
+        <v>220.73</v>
       </c>
       <c r="C5" t="n">
-        <v>10.42</v>
+        <v>10.22</v>
       </c>
       <c r="D5" t="n">
-        <v>208.84</v>
+        <v>210.51</v>
       </c>
       <c r="E5" t="n">
-        <v>250.51</v>
+        <v>251.39</v>
       </c>
       <c r="F5" t="n">
-        <v>1823.09</v>
+        <v>1788.27</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>48.90999984741211</v>
       </c>
       <c r="F5" t="n">
-        <v>27048</v>
+        <v>26998.31991577148</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>27048</v>
+        <v>26998.31991577148</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219.2599945068359</v>
+        <v>220.7299957275391</v>
       </c>
       <c r="F6" t="n">
-        <v>38370.49903869629</v>
+        <v>38627.74925231934</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>38370.49903869629</v>
+        <v>38627.74925231934</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.96000003814697</v>
+        <v>15.97999954223633</v>
       </c>
       <c r="F7" t="n">
-        <v>40346.88009643555</v>
+        <v>40397.43884277344</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>40346.88009643555</v>
+        <v>40397.43884277344</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4172.89990234375</v>
+        <v>4208.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.03583643661188773</v>
+        <v>-0.02816966513910357</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0769962613705486</v>
+        <v>-0.06903342129092016</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64.91000366210938</v>
+        <v>65.125</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.07358773286252773</v>
+        <v>-0.06829857270436535</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1447168303585835</v>
+        <v>-0.1418839426839872</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.57</v>
+        <v>-0.16</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>90119.98180923461</v>
+        <v>85889.43964462281</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.9%</t>
+          <t>+52.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-55023.71836700439</v>
+        <v>-52844.80039520264</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.1%</t>
+          <t>+32.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-35096.26344223023</v>
+        <v>-33044.63924942016</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.91</v>
+        <v>46.22</v>
       </c>
       <c r="C2" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="D2" t="n">
-        <v>46.13</v>
+        <v>43.36</v>
       </c>
       <c r="E2" t="n">
-        <v>57.26</v>
+        <v>54.8</v>
       </c>
       <c r="F2" t="n">
-        <v>1536.53</v>
+        <v>1578.33</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.98</v>
+        <v>15.07</v>
       </c>
       <c r="C3" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="D3" t="n">
-        <v>14.99</v>
+        <v>14.04</v>
       </c>
       <c r="E3" t="n">
-        <v>18.95</v>
+        <v>18.16</v>
       </c>
       <c r="F3" t="n">
-        <v>2500.9</v>
+        <v>2603.84</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>220.73</v>
+        <v>213.92</v>
       </c>
       <c r="C5" t="n">
-        <v>10.22</v>
+        <v>10.06</v>
       </c>
       <c r="D5" t="n">
-        <v>210.51</v>
+        <v>203.86</v>
       </c>
       <c r="E5" t="n">
-        <v>251.39</v>
+        <v>244.1</v>
       </c>
       <c r="F5" t="n">
-        <v>1788.27</v>
+        <v>1760.24</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>48.90999984741211</v>
+        <v>46.22000122070312</v>
       </c>
       <c r="F5" t="n">
-        <v>26998.31991577148</v>
+        <v>25513.44067382812</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>26998.31991577148</v>
+        <v>25513.44067382812</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220.7299957275391</v>
+        <v>213.9199981689453</v>
       </c>
       <c r="F6" t="n">
-        <v>38627.74925231934</v>
+        <v>37435.99967956543</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>38627.74925231934</v>
+        <v>37435.99967956543</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.97999954223633</v>
+        <v>15.06999969482422</v>
       </c>
       <c r="F7" t="n">
-        <v>40397.43884277344</v>
+        <v>38096.95922851562</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>40397.43884277344</v>
+        <v>38096.95922851562</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4208.89990234375</v>
+        <v>4119.10009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02816966513910357</v>
+        <v>-0.05501383607330856</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.06903342129092016</v>
+        <v>-0.08472576059050307</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.125</v>
+        <v>61.45999908447266</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.06829857270436535</v>
+        <v>-0.1306438861133492</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1418839426839872</v>
+        <v>-0.1945482099643762</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.16</v>
+        <v>-0.31</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85889.43964462281</v>
+        <v>83230.16388015747</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+52.3%</t>
+          <t>+52.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-52844.80039520264</v>
+        <v>-51419.49471588134</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+32.7%</t>
+          <t>+32.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-33044.63924942016</v>
+        <v>-31810.66916427613</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46.22</v>
+        <v>44.39</v>
       </c>
       <c r="C2" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="D2" t="n">
-        <v>43.36</v>
+        <v>41.54</v>
       </c>
       <c r="E2" t="n">
-        <v>54.8</v>
+        <v>52.94</v>
       </c>
       <c r="F2" t="n">
-        <v>1578.33</v>
+        <v>1572.41</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.07</v>
+        <v>14.52</v>
       </c>
       <c r="C3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="D3" t="n">
-        <v>14.04</v>
+        <v>13.51</v>
       </c>
       <c r="E3" t="n">
-        <v>18.16</v>
+        <v>17.54</v>
       </c>
       <c r="F3" t="n">
-        <v>2603.84</v>
+        <v>2542.45</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>213.92</v>
+        <v>209.76</v>
       </c>
       <c r="C5" t="n">
-        <v>10.06</v>
+        <v>10.1</v>
       </c>
       <c r="D5" t="n">
-        <v>203.86</v>
+        <v>199.66</v>
       </c>
       <c r="E5" t="n">
-        <v>244.1</v>
+        <v>240.06</v>
       </c>
       <c r="F5" t="n">
-        <v>1760.24</v>
+        <v>1767.29</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46.22000122070312</v>
+        <v>44.38999938964844</v>
       </c>
       <c r="F5" t="n">
-        <v>25513.44067382812</v>
+        <v>24503.27966308594</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>25513.44067382812</v>
+        <v>24503.27966308594</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>213.9199981689453</v>
+        <v>209.7599945068359</v>
       </c>
       <c r="F6" t="n">
-        <v>37435.99967956543</v>
+        <v>36707.99903869629</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>37435.99967956543</v>
+        <v>36707.99903869629</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.06999969482422</v>
+        <v>14.52000045776367</v>
       </c>
       <c r="F7" t="n">
-        <v>38096.95922851562</v>
+        <v>36706.56115722656</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>38096.95922851562</v>
+        <v>36706.56115722656</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4119.10009765625</v>
+        <v>4010.800048828125</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.05501383607330856</v>
+        <v>-0.05049597402923167</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.08472576059050307</v>
+        <v>-0.09818998340008434</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.45999908447266</v>
+        <v>57.52500152587891</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1306438861133492</v>
+        <v>-0.1317635814570757</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1945482099643762</v>
+        <v>-0.2288770321461591</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.31</v>
+        <v>-0.29</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83230.16388015747</v>
+        <v>84901.12796783447</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+52.5%</t>
+          <t>+51.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-51419.49471588134</v>
+        <v>-51596.11293029785</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+32.5%</t>
+          <t>+33.3%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-31810.66916427613</v>
+        <v>-33305.01503753662</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.39</v>
+        <v>44.99</v>
       </c>
       <c r="C2" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="D2" t="n">
-        <v>41.54</v>
+        <v>42.16</v>
       </c>
       <c r="E2" t="n">
-        <v>52.94</v>
+        <v>53.49</v>
       </c>
       <c r="F2" t="n">
-        <v>1572.41</v>
+        <v>1563.34</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.52</v>
+        <v>15.15</v>
       </c>
       <c r="C3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="D3" t="n">
-        <v>13.51</v>
+        <v>14.13</v>
       </c>
       <c r="E3" t="n">
-        <v>17.54</v>
+        <v>18.22</v>
       </c>
       <c r="F3" t="n">
-        <v>2542.45</v>
+        <v>2587.59</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>209.76</v>
+        <v>210</v>
       </c>
       <c r="C5" t="n">
-        <v>10.1</v>
+        <v>9.77</v>
       </c>
       <c r="D5" t="n">
-        <v>199.66</v>
+        <v>200.23</v>
       </c>
       <c r="E5" t="n">
-        <v>240.06</v>
+        <v>239.3</v>
       </c>
       <c r="F5" t="n">
-        <v>1767.29</v>
+        <v>1709.29</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.38999938964844</v>
+        <v>44.9900016784668</v>
       </c>
       <c r="F5" t="n">
-        <v>24503.27966308594</v>
+        <v>24834.48092651367</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24503.27966308594</v>
+        <v>24834.48092651367</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>209.7599945068359</v>
+        <v>210</v>
       </c>
       <c r="F6" t="n">
-        <v>36707.99903869629</v>
+        <v>36750</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>36707.99903869629</v>
+        <v>36750</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.52000045776367</v>
+        <v>15.14999961853027</v>
       </c>
       <c r="F7" t="n">
-        <v>36706.56115722656</v>
+        <v>38299.19903564453</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>36706.56115722656</v>
+        <v>38299.19903564453</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4010.800048828125</v>
+        <v>4037.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.05049597402923167</v>
+        <v>-0.04408044104253439</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.09818998340008434</v>
+        <v>-0.1025492681912529</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57.52500152587891</v>
+        <v>57.75500106811523</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1317635814570757</v>
+        <v>-0.1282921521042586</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2288770321461591</v>
+        <v>-0.2364993901627856</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>84901.12796783447</v>
+        <v>86719.56718521118</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.7%</t>
+          <t>+51.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-51596.11293029785</v>
+        <v>-52535.5982925415</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.3%</t>
+          <t>+33.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-33305.01503753662</v>
+        <v>-34183.96889266968</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.99</v>
+        <v>45.45</v>
       </c>
       <c r="C2" t="n">
-        <v>2.83</v>
+        <v>2.52</v>
       </c>
       <c r="D2" t="n">
-        <v>42.16</v>
+        <v>42.93</v>
       </c>
       <c r="E2" t="n">
-        <v>53.49</v>
+        <v>53.01</v>
       </c>
       <c r="F2" t="n">
-        <v>1563.34</v>
+        <v>1391.04</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.15</v>
+        <v>15.54</v>
       </c>
       <c r="C3" t="n">
-        <v>1.02</v>
+        <v>0.92</v>
       </c>
       <c r="D3" t="n">
-        <v>14.13</v>
+        <v>14.62</v>
       </c>
       <c r="E3" t="n">
-        <v>18.22</v>
+        <v>18.31</v>
       </c>
       <c r="F3" t="n">
-        <v>2587.59</v>
+        <v>2336.65</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>210</v>
+        <v>215.14</v>
       </c>
       <c r="C5" t="n">
-        <v>9.77</v>
+        <v>8.99</v>
       </c>
       <c r="D5" t="n">
-        <v>200.23</v>
+        <v>206.15</v>
       </c>
       <c r="E5" t="n">
-        <v>239.3</v>
+        <v>242.1</v>
       </c>
       <c r="F5" t="n">
-        <v>1709.29</v>
+        <v>1572.56</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.9900016784668</v>
+        <v>45.45000076293945</v>
       </c>
       <c r="F5" t="n">
-        <v>24834.48092651367</v>
+        <v>25088.40042114258</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24834.48092651367</v>
+        <v>25088.40042114258</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>215.1399993896484</v>
       </c>
       <c r="F6" t="n">
-        <v>36750</v>
+        <v>37649.49989318848</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>36750</v>
+        <v>37649.49989318848</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.14999961853027</v>
+        <v>15.53999996185303</v>
       </c>
       <c r="F7" t="n">
-        <v>38299.19903564453</v>
+        <v>39285.11990356445</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>38299.19903564453</v>
+        <v>39285.11990356445</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4037.89990234375</v>
+        <v>4103</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.04408044104253439</v>
+        <v>-0.02866885131899277</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1025492681912529</v>
+        <v>-0.08808032847124869</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57.75500106811523</v>
+        <v>59.60499954223633</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1282921521042586</v>
+        <v>-0.1003697530277775</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2364993901627856</v>
+        <v>-0.2120430671246556</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.29</v>
+        <v>-0.36</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86719.56718521118</v>
+        <v>84880.60650405883</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.5%</t>
+          <t>+51.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-52535.5982925415</v>
+        <v>-50942.38432159425</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.5%</t>
+          <t>+34.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-34183.96889266968</v>
+        <v>-33938.2221824646</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45.45</v>
+        <v>44.67</v>
       </c>
       <c r="C2" t="n">
         <v>2.52</v>
       </c>
       <c r="D2" t="n">
-        <v>42.93</v>
+        <v>42.15</v>
       </c>
       <c r="E2" t="n">
-        <v>53.01</v>
+        <v>52.22</v>
       </c>
       <c r="F2" t="n">
-        <v>1391.04</v>
+        <v>1389.46</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.54</v>
+        <v>15.4</v>
       </c>
       <c r="C3" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="D3" t="n">
-        <v>14.62</v>
+        <v>14.47</v>
       </c>
       <c r="E3" t="n">
-        <v>18.31</v>
+        <v>18.2</v>
       </c>
       <c r="F3" t="n">
-        <v>2336.65</v>
+        <v>2359.17</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>215.14</v>
+        <v>207.26</v>
       </c>
       <c r="C5" t="n">
-        <v>8.99</v>
+        <v>9.07</v>
       </c>
       <c r="D5" t="n">
-        <v>206.15</v>
+        <v>198.19</v>
       </c>
       <c r="E5" t="n">
-        <v>242.1</v>
+        <v>234.46</v>
       </c>
       <c r="F5" t="n">
-        <v>1572.56</v>
+        <v>1586.39</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>45.45000076293945</v>
+        <v>44.66999816894531</v>
       </c>
       <c r="F5" t="n">
-        <v>25088.40042114258</v>
+        <v>24657.83898925781</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>25088.40042114258</v>
+        <v>24657.83898925781</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>215.1399993896484</v>
+        <v>207.2599945068359</v>
       </c>
       <c r="F6" t="n">
-        <v>37649.49989318848</v>
+        <v>36270.49903869629</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>37649.49989318848</v>
+        <v>36270.49903869629</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.53999996185303</v>
+        <v>15.39999961853027</v>
       </c>
       <c r="F7" t="n">
-        <v>39285.11990356445</v>
+        <v>38931.19903564453</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>39285.11990356445</v>
+        <v>38931.19903564453</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4103</v>
+        <v>4028.699951171875</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02866885131899277</v>
+        <v>-0.02450421404025871</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.08808032847124869</v>
+        <v>-0.09977212742533992</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.60499954223633</v>
+        <v>58.70000076293945</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.1003697530277775</v>
+        <v>-0.05353111367816221</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2120430671246556</v>
+        <v>-0.2174064047160309</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.36</v>
+        <v>-0.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>84880.60650405883</v>
+        <v>85176.90344848632</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.0%</t>
+          <t>+51.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-50942.38432159425</v>
+        <v>-51180.26876220704</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+34.0%</t>
+          <t>+33.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-33938.2221824646</v>
+        <v>-33996.63468627929</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.67</v>
+        <v>44.79</v>
       </c>
       <c r="C2" t="n">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="D2" t="n">
-        <v>42.15</v>
+        <v>42.45</v>
       </c>
       <c r="E2" t="n">
-        <v>52.22</v>
+        <v>51.8</v>
       </c>
       <c r="F2" t="n">
-        <v>1389.46</v>
+        <v>1290.69</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.4</v>
+        <v>15.43</v>
       </c>
       <c r="C3" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="D3" t="n">
-        <v>14.47</v>
+        <v>14.55</v>
       </c>
       <c r="E3" t="n">
-        <v>18.2</v>
+        <v>18.08</v>
       </c>
       <c r="F3" t="n">
-        <v>2359.17</v>
+        <v>2230.96</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>207.26</v>
+        <v>208.44</v>
       </c>
       <c r="C5" t="n">
-        <v>9.07</v>
+        <v>8.67</v>
       </c>
       <c r="D5" t="n">
-        <v>198.19</v>
+        <v>199.77</v>
       </c>
       <c r="E5" t="n">
-        <v>234.46</v>
+        <v>234.45</v>
       </c>
       <c r="F5" t="n">
-        <v>1586.39</v>
+        <v>1517.18</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.66999816894531</v>
+        <v>44.79000091552734</v>
       </c>
       <c r="F5" t="n">
-        <v>24657.83898925781</v>
+        <v>24724.08050537109</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24657.83898925781</v>
+        <v>24724.08050537109</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>207.2599945068359</v>
+        <v>208.4400024414062</v>
       </c>
       <c r="F6" t="n">
-        <v>36270.49903869629</v>
+        <v>36477.00042724609</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>36270.49903869629</v>
+        <v>36477.00042724609</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.39999961853027</v>
+        <v>15.43000030517578</v>
       </c>
       <c r="F7" t="n">
-        <v>38931.19903564453</v>
+        <v>39007.04077148438</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>38931.19903564453</v>
+        <v>39007.04077148438</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4028.699951171875</v>
+        <v>4030.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02450421404025871</v>
+        <v>0.01017463674882002</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.09977212742533992</v>
+        <v>-0.1020694984172275</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58.70000076293945</v>
+        <v>59.27500152587891</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.05353111367816221</v>
+        <v>0.02106737798300862</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2174064047160309</v>
+        <v>-0.2129303304990506</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.3</v>
+        <v>0.01</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85176.90344848632</v>
+        <v>85312.31750411987</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.1%</t>
+          <t>+50.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-51180.26876220704</v>
+        <v>-50919.16873626709</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.9%</t>
+          <t>+34.3%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-33996.63468627929</v>
+        <v>-34393.14876785278</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.79</v>
+        <v>44.33</v>
       </c>
       <c r="C2" t="n">
         <v>2.34</v>
       </c>
       <c r="D2" t="n">
-        <v>42.45</v>
+        <v>41.99</v>
       </c>
       <c r="E2" t="n">
-        <v>51.8</v>
+        <v>51.36</v>
       </c>
       <c r="F2" t="n">
-        <v>1290.69</v>
+        <v>1292.86</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.43</v>
+        <v>15.59</v>
       </c>
       <c r="C3" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="D3" t="n">
-        <v>14.55</v>
+        <v>14.68</v>
       </c>
       <c r="E3" t="n">
-        <v>18.08</v>
+        <v>18.32</v>
       </c>
       <c r="F3" t="n">
-        <v>2230.96</v>
+        <v>2301.38</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>208.44</v>
+        <v>208.49</v>
       </c>
       <c r="C5" t="n">
-        <v>8.67</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>199.77</v>
+        <v>199.94</v>
       </c>
       <c r="E5" t="n">
-        <v>234.45</v>
+        <v>234.14</v>
       </c>
       <c r="F5" t="n">
-        <v>1517.18</v>
+        <v>1496.5</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.79000091552734</v>
+        <v>44.33000183105469</v>
       </c>
       <c r="F5" t="n">
-        <v>24724.08050537109</v>
+        <v>24470.16101074219</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24724.08050537109</v>
+        <v>24470.16101074219</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208.4400024414062</v>
+        <v>208.4900054931641</v>
       </c>
       <c r="F6" t="n">
-        <v>36477.00042724609</v>
+        <v>36485.75096130371</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>36477.00042724609</v>
+        <v>36485.75096130371</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.43000030517578</v>
+        <v>15.59000015258789</v>
       </c>
       <c r="F7" t="n">
-        <v>39007.04077148438</v>
+        <v>39411.52038574219</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>39007.04077148438</v>
+        <v>39411.52038574219</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4030.89990234375</v>
+        <v>4053.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01017463674882002</v>
+        <v>0.005681652981950114</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1020694984172275</v>
+        <v>-0.08639310210180928</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.27500152587891</v>
+        <v>59.77999877929688</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02106737798300862</v>
+        <v>0.0245423873488142</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2129303304990506</v>
+        <v>-0.1864009953226399</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.01</v>
+        <v>-0.26</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85312.31750411987</v>
+        <v>89174.19753799438</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-50919.16873626709</v>
+        <v>-53137.4987625122</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-34393.14876785278</v>
+        <v>-36036.69877548217</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.33</v>
+        <v>46.29</v>
       </c>
       <c r="C2" t="n">
         <v>2.34</v>
       </c>
       <c r="D2" t="n">
-        <v>41.99</v>
+        <v>43.95</v>
       </c>
       <c r="E2" t="n">
-        <v>51.36</v>
+        <v>53.32</v>
       </c>
       <c r="F2" t="n">
-        <v>1292.86</v>
+        <v>1293.26</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.59</v>
+        <v>16.33</v>
       </c>
       <c r="C3" t="n">
         <v>0.91</v>
       </c>
       <c r="D3" t="n">
-        <v>14.68</v>
+        <v>15.42</v>
       </c>
       <c r="E3" t="n">
-        <v>18.32</v>
+        <v>19.06</v>
       </c>
       <c r="F3" t="n">
-        <v>2301.38</v>
+        <v>2299.59</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>208.49</v>
+        <v>217.58</v>
       </c>
       <c r="C5" t="n">
-        <v>8.550000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>199.94</v>
+        <v>208.69</v>
       </c>
       <c r="E5" t="n">
-        <v>234.14</v>
+        <v>244.24</v>
       </c>
       <c r="F5" t="n">
-        <v>1496.5</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.33000183105469</v>
+        <v>46.29000091552734</v>
       </c>
       <c r="F5" t="n">
-        <v>24470.16101074219</v>
+        <v>25552.08050537109</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24470.16101074219</v>
+        <v>25552.08050537109</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208.4900054931641</v>
+        <v>217.5800018310547</v>
       </c>
       <c r="F6" t="n">
-        <v>36485.75096130371</v>
+        <v>38076.50032043457</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>36485.75096130371</v>
+        <v>38076.50032043457</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.59000015258789</v>
+        <v>16.32999992370605</v>
       </c>
       <c r="F7" t="n">
-        <v>39411.52038574219</v>
+        <v>41282.23980712891</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>39411.52038574219</v>
+        <v>41282.23980712891</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4053.39990234375</v>
+        <v>4137.2001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005681652981950114</v>
+        <v>0.01434286533477835</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.08639310210180928</v>
+        <v>-0.07565119624438632</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.77999877929688</v>
+        <v>61.51499938964844</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0245423873488142</v>
+        <v>0.03880643011983032</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1864009953226399</v>
+        <v>-0.1662261626013755</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -752,7 +752,7 @@
         <v>19.06</v>
       </c>
       <c r="F3" t="n">
-        <v>2299.59</v>
+        <v>2300.48</v>
       </c>
     </row>
     <row r="4">
@@ -785,10 +785,10 @@
         <v>208.69</v>
       </c>
       <c r="E5" t="n">
-        <v>244.24</v>
+        <v>244.26</v>
       </c>
       <c r="F5" t="n">
-        <v>1555</v>
+        <v>1556.25</v>
       </c>
     </row>
     <row r="6">
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4137.2001953125</v>
+        <v>4187.2998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01434286533477835</v>
+        <v>0.02662609527931137</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.07565119624438632</v>
+        <v>-0.06445775338250259</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.51499938964844</v>
+        <v>62.81499862670898</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03880643011983032</v>
+        <v>0.06075957293066514</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1662261626013755</v>
+        <v>-0.1486059827549354</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.26</v>
+        <v>0.02</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>89174.19753799438</v>
+        <v>88142.16838302612</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+50.7%</t>
+          <t>+49.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-53137.4987625122</v>
+        <v>-51716.12413177491</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+34.3%</t>
+          <t>+35.1%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-36036.69877548217</v>
+        <v>-36426.04425125122</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46.29</v>
+        <v>45.02</v>
       </c>
       <c r="C2" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="D2" t="n">
-        <v>43.95</v>
+        <v>42.66</v>
       </c>
       <c r="E2" t="n">
-        <v>53.32</v>
+        <v>52.1</v>
       </c>
       <c r="F2" t="n">
-        <v>1293.26</v>
+        <v>1303.51</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.33</v>
+        <v>16.46</v>
       </c>
       <c r="C3" t="n">
         <v>0.91</v>
       </c>
       <c r="D3" t="n">
-        <v>15.42</v>
+        <v>15.55</v>
       </c>
       <c r="E3" t="n">
-        <v>19.06</v>
+        <v>19.18</v>
       </c>
       <c r="F3" t="n">
-        <v>2300.48</v>
+        <v>2293.26</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>217.58</v>
+        <v>212.77</v>
       </c>
       <c r="C5" t="n">
-        <v>8.890000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>208.69</v>
+        <v>203.91</v>
       </c>
       <c r="E5" t="n">
-        <v>244.26</v>
+        <v>239.34</v>
       </c>
       <c r="F5" t="n">
-        <v>1556.25</v>
+        <v>1549.75</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46.29000091552734</v>
+        <v>45.02000045776367</v>
       </c>
       <c r="F5" t="n">
-        <v>25552.08050537109</v>
+        <v>24851.04025268555</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>25552.08050537109</v>
+        <v>24851.04025268555</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>217.5800018310547</v>
+        <v>212.7700042724609</v>
       </c>
       <c r="F6" t="n">
-        <v>38076.50032043457</v>
+        <v>37234.75074768066</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>38076.50032043457</v>
+        <v>37234.75074768066</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.32999992370605</v>
+        <v>16.45999908447266</v>
       </c>
       <c r="F7" t="n">
-        <v>41282.23980712891</v>
+        <v>41610.87768554688</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>41282.23980712891</v>
+        <v>41610.87768554688</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4187.2998046875</v>
+        <v>4176.2998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02662609527931137</v>
+        <v>0.03813167269073214</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.06445775338250259</v>
+        <v>-0.03680899034822716</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62.81499862670898</v>
+        <v>62.5099983215332</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06075957293066514</v>
+        <v>0.05099445282470194</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1486059827549354</v>
+        <v>-0.08644507806233348</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.02</v>
+        <v>0.47</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>88142.16838302612</v>
+        <v>85333.20173797607</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+49.9%</t>
+          <t>+50.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-51716.12413177491</v>
+        <v>-51017.12077941895</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+35.1%</t>
+          <t>+34.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-36426.04425125122</v>
+        <v>-34316.08095855713</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45.02</v>
+        <v>44.16</v>
       </c>
       <c r="C2" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="D2" t="n">
-        <v>42.66</v>
+        <v>41.99</v>
       </c>
       <c r="E2" t="n">
-        <v>52.1</v>
+        <v>50.67</v>
       </c>
       <c r="F2" t="n">
-        <v>1303.51</v>
+        <v>1197.84</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.46</v>
+        <v>15.56</v>
       </c>
       <c r="C3" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="D3" t="n">
-        <v>15.55</v>
+        <v>14.7</v>
       </c>
       <c r="E3" t="n">
-        <v>19.18</v>
+        <v>18.15</v>
       </c>
       <c r="F3" t="n">
-        <v>2293.26</v>
+        <v>2186.72</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>212.77</v>
+        <v>209.6</v>
       </c>
       <c r="C5" t="n">
-        <v>8.859999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>203.91</v>
+        <v>201.23</v>
       </c>
       <c r="E5" t="n">
-        <v>239.34</v>
+        <v>234.7</v>
       </c>
       <c r="F5" t="n">
-        <v>1549.75</v>
+        <v>1463.94</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>45.02000045776367</v>
+        <v>44.15999984741211</v>
       </c>
       <c r="F5" t="n">
-        <v>24851.04025268555</v>
+        <v>24376.31991577148</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24851.04025268555</v>
+        <v>24376.31991577148</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>212.7700042724609</v>
+        <v>209.6000061035156</v>
       </c>
       <c r="F6" t="n">
-        <v>37234.75074768066</v>
+        <v>36680.00106811523</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>37234.75074768066</v>
+        <v>36680.00106811523</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.45999908447266</v>
+        <v>15.5600004196167</v>
       </c>
       <c r="F7" t="n">
-        <v>41610.87768554688</v>
+        <v>39335.68106079102</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>41610.87768554688</v>
+        <v>39335.68106079102</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4176.2998046875</v>
+        <v>4107.10009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03813167269073214</v>
+        <v>0.009537164998265402</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.03680899034822716</v>
+        <v>-0.03589199585534042</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62.5099983215332</v>
+        <v>60.10499954223633</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05099445282470194</v>
+        <v>0.0003328694028197354</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.08644507806233348</v>
+        <v>-0.07664304071225492</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.47</v>
+        <v>0.84</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85333.20173797607</v>
+        <v>82707.73715667725</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-51017.12077941895</v>
+        <v>-49425.37778015137</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-34316.08095855713</v>
+        <v>-33282.35937652588</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.16</v>
+        <v>42.6</v>
       </c>
       <c r="C2" t="n">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="D2" t="n">
-        <v>41.99</v>
+        <v>40.36</v>
       </c>
       <c r="E2" t="n">
-        <v>50.67</v>
+        <v>49.33</v>
       </c>
       <c r="F2" t="n">
-        <v>1197.84</v>
+        <v>1237.66</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.56</v>
+        <v>15.09</v>
       </c>
       <c r="C3" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="D3" t="n">
-        <v>14.7</v>
+        <v>14.21</v>
       </c>
       <c r="E3" t="n">
-        <v>18.15</v>
+        <v>17.74</v>
       </c>
       <c r="F3" t="n">
-        <v>2186.72</v>
+        <v>2232.77</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>209.6</v>
+        <v>203.66</v>
       </c>
       <c r="C5" t="n">
-        <v>8.369999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="D5" t="n">
-        <v>201.23</v>
+        <v>195.32</v>
       </c>
       <c r="E5" t="n">
-        <v>234.7</v>
+        <v>228.69</v>
       </c>
       <c r="F5" t="n">
-        <v>1463.94</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.15999984741211</v>
+        <v>42.59999847412109</v>
       </c>
       <c r="F5" t="n">
-        <v>24376.31991577148</v>
+        <v>23515.19915771484</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24376.31991577148</v>
+        <v>23515.19915771484</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>209.6000061035156</v>
+        <v>203.6600036621094</v>
       </c>
       <c r="F6" t="n">
-        <v>36680.00106811523</v>
+        <v>35640.50064086914</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>36680.00106811523</v>
+        <v>35640.50064086914</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.5600004196167</v>
+        <v>15.09000015258789</v>
       </c>
       <c r="F7" t="n">
-        <v>39335.68106079102</v>
+        <v>38147.52038574219</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>39335.68106079102</v>
+        <v>38147.52038574219</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4107.10009765625</v>
+        <v>4084.300048828125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009537164998265402</v>
+        <v>-0.006905474538782208</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.03589199585534042</v>
+        <v>-0.005817668406628562</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60.10499954223633</v>
+        <v>58.75500106811523</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0003328694028197354</v>
+        <v>-0.03113303167432202</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.07664304071225492</v>
+        <v>-0.09046576639990933</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.84</v>
+        <v>0.54</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>82707.73715667725</v>
+        <v>85584.04237213134</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+50.8%</t>
+          <t>+50.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-49425.37778015137</v>
+        <v>-50701.27790222168</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+34.2%</t>
+          <t>+34.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-33282.35937652588</v>
+        <v>-34882.76446990967</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42.6</v>
+        <v>44.12</v>
       </c>
       <c r="C2" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="D2" t="n">
-        <v>40.36</v>
+        <v>42.01</v>
       </c>
       <c r="E2" t="n">
-        <v>49.33</v>
+        <v>50.43</v>
       </c>
       <c r="F2" t="n">
-        <v>1237.66</v>
+        <v>1161.96</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.09</v>
+        <v>15.79</v>
       </c>
       <c r="C3" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="D3" t="n">
-        <v>14.21</v>
+        <v>14.94</v>
       </c>
       <c r="E3" t="n">
-        <v>17.74</v>
+        <v>18.35</v>
       </c>
       <c r="F3" t="n">
-        <v>2232.77</v>
+        <v>2159.63</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>203.66</v>
+        <v>208.09</v>
       </c>
       <c r="C5" t="n">
-        <v>8.34</v>
+        <v>7.97</v>
       </c>
       <c r="D5" t="n">
-        <v>195.32</v>
+        <v>200.12</v>
       </c>
       <c r="E5" t="n">
-        <v>228.69</v>
+        <v>231.99</v>
       </c>
       <c r="F5" t="n">
-        <v>1460</v>
+        <v>1394.38</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>42.59999847412109</v>
+        <v>44.11999893188477</v>
       </c>
       <c r="F5" t="n">
-        <v>23515.19915771484</v>
+        <v>24354.23941040039</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>23515.19915771484</v>
+        <v>24354.23941040039</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>203.6600036621094</v>
+        <v>208.0899963378906</v>
       </c>
       <c r="F6" t="n">
-        <v>35640.50064086914</v>
+        <v>36415.74935913086</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>35640.50064086914</v>
+        <v>36415.74935913086</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.09000015258789</v>
+        <v>15.78999996185303</v>
       </c>
       <c r="F7" t="n">
-        <v>38147.52038574219</v>
+        <v>39917.11990356445</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>38147.52038574219</v>
+        <v>39917.11990356445</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4084.300048828125</v>
+        <v>4133.10009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.006905474538782208</v>
+        <v>0.004960221113856411</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.005817668406628562</v>
+        <v>0.01046379197545355</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58.75500106811523</v>
+        <v>60.40499877929688</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03113303167432202</v>
+        <v>-0.003924653644959752</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.09046576639990933</v>
+        <v>-0.05447287522371824</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85584.04237213134</v>
+        <v>85055.07912063599</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+50.4%</t>
+          <t>+50.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-50701.27790222168</v>
+        <v>-50065.35984039307</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+34.6%</t>
+          <t>+35.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-34882.76446990967</v>
+        <v>-34989.71928024292</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.12</v>
+        <v>43.67</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="D2" t="n">
-        <v>42.01</v>
+        <v>41.7</v>
       </c>
       <c r="E2" t="n">
-        <v>50.43</v>
+        <v>49.58</v>
       </c>
       <c r="F2" t="n">
-        <v>1161.96</v>
+        <v>1088.23</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.79</v>
+        <v>15.82</v>
       </c>
       <c r="C3" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="D3" t="n">
-        <v>14.94</v>
+        <v>14.99</v>
       </c>
       <c r="E3" t="n">
-        <v>18.35</v>
+        <v>18.31</v>
       </c>
       <c r="F3" t="n">
-        <v>2159.63</v>
+        <v>2101.76</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>208.09</v>
+        <v>205.52</v>
       </c>
       <c r="C5" t="n">
-        <v>7.97</v>
+        <v>7.26</v>
       </c>
       <c r="D5" t="n">
-        <v>200.12</v>
+        <v>198.26</v>
       </c>
       <c r="E5" t="n">
-        <v>231.99</v>
+        <v>227.31</v>
       </c>
       <c r="F5" t="n">
-        <v>1394.38</v>
+        <v>1271.06</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.11999893188477</v>
+        <v>43.66999816894531</v>
       </c>
       <c r="F5" t="n">
-        <v>24354.23941040039</v>
+        <v>24105.83898925781</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24354.23941040039</v>
+        <v>24105.83898925781</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208.0899963378906</v>
+        <v>205.5200042724609</v>
       </c>
       <c r="F6" t="n">
-        <v>36415.74935913086</v>
+        <v>35966.00074768066</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>36415.74935913086</v>
+        <v>35966.00074768066</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.78999996185303</v>
+        <v>15.81999969482422</v>
       </c>
       <c r="F7" t="n">
-        <v>39917.11990356445</v>
+        <v>39992.95922851562</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>39917.11990356445</v>
+        <v>39992.95922851562</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4133.10009765625</v>
+        <v>4128.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004960221113856411</v>
+        <v>-0.006305550936613669</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01046379197545355</v>
+        <v>-0.02042706943208783</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60.40499877929688</v>
+        <v>60.29999923706055</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.003924653644959752</v>
+        <v>-0.02616277422141855</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.05447287522371824</v>
+        <v>-0.1113927672590047</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.52</v>
+        <v>0.26</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85055.07912063599</v>
+        <v>82626.92867507934</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+50.0%</t>
+          <t>+50.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-50065.35984039307</v>
+        <v>-48935.33624420166</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+35.0%</t>
+          <t>+34.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-34989.71928024292</v>
+        <v>-33691.59243087769</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.67</v>
+        <v>42.7</v>
       </c>
       <c r="C2" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>41.7</v>
+        <v>40.7</v>
       </c>
       <c r="E2" t="n">
-        <v>49.58</v>
+        <v>48.7</v>
       </c>
       <c r="F2" t="n">
-        <v>1088.23</v>
+        <v>1104.79</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.82</v>
+        <v>15.25</v>
       </c>
       <c r="C3" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="D3" t="n">
-        <v>14.99</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="n">
-        <v>18.31</v>
+        <v>17.81</v>
       </c>
       <c r="F3" t="n">
-        <v>2101.76</v>
+        <v>2156.02</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>205.52</v>
+        <v>200.49</v>
       </c>
       <c r="C5" t="n">
-        <v>7.26</v>
+        <v>7.23</v>
       </c>
       <c r="D5" t="n">
-        <v>198.26</v>
+        <v>193.27</v>
       </c>
       <c r="E5" t="n">
-        <v>227.31</v>
+        <v>222.17</v>
       </c>
       <c r="F5" t="n">
-        <v>1271.06</v>
+        <v>1264.38</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>43.66999816894531</v>
+        <v>42.70000076293945</v>
       </c>
       <c r="F5" t="n">
-        <v>24105.83898925781</v>
+        <v>23570.40042114258</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24105.83898925781</v>
+        <v>23570.40042114258</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205.5200042724609</v>
+        <v>200.4900054931641</v>
       </c>
       <c r="F6" t="n">
-        <v>35966.00074768066</v>
+        <v>35085.75096130371</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>35966.00074768066</v>
+        <v>35085.75096130371</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.81999969482422</v>
+        <v>15.25</v>
       </c>
       <c r="F7" t="n">
-        <v>39992.95922851562</v>
+        <v>38552</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>39992.95922851562</v>
+        <v>38552</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4128.89990234375</v>
+        <v>4010.10009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.006305550936613669</v>
+        <v>-0.03261518186896073</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02042706943208783</v>
+        <v>-0.0734519182864487</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60.29999923706055</v>
+        <v>57.97000122070312</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.02616277422141855</v>
+        <v>-0.04859592895275788</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1113927672590047</v>
+        <v>-0.172637232676927</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>82626.92867507934</v>
+        <v>83910.1032585144</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-48935.33624420166</v>
+        <v>-49661.99168548585</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-33691.59243087769</v>
+        <v>-34248.11157302857</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42.7</v>
+        <v>43.51</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="D2" t="n">
-        <v>40.7</v>
+        <v>41.61</v>
       </c>
       <c r="E2" t="n">
-        <v>48.7</v>
+        <v>49.2</v>
       </c>
       <c r="F2" t="n">
-        <v>1104.79</v>
+        <v>1047.62</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.25</v>
+        <v>15.5</v>
       </c>
       <c r="C3" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>14.67</v>
       </c>
       <c r="E3" t="n">
-        <v>17.81</v>
+        <v>17.98</v>
       </c>
       <c r="F3" t="n">
-        <v>2156.02</v>
+        <v>2092.82</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>200.49</v>
+        <v>202.95</v>
       </c>
       <c r="C5" t="n">
-        <v>7.23</v>
+        <v>7.1</v>
       </c>
       <c r="D5" t="n">
-        <v>193.27</v>
+        <v>195.85</v>
       </c>
       <c r="E5" t="n">
-        <v>222.17</v>
+        <v>224.25</v>
       </c>
       <c r="F5" t="n">
-        <v>1264.38</v>
+        <v>1242.63</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>42.70000076293945</v>
+        <v>43.5099983215332</v>
       </c>
       <c r="F5" t="n">
-        <v>23570.40042114258</v>
+        <v>24017.51907348633</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>23570.40042114258</v>
+        <v>24017.51907348633</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>200.4900054931641</v>
+        <v>202.9499969482422</v>
       </c>
       <c r="F6" t="n">
-        <v>35085.75096130371</v>
+        <v>35516.24946594238</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>35085.75096130371</v>
+        <v>35516.24946594238</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.25</v>
+        <v>15.5</v>
       </c>
       <c r="F7" t="n">
-        <v>38552</v>
+        <v>39184</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>38552</v>
+        <v>39184</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4010.10009765625</v>
+        <v>4055.699951171875</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.03261518186896073</v>
+        <v>-0.00373380616976704</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0734519182864487</v>
+        <v>-0.063543364514831</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57.97000122070312</v>
+        <v>58.99499893188477</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.04859592895275788</v>
+        <v>0.01428714404292308</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.172637232676927</v>
+        <v>-0.1559965495870791</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.28</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83910.1032585144</v>
+        <v>83792.80489273071</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+50.3%</t>
+          <t>+50.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-49661.99168548585</v>
+        <v>-49638.91331939698</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+34.7%</t>
+          <t>+34.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-34248.11157302857</v>
+        <v>-34153.89157333374</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.51</v>
+        <v>43.57</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="D2" t="n">
-        <v>41.61</v>
+        <v>41.71</v>
       </c>
       <c r="E2" t="n">
-        <v>49.2</v>
+        <v>49.15</v>
       </c>
       <c r="F2" t="n">
-        <v>1047.62</v>
+        <v>1026.33</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.5</v>
+        <v>15.46</v>
       </c>
       <c r="C3" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="D3" t="n">
-        <v>14.67</v>
+        <v>14.62</v>
       </c>
       <c r="E3" t="n">
-        <v>17.98</v>
+        <v>17.97</v>
       </c>
       <c r="F3" t="n">
-        <v>2092.82</v>
+        <v>2111.76</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>202.95</v>
+        <v>202.55</v>
       </c>
       <c r="C5" t="n">
-        <v>7.1</v>
+        <v>6.95</v>
       </c>
       <c r="D5" t="n">
-        <v>195.85</v>
+        <v>195.6</v>
       </c>
       <c r="E5" t="n">
-        <v>224.25</v>
+        <v>223.41</v>
       </c>
       <c r="F5" t="n">
-        <v>1242.63</v>
+        <v>1217.06</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>43.5099983215332</v>
+        <v>43.56999969482422</v>
       </c>
       <c r="F5" t="n">
-        <v>24017.51907348633</v>
+        <v>24050.63983154297</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24017.51907348633</v>
+        <v>24050.63983154297</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>202.9499969482422</v>
+        <v>202.5500030517578</v>
       </c>
       <c r="F6" t="n">
-        <v>35516.24946594238</v>
+        <v>35446.25053405762</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>35516.24946594238</v>
+        <v>35446.25053405762</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.5</v>
+        <v>15.46000003814697</v>
       </c>
       <c r="F7" t="n">
-        <v>39184</v>
+        <v>39082.88009643555</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>39184</v>
+        <v>39082.88009643555</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4055.699951171875</v>
+        <v>4064.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.00373380616976704</v>
+        <v>-0.016026774257344</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.063543364514831</v>
+        <v>-0.06756291876343601</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58.99499893188477</v>
+        <v>58.07500076293945</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01428714404292308</v>
+        <v>-0.03814299334143301</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1559965495870791</v>
+        <v>-0.1785249311858735</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83792.80489273071</v>
+        <v>80370.91767807007</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+50.4%</t>
+          <t>+51.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-49638.91331939698</v>
+        <v>-48392.05756072998</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+34.6%</t>
+          <t>+33.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-34153.89157333374</v>
+        <v>-31978.86011734009</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.57</v>
+        <v>41.98</v>
       </c>
       <c r="C2" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="D2" t="n">
-        <v>41.71</v>
+        <v>40.08</v>
       </c>
       <c r="E2" t="n">
-        <v>49.15</v>
+        <v>47.67</v>
       </c>
       <c r="F2" t="n">
-        <v>1026.33</v>
+        <v>1046.43</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.46</v>
+        <v>14.52</v>
       </c>
       <c r="C3" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="D3" t="n">
-        <v>14.62</v>
+        <v>13.67</v>
       </c>
       <c r="E3" t="n">
-        <v>17.97</v>
+        <v>17.08</v>
       </c>
       <c r="F3" t="n">
-        <v>2111.76</v>
+        <v>2156.02</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>202.55</v>
+        <v>198.14</v>
       </c>
       <c r="C5" t="n">
-        <v>6.95</v>
+        <v>6.94</v>
       </c>
       <c r="D5" t="n">
-        <v>195.6</v>
+        <v>191.2</v>
       </c>
       <c r="E5" t="n">
-        <v>223.41</v>
+        <v>218.96</v>
       </c>
       <c r="F5" t="n">
-        <v>1217.06</v>
+        <v>1214.31</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>43.56999969482422</v>
+        <v>41.97999954223633</v>
       </c>
       <c r="F5" t="n">
-        <v>24050.63983154297</v>
+        <v>23172.95974731445</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24050.63983154297</v>
+        <v>23172.95974731445</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>202.5500030517578</v>
+        <v>198.1399993896484</v>
       </c>
       <c r="F6" t="n">
-        <v>35446.25053405762</v>
+        <v>34674.49989318848</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>35446.25053405762</v>
+        <v>34674.49989318848</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.46000003814697</v>
+        <v>14.52000045776367</v>
       </c>
       <c r="F7" t="n">
-        <v>39082.88009643555</v>
+        <v>36706.56115722656</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>39082.88009643555</v>
+        <v>36706.56115722656</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4064.39990234375</v>
+        <v>3978.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.016026774257344</v>
+        <v>-0.03062795553750852</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.06756291876343601</v>
+        <v>-0.05816628148770131</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58.07500076293945</v>
+        <v>55.75</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03814299334143301</v>
+        <v>-0.06786601073949983</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1785249311858735</v>
+        <v>-0.1585540365089372</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.66</v>
+        <v>0.99</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80370.91767807007</v>
+        <v>80255.32618637085</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.2%</t>
+          <t>+51.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-48392.05756072998</v>
+        <v>-48749.98791961669</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.8%</t>
+          <t>+33.4%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-31978.86011734009</v>
+        <v>-31505.33826675415</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41.98</v>
+        <v>41.77</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="D2" t="n">
-        <v>40.08</v>
+        <v>39.88</v>
       </c>
       <c r="E2" t="n">
-        <v>47.67</v>
+        <v>47.44</v>
       </c>
       <c r="F2" t="n">
-        <v>1046.43</v>
+        <v>1043.48</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.52</v>
+        <v>14.33</v>
       </c>
       <c r="C3" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="D3" t="n">
-        <v>13.67</v>
+        <v>13.49</v>
       </c>
       <c r="E3" t="n">
-        <v>17.08</v>
+        <v>16.85</v>
       </c>
       <c r="F3" t="n">
-        <v>2156.02</v>
+        <v>2122.62</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>198.14</v>
+        <v>200.77</v>
       </c>
       <c r="C5" t="n">
-        <v>6.94</v>
+        <v>6.87</v>
       </c>
       <c r="D5" t="n">
-        <v>191.2</v>
+        <v>193.9</v>
       </c>
       <c r="E5" t="n">
-        <v>218.96</v>
+        <v>221.39</v>
       </c>
       <c r="F5" t="n">
-        <v>1214.31</v>
+        <v>1202.82</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>41.97999954223633</v>
+        <v>41.77000045776367</v>
       </c>
       <c r="F5" t="n">
-        <v>23172.95974731445</v>
+        <v>23057.04025268555</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>23172.95974731445</v>
+        <v>23057.04025268555</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>198.1399993896484</v>
+        <v>200.7700042724609</v>
       </c>
       <c r="F6" t="n">
-        <v>34674.49989318848</v>
+        <v>35134.75074768066</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>34674.49989318848</v>
+        <v>35134.75074768066</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.52000045776367</v>
+        <v>14.32999992370605</v>
       </c>
       <c r="F7" t="n">
-        <v>36706.56115722656</v>
+        <v>36226.23980712891</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>36706.56115722656</v>
+        <v>36226.23980712891</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3978.39990234375</v>
+        <v>4023</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.03062795553750852</v>
+        <v>-0.01976075040239988</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.05816628148770131</v>
+        <v>-0.04760779645535174</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55.75</v>
+        <v>56.22000122070312</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.06786601073949983</v>
+        <v>-0.06000764100297418</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1585540365089372</v>
+        <v>-0.1514602135493585</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.99</v>
+        <v>1.09</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CERRAR ARBITRAJE (Media alcanzada)</t>
+          <t>MANTENER</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80255.32618637085</v>
+        <v>80277.18650131226</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.6%</t>
+          <t>+51.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-48749.98791961669</v>
+        <v>-48874.25403900146</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.4%</t>
+          <t>+33.3%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-31505.33826675415</v>
+        <v>-31402.93246231079</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41.77</v>
+        <v>42.19</v>
       </c>
       <c r="C2" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="D2" t="n">
-        <v>39.88</v>
+        <v>40.34</v>
       </c>
       <c r="E2" t="n">
-        <v>47.44</v>
+        <v>47.73</v>
       </c>
       <c r="F2" t="n">
-        <v>1043.48</v>
+        <v>1018.83</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.33</v>
+        <v>14.29</v>
       </c>
       <c r="C3" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="D3" t="n">
-        <v>13.49</v>
+        <v>13.46</v>
       </c>
       <c r="E3" t="n">
-        <v>16.85</v>
+        <v>16.77</v>
       </c>
       <c r="F3" t="n">
-        <v>2122.62</v>
+        <v>2089.21</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>200.77</v>
+        <v>200.17</v>
       </c>
       <c r="C5" t="n">
-        <v>6.87</v>
+        <v>6.41</v>
       </c>
       <c r="D5" t="n">
-        <v>193.9</v>
+        <v>193.76</v>
       </c>
       <c r="E5" t="n">
-        <v>221.39</v>
+        <v>219.41</v>
       </c>
       <c r="F5" t="n">
-        <v>1202.82</v>
+        <v>1122.25</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>41.77000045776367</v>
+        <v>42.18999862670898</v>
       </c>
       <c r="F5" t="n">
-        <v>23057.04025268555</v>
+        <v>23288.87924194336</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>23057.04025268555</v>
+        <v>23288.87924194336</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>200.7700042724609</v>
+        <v>200.1699981689453</v>
       </c>
       <c r="F6" t="n">
-        <v>35134.75074768066</v>
+        <v>35029.74967956543</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>35134.75074768066</v>
+        <v>35029.74967956543</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.32999992370605</v>
+        <v>14.28999996185303</v>
       </c>
       <c r="F7" t="n">
-        <v>36226.23980712891</v>
+        <v>36125.11990356445</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>36226.23980712891</v>
+        <v>36125.11990356445</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4023</v>
+        <v>4004.199951171875</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01976075040239988</v>
+        <v>-0.01401101797939264</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04760779645535174</v>
+        <v>-0.04249263619922683</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56.22000122070312</v>
+        <v>56.42499923706055</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.06000764100297418</v>
+        <v>-0.03993398468084752</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1514602135493585</v>
+        <v>-0.1389045909447877</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.09</v>
+        <v>0.74</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MANTENER</t>
+          <t>CERRAR ARBITRAJE (Media alcanzada)</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80277.18650131226</v>
+        <v>84552.45715332031</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.7%</t>
+          <t>+51.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-48874.25403900146</v>
+        <v>-50873.01119995118</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.3%</t>
+          <t>+33.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-31402.93246231079</v>
+        <v>-33679.44595336914</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42.19</v>
+        <v>44.43</v>
       </c>
       <c r="C2" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="D2" t="n">
-        <v>40.34</v>
+        <v>42.52</v>
       </c>
       <c r="E2" t="n">
-        <v>47.73</v>
+        <v>50.17</v>
       </c>
       <c r="F2" t="n">
-        <v>1018.83</v>
+        <v>1057.08</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.29</v>
+        <v>15.29</v>
       </c>
       <c r="C3" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="D3" t="n">
-        <v>13.46</v>
+        <v>14.43</v>
       </c>
       <c r="E3" t="n">
-        <v>16.77</v>
+        <v>17.88</v>
       </c>
       <c r="F3" t="n">
-        <v>2089.21</v>
+        <v>2184.91</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>200.17</v>
+        <v>207.4</v>
       </c>
       <c r="C5" t="n">
-        <v>6.41</v>
+        <v>6.68</v>
       </c>
       <c r="D5" t="n">
-        <v>193.76</v>
+        <v>200.72</v>
       </c>
       <c r="E5" t="n">
-        <v>219.41</v>
+        <v>227.42</v>
       </c>
       <c r="F5" t="n">
-        <v>1122.25</v>
+        <v>1168.13</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>42.18999862670898</v>
+        <v>44.43000030517578</v>
       </c>
       <c r="F5" t="n">
-        <v>23288.87924194336</v>
+        <v>24525.36016845703</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>23288.87924194336</v>
+        <v>24525.36016845703</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>200.1699981689453</v>
+        <v>207.3999938964844</v>
       </c>
       <c r="F6" t="n">
-        <v>35029.74967956543</v>
+        <v>36294.99893188477</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>35029.74967956543</v>
+        <v>36294.99893188477</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.28999996185303</v>
+        <v>15.28999996185303</v>
       </c>
       <c r="F7" t="n">
-        <v>36125.11990356445</v>
+        <v>38653.11990356445</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>36125.11990356445</v>
+        <v>38653.11990356445</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4004.199951171875</v>
+        <v>4083.199951171875</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.01401101797939264</v>
+        <v>0.009693360823905817</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.04249263619922683</v>
+        <v>-0.01130776829369939</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>56.42499923706055</v>
+        <v>59.08499908447266</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03993398468084752</v>
+        <v>0.03458235778346519</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1389045909447877</v>
+        <v>-0.04732346584372871</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.74</v>
+        <v>0.41</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>84552.45715332031</v>
+        <v>86813.60211868286</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.1%</t>
+          <t>+51.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-50873.01119995118</v>
+        <v>-52255.96565704346</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.9%</t>
+          <t>+33.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-33679.44595336914</v>
+        <v>-34557.63646163941</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.43</v>
+        <v>45.29</v>
       </c>
       <c r="C2" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="D2" t="n">
-        <v>42.52</v>
+        <v>43.4</v>
       </c>
       <c r="E2" t="n">
-        <v>50.17</v>
+        <v>50.97</v>
       </c>
       <c r="F2" t="n">
-        <v>1057.08</v>
+        <v>1046.04</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.29</v>
+        <v>15.69</v>
       </c>
       <c r="C3" t="n">
         <v>0.86</v>
       </c>
       <c r="D3" t="n">
-        <v>14.43</v>
+        <v>14.83</v>
       </c>
       <c r="E3" t="n">
-        <v>17.88</v>
+        <v>18.27</v>
       </c>
       <c r="F3" t="n">
-        <v>2184.91</v>
+        <v>2172.26</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>207.4</v>
+        <v>214.11</v>
       </c>
       <c r="C5" t="n">
-        <v>6.68</v>
+        <v>6.85</v>
       </c>
       <c r="D5" t="n">
-        <v>200.72</v>
+        <v>207.26</v>
       </c>
       <c r="E5" t="n">
-        <v>227.42</v>
+        <v>234.65</v>
       </c>
       <c r="F5" t="n">
-        <v>1168.13</v>
+        <v>1198.19</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.43000030517578</v>
+        <v>45.29000091552734</v>
       </c>
       <c r="F5" t="n">
-        <v>24525.36016845703</v>
+        <v>25000.08050537109</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24525.36016845703</v>
+        <v>25000.08050537109</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>207.3999938964844</v>
+        <v>214.1100006103516</v>
       </c>
       <c r="F6" t="n">
-        <v>36294.99893188477</v>
+        <v>37469.25010681152</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>36294.99893188477</v>
+        <v>37469.25010681152</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.28999996185303</v>
+        <v>15.6899995803833</v>
       </c>
       <c r="F7" t="n">
-        <v>38653.11990356445</v>
+        <v>39664.31893920898</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>38653.11990356445</v>
+        <v>39664.31893920898</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4083.199951171875</v>
+        <v>4121.2998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009693360823905817</v>
+        <v>0.03404749691547049</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01130776829369939</v>
+        <v>0.03282955022338419</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.08499908447266</v>
+        <v>59.63000106811523</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03458235778346519</v>
+        <v>0.06676450566680248</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04732346584372871</v>
+        <v>0.02718257734944252</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.41</v>
+        <v>0.21</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86813.60211868286</v>
+        <v>85518.78788146972</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.2%</t>
+          <t>+51.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-52255.96565704346</v>
+        <v>-51820.34558715821</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.8%</t>
+          <t>+33.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-34557.63646163941</v>
+        <v>-33698.44229431153</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45.29</v>
+        <v>44.19</v>
       </c>
       <c r="C2" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="D2" t="n">
-        <v>43.4</v>
+        <v>42.36</v>
       </c>
       <c r="E2" t="n">
-        <v>50.97</v>
+        <v>49.69</v>
       </c>
       <c r="F2" t="n">
-        <v>1046.04</v>
+        <v>1012.13</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.69</v>
+        <v>15.32</v>
       </c>
       <c r="C3" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="D3" t="n">
-        <v>14.83</v>
+        <v>14.48</v>
       </c>
       <c r="E3" t="n">
-        <v>18.27</v>
+        <v>17.84</v>
       </c>
       <c r="F3" t="n">
-        <v>2172.26</v>
+        <v>2119.91</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>214.11</v>
+        <v>214.22</v>
       </c>
       <c r="C5" t="n">
-        <v>6.85</v>
+        <v>6.64</v>
       </c>
       <c r="D5" t="n">
-        <v>207.26</v>
+        <v>207.58</v>
       </c>
       <c r="E5" t="n">
-        <v>234.65</v>
+        <v>234.13</v>
       </c>
       <c r="F5" t="n">
-        <v>1198.19</v>
+        <v>1161.47</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>45.29000091552734</v>
+        <v>44.18999862670898</v>
       </c>
       <c r="F5" t="n">
-        <v>25000.08050537109</v>
+        <v>24392.87924194336</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>25000.08050537109</v>
+        <v>24392.87924194336</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>214.1100006103516</v>
+        <v>214.2200012207031</v>
       </c>
       <c r="F6" t="n">
-        <v>37469.25010681152</v>
+        <v>37488.50021362305</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>37469.25010681152</v>
+        <v>37488.50021362305</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.6899995803833</v>
+        <v>15.31999969482422</v>
       </c>
       <c r="F7" t="n">
-        <v>39664.31893920898</v>
+        <v>38728.95922851562</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>39664.31893920898</v>
+        <v>38728.95922851562</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4121.2998046875</v>
+        <v>4052.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03404749691547049</v>
+        <v>0.0098935758105414</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03282955022338419</v>
+        <v>0.005433544806785706</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.63000106811523</v>
+        <v>57.94499969482422</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06676450566680248</v>
+        <v>0.03403050709580135</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02718257734944252</v>
+        <v>-0.006906832811417796</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85518.78788146972</v>
+        <v>85125.35707550049</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.5%</t>
+          <t>+51.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-51820.34558715821</v>
+        <v>-51858.81015319824</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.5%</t>
+          <t>+33.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-33698.44229431153</v>
+        <v>-33266.54692230224</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.19</v>
+        <v>44.03</v>
       </c>
       <c r="C2" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="D2" t="n">
-        <v>42.36</v>
+        <v>42.32</v>
       </c>
       <c r="E2" t="n">
-        <v>49.69</v>
+        <v>49.17</v>
       </c>
       <c r="F2" t="n">
-        <v>1012.13</v>
+        <v>946.29</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.32</v>
+        <v>15.14</v>
       </c>
       <c r="C3" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="D3" t="n">
-        <v>14.48</v>
+        <v>14.31</v>
       </c>
       <c r="E3" t="n">
-        <v>17.84</v>
+        <v>17.64</v>
       </c>
       <c r="F3" t="n">
-        <v>2119.91</v>
+        <v>2104.56</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>214.22</v>
+        <v>214.68</v>
       </c>
       <c r="C5" t="n">
-        <v>6.64</v>
+        <v>6.24</v>
       </c>
       <c r="D5" t="n">
-        <v>207.58</v>
+        <v>208.44</v>
       </c>
       <c r="E5" t="n">
-        <v>234.13</v>
+        <v>233.4</v>
       </c>
       <c r="F5" t="n">
-        <v>1161.47</v>
+        <v>1092.13</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.18999862670898</v>
+        <v>44.02999877929688</v>
       </c>
       <c r="F5" t="n">
-        <v>24392.87924194336</v>
+        <v>24304.55932617188</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24392.87924194336</v>
+        <v>24304.55932617188</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>214.2200012207031</v>
+        <v>214.6799926757812</v>
       </c>
       <c r="F6" t="n">
-        <v>37488.50021362305</v>
+        <v>37568.99871826172</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>37488.50021362305</v>
+        <v>37568.99871826172</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.31999969482422</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="F7" t="n">
-        <v>38728.95922851562</v>
+        <v>38273.92086791992</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>38728.95922851562</v>
+        <v>38273.92086791992</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4052.39990234375</v>
+        <v>4055.699951171875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0098935758105414</v>
+        <v>0.01132082432510662</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005433544806785706</v>
+        <v>-0.005639051726124555</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57.94499969482422</v>
+        <v>58.4900016784668</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03403050709580135</v>
+        <v>0.0297173267730011</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.006906832811417796</v>
+        <v>-0.01227683582590677</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85125.35707550049</v>
+        <v>85242.52901000976</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.8%</t>
+          <t>+51.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-51858.81015319824</v>
+        <v>-51856.4764831543</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.2%</t>
+          <t>+33.3%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-33266.54692230224</v>
+        <v>-33386.05252685547</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.03</v>
+        <v>44.13</v>
       </c>
       <c r="C2" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="D2" t="n">
-        <v>42.32</v>
+        <v>42.36</v>
       </c>
       <c r="E2" t="n">
-        <v>49.17</v>
+        <v>49.44</v>
       </c>
       <c r="F2" t="n">
-        <v>946.29</v>
+        <v>977.04</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.14</v>
+        <v>15.19</v>
       </c>
       <c r="C3" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="D3" t="n">
-        <v>14.31</v>
+        <v>14.35</v>
       </c>
       <c r="E3" t="n">
-        <v>17.64</v>
+        <v>17.72</v>
       </c>
       <c r="F3" t="n">
-        <v>2104.56</v>
+        <v>2134.35</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>214.68</v>
+        <v>214.43</v>
       </c>
       <c r="C5" t="n">
-        <v>6.24</v>
+        <v>6.44</v>
       </c>
       <c r="D5" t="n">
-        <v>208.44</v>
+        <v>207.99</v>
       </c>
       <c r="E5" t="n">
-        <v>233.4</v>
+        <v>233.74</v>
       </c>
       <c r="F5" t="n">
-        <v>1092.13</v>
+        <v>1126.36</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.02999877929688</v>
+        <v>44.13000106811523</v>
       </c>
       <c r="F5" t="n">
-        <v>24304.55932617188</v>
+        <v>24359.76058959961</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24304.55932617188</v>
+        <v>24359.76058959961</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>214.6799926757812</v>
+        <v>214.4299926757812</v>
       </c>
       <c r="F6" t="n">
-        <v>37568.99871826172</v>
+        <v>37525.24871826172</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>37568.99871826172</v>
+        <v>37525.24871826172</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.14000034332275</v>
+        <v>15.1899995803833</v>
       </c>
       <c r="F7" t="n">
-        <v>38273.92086791992</v>
+        <v>38400.31893920898</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>38273.92086791992</v>
+        <v>38400.31893920898</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4055.699951171875</v>
+        <v>4074.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01132082432510662</v>
+        <v>0.0009333606632977443</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.005639051726124555</v>
+        <v>0.01307705861748176</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58.4900016784668</v>
+        <v>58.63999938964844</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0297173267730011</v>
+        <v>-0.003314348565625846</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01227683582590677</v>
+        <v>0.00799312692197951</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85242.52901000976</v>
+        <v>82875.30710296631</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.7%</t>
+          <t>+52.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-51856.4764831543</v>
+        <v>-50967.92468566895</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.3%</t>
+          <t>+32.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-33386.05252685547</v>
+        <v>-31907.38241729736</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.13</v>
+        <v>43.23</v>
       </c>
       <c r="C2" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="D2" t="n">
-        <v>42.36</v>
+        <v>41.48</v>
       </c>
       <c r="E2" t="n">
-        <v>49.44</v>
+        <v>48.48</v>
       </c>
       <c r="F2" t="n">
-        <v>977.04</v>
+        <v>966.91</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.19</v>
+        <v>14.55</v>
       </c>
       <c r="C3" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="D3" t="n">
-        <v>14.35</v>
+        <v>13.76</v>
       </c>
       <c r="E3" t="n">
-        <v>17.72</v>
+        <v>16.92</v>
       </c>
       <c r="F3" t="n">
-        <v>2134.35</v>
+        <v>1995.28</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>214.43</v>
+        <v>210.6</v>
       </c>
       <c r="C5" t="n">
-        <v>6.44</v>
+        <v>6.35</v>
       </c>
       <c r="D5" t="n">
-        <v>207.99</v>
+        <v>204.25</v>
       </c>
       <c r="E5" t="n">
-        <v>233.74</v>
+        <v>229.65</v>
       </c>
       <c r="F5" t="n">
-        <v>1126.36</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.13000106811523</v>
+        <v>43.22999954223633</v>
       </c>
       <c r="F5" t="n">
-        <v>24359.76058959961</v>
+        <v>23862.95974731445</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24359.76058959961</v>
+        <v>23862.95974731445</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>214.4299926757812</v>
+        <v>210.6000061035156</v>
       </c>
       <c r="F6" t="n">
-        <v>37525.24871826172</v>
+        <v>36855.00106811523</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>37525.24871826172</v>
+        <v>36855.00106811523</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.1899995803833</v>
+        <v>14.55000019073486</v>
       </c>
       <c r="F7" t="n">
-        <v>38400.31893920898</v>
+        <v>36782.40048217773</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>38400.31893920898</v>
+        <v>36782.40048217773</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4074.89990234375</v>
+        <v>4017.300048828125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009333606632977443</v>
+        <v>-0.03125222613701806</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01307705861748176</v>
+        <v>-0.001391994245833139</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58.63999938964844</v>
+        <v>57.15999984741211</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.003314348565625846</v>
+        <v>-0.04763493413245434</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00799312692197951</v>
+        <v>-0.03895625698014804</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.26</v>
+        <v>0.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>No Convencente / Correctivo</t>
+          <t>Sí (Posible Onda de Impulso)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>82875.30710296631</v>
+        <v>82257.51559600829</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+52.3%</t>
+          <t>+53.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-50967.92468566895</v>
+        <v>-51324.99394836426</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+32.7%</t>
+          <t>+32.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-31907.38241729736</v>
+        <v>-30932.52164764404</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.23</v>
+        <v>42.55</v>
       </c>
       <c r="C2" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="D2" t="n">
-        <v>41.48</v>
+        <v>40.87</v>
       </c>
       <c r="E2" t="n">
-        <v>48.48</v>
+        <v>47.6</v>
       </c>
       <c r="F2" t="n">
-        <v>966.91</v>
+        <v>928.9299999999999</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.55</v>
+        <v>14.15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="D3" t="n">
-        <v>13.76</v>
+        <v>13.37</v>
       </c>
       <c r="E3" t="n">
-        <v>16.92</v>
+        <v>16.49</v>
       </c>
       <c r="F3" t="n">
-        <v>1995.28</v>
+        <v>1975.45</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>210.6</v>
+        <v>214.37</v>
       </c>
       <c r="C5" t="n">
-        <v>6.35</v>
+        <v>6.24</v>
       </c>
       <c r="D5" t="n">
-        <v>204.25</v>
+        <v>208.13</v>
       </c>
       <c r="E5" t="n">
-        <v>229.65</v>
+        <v>233.08</v>
       </c>
       <c r="F5" t="n">
-        <v>1111</v>
+        <v>1091.69</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>43.22999954223633</v>
+        <v>42.54999923706055</v>
       </c>
       <c r="F5" t="n">
-        <v>23862.95974731445</v>
+        <v>23487.59957885742</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>23862.95974731445</v>
+        <v>23487.59957885742</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210.6000061035156</v>
+        <v>214.3699951171875</v>
       </c>
       <c r="F6" t="n">
-        <v>36855.00106811523</v>
+        <v>37514.74914550781</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>36855.00106811523</v>
+        <v>37514.74914550781</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.55000019073486</v>
+        <v>14.14999961853027</v>
       </c>
       <c r="F7" t="n">
-        <v>36782.40048217773</v>
+        <v>35771.19903564453</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>36782.40048217773</v>
+        <v>35771.19903564453</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4017.300048828125</v>
+        <v>4142.5</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.03125222613701806</v>
+        <v>0.02369888302016654</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.001391994245833139</v>
+        <v>0.01823856408851854</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57.15999984741211</v>
+        <v>58.47999954223633</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.04763493413245434</v>
+        <v>0.01179970245651907</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.03895625698014804</v>
+        <v>-0.02671215056490028</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>82257.51559600829</v>
+        <v>85667.76017379761</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+53.0%</t>
+          <t>+52.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-51324.99394836426</v>
+        <v>-52963.99941253662</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+32.0%</t>
+          <t>+32.4%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-30932.52164764404</v>
+        <v>-32703.76076126099</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42.55</v>
+        <v>44.03</v>
       </c>
       <c r="C2" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="D2" t="n">
-        <v>40.87</v>
+        <v>42.3</v>
       </c>
       <c r="E2" t="n">
-        <v>47.6</v>
+        <v>49.21</v>
       </c>
       <c r="F2" t="n">
-        <v>928.9299999999999</v>
+        <v>953.1900000000001</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.15</v>
+        <v>14.93</v>
       </c>
       <c r="C3" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="D3" t="n">
-        <v>13.37</v>
+        <v>14.13</v>
       </c>
       <c r="E3" t="n">
-        <v>16.49</v>
+        <v>17.34</v>
       </c>
       <c r="F3" t="n">
-        <v>1975.45</v>
+        <v>2032.33</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>214.37</v>
+        <v>221.36</v>
       </c>
       <c r="C5" t="n">
-        <v>6.24</v>
+        <v>6.43</v>
       </c>
       <c r="D5" t="n">
-        <v>208.13</v>
+        <v>214.93</v>
       </c>
       <c r="E5" t="n">
-        <v>233.08</v>
+        <v>240.65</v>
       </c>
       <c r="F5" t="n">
-        <v>1091.69</v>
+        <v>1125.5</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>42.54999923706055</v>
+        <v>44.02999877929688</v>
       </c>
       <c r="F5" t="n">
-        <v>23487.59957885742</v>
+        <v>24304.55932617188</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>23487.59957885742</v>
+        <v>24304.55932617188</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>214.3699951171875</v>
+        <v>221.3600006103516</v>
       </c>
       <c r="F6" t="n">
-        <v>37514.74914550781</v>
+        <v>38738.00010681152</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>37514.74914550781</v>
+        <v>38738.00010681152</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.14999961853027</v>
+        <v>14.93000030517578</v>
       </c>
       <c r="F7" t="n">
-        <v>35771.19903564453</v>
+        <v>37743.04077148438</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>35771.19903564453</v>
+        <v>37743.04077148438</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4142.5</v>
+        <v>4169.2998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02369888302016654</v>
+        <v>0.02500238582692771</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01823856408851854</v>
+        <v>0.0137621530106935</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58.47999954223633</v>
+        <v>59.34000015258789</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01179970245651907</v>
+        <v>0.01166124425886617</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02671215056490028</v>
+        <v>-0.02148642663402522</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2</v>
+        <v>0.48</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -530,7 +530,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sí (Posible Onda de Impulso)</t>
+          <t>No Convencente / Correctivo</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85667.76017379761</v>
+        <v>82240.11776809693</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+52.6%</t>
+          <t>+53.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-52963.99941253662</v>
+        <v>-51382.41204376221</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+32.4%</t>
+          <t>+31.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-32703.76076126099</v>
+        <v>-30857.70572433472</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.03</v>
+        <v>43.11</v>
       </c>
       <c r="C2" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="D2" t="n">
-        <v>42.3</v>
+        <v>41.34</v>
       </c>
       <c r="E2" t="n">
-        <v>49.21</v>
+        <v>48.41</v>
       </c>
       <c r="F2" t="n">
-        <v>953.1900000000001</v>
+        <v>975.46</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.93</v>
+        <v>14.12</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>14.13</v>
+        <v>13.31</v>
       </c>
       <c r="E3" t="n">
-        <v>17.34</v>
+        <v>16.56</v>
       </c>
       <c r="F3" t="n">
-        <v>2032.33</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>221.36</v>
+        <v>212.92</v>
       </c>
       <c r="C5" t="n">
-        <v>6.43</v>
+        <v>6.74</v>
       </c>
       <c r="D5" t="n">
-        <v>214.93</v>
+        <v>206.18</v>
       </c>
       <c r="E5" t="n">
-        <v>240.65</v>
+        <v>233.15</v>
       </c>
       <c r="F5" t="n">
-        <v>1125.5</v>
+        <v>1180.25</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.02999877929688</v>
+        <v>43.11000061035156</v>
       </c>
       <c r="F5" t="n">
-        <v>24304.55932617188</v>
+        <v>23796.72033691406</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24304.55932617188</v>
+        <v>23796.72033691406</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221.3600006103516</v>
+        <v>212.9199981689453</v>
       </c>
       <c r="F6" t="n">
-        <v>38738.00010681152</v>
+        <v>37260.99967956543</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>38738.00010681152</v>
+        <v>37260.99967956543</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.93000030517578</v>
+        <v>14.11999988555908</v>
       </c>
       <c r="F7" t="n">
-        <v>37743.04077148438</v>
+        <v>35695.35971069336</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>37743.04077148438</v>
+        <v>35695.35971069336</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4169.2998046875</v>
+        <v>4098.60009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02500238582692771</v>
+        <v>0.007621201508442921</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0137621530106935</v>
+        <v>-0.00342842827987333</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.34000015258789</v>
+        <v>57.77500152587891</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01166124425886617</v>
+        <v>-0.01501972058590362</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02148642663402522</v>
+        <v>-0.04729317409941214</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.48</v>
+        <v>-0.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>82240.11776809693</v>
+        <v>83450.02471466064</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+53.1%</t>
+          <t>+52.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-51382.41204376221</v>
+        <v>-51879.8089263916</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+31.9%</t>
+          <t>+32.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-30857.70572433472</v>
+        <v>-31570.21578826904</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.11</v>
+        <v>43.73</v>
       </c>
       <c r="C2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="D2" t="n">
-        <v>41.34</v>
+        <v>41.97</v>
       </c>
       <c r="E2" t="n">
-        <v>48.41</v>
+        <v>49.02</v>
       </c>
       <c r="F2" t="n">
-        <v>975.46</v>
+        <v>972.51</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.12</v>
+        <v>14.43</v>
       </c>
       <c r="C3" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>13.31</v>
+        <v>13.62</v>
       </c>
       <c r="E3" t="n">
-        <v>16.56</v>
+        <v>16.86</v>
       </c>
       <c r="F3" t="n">
-        <v>2054</v>
+        <v>2044.07</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>212.92</v>
+        <v>214.62</v>
       </c>
       <c r="C5" t="n">
-        <v>6.74</v>
+        <v>6.64</v>
       </c>
       <c r="D5" t="n">
-        <v>206.18</v>
+        <v>207.98</v>
       </c>
       <c r="E5" t="n">
-        <v>233.15</v>
+        <v>234.55</v>
       </c>
       <c r="F5" t="n">
-        <v>1180.25</v>
+        <v>1162.5</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>43.11000061035156</v>
+        <v>43.72999954223633</v>
       </c>
       <c r="F5" t="n">
-        <v>23796.72033691406</v>
+        <v>24138.95974731445</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>23796.72033691406</v>
+        <v>24138.95974731445</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>212.9199981689453</v>
+        <v>214.6199951171875</v>
       </c>
       <c r="F6" t="n">
-        <v>37260.99967956543</v>
+        <v>37558.49914550781</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>37260.99967956543</v>
+        <v>37558.49914550781</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.11999988555908</v>
+        <v>14.43000030517578</v>
       </c>
       <c r="F7" t="n">
-        <v>35695.35971069336</v>
+        <v>36479.04077148438</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>35695.35971069336</v>
+        <v>36479.04077148438</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4098.60009765625</v>
+        <v>4108.60009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007621201508442921</v>
+        <v>0.01791245644612482</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.00342842827987333</v>
+        <v>-0.01119106613730658</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57.77500152587891</v>
+        <v>58.34999847412109</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.01501972058590362</v>
+        <v>0.01839564739963628</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04729317409941214</v>
+        <v>-0.05765503553607465</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.1</v>
+        <v>-0.43</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83450.02471466064</v>
+        <v>86697.22975692748</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+52.8%</t>
+          <t>+51.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-51879.8089263916</v>
+        <v>-52891.14593353272</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+32.2%</t>
+          <t>+33.1%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-31570.21578826904</v>
+        <v>-33806.08382339477</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.73</v>
+        <v>44.91</v>
       </c>
       <c r="C2" t="n">
         <v>1.76</v>
       </c>
       <c r="D2" t="n">
-        <v>41.97</v>
+        <v>43.15</v>
       </c>
       <c r="E2" t="n">
-        <v>49.02</v>
+        <v>50.19</v>
       </c>
       <c r="F2" t="n">
-        <v>972.51</v>
+        <v>970.73</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.43</v>
+        <v>15.39</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="D3" t="n">
-        <v>13.62</v>
+        <v>14.56</v>
       </c>
       <c r="E3" t="n">
-        <v>16.86</v>
+        <v>17.89</v>
       </c>
       <c r="F3" t="n">
-        <v>2044.07</v>
+        <v>2108.17</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>214.62</v>
+        <v>218.86</v>
       </c>
       <c r="C5" t="n">
-        <v>6.64</v>
+        <v>6.79</v>
       </c>
       <c r="D5" t="n">
-        <v>207.98</v>
+        <v>212.07</v>
       </c>
       <c r="E5" t="n">
-        <v>234.55</v>
+        <v>239.24</v>
       </c>
       <c r="F5" t="n">
-        <v>1162.5</v>
+        <v>1188.56</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>43.72999954223633</v>
+        <v>44.90999984741211</v>
       </c>
       <c r="F5" t="n">
-        <v>24138.95974731445</v>
+        <v>24790.31991577148</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24138.95974731445</v>
+        <v>24790.31991577148</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>214.6199951171875</v>
+        <v>218.8600006103516</v>
       </c>
       <c r="F6" t="n">
-        <v>37558.49914550781</v>
+        <v>38300.50010681152</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>37558.49914550781</v>
+        <v>38300.50010681152</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14.43000030517578</v>
+        <v>15.39000034332275</v>
       </c>
       <c r="F7" t="n">
-        <v>36479.04077148438</v>
+        <v>38905.92086791992</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>36479.04077148438</v>
+        <v>38905.92086791992</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4108.60009765625</v>
+        <v>4133.7001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01791245644612482</v>
+        <v>0.02453720111501001</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01119106613730658</v>
+        <v>-0.002798255837100916</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>58.34999847412109</v>
+        <v>59.70999908447266</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01839564739963628</v>
+        <v>0.03192022804193817</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.05765503553607465</v>
+        <v>-0.02003907167581476</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.43</v>
+        <v>-0.72</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -530,7 +530,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>No Convencente / Correctivo</t>
+          <t>Sí (Posible Onda de Impulso)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86697.22975692748</v>
+        <v>91874.67570877075</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.9%</t>
+          <t>+51.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-52891.14593353272</v>
+        <v>-55465.94608306885</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.1%</t>
+          <t>+33.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-33806.08382339477</v>
+        <v>-36408.7296257019</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44.91</v>
+        <v>48.24</v>
       </c>
       <c r="C2" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="D2" t="n">
-        <v>43.15</v>
+        <v>46.36</v>
       </c>
       <c r="E2" t="n">
-        <v>50.19</v>
+        <v>53.88</v>
       </c>
       <c r="F2" t="n">
-        <v>970.73</v>
+        <v>1038.15</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.39</v>
+        <v>16.54</v>
       </c>
       <c r="C3" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="D3" t="n">
-        <v>14.56</v>
+        <v>15.67</v>
       </c>
       <c r="E3" t="n">
-        <v>17.89</v>
+        <v>19.15</v>
       </c>
       <c r="F3" t="n">
-        <v>2108.17</v>
+        <v>2199.36</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>218.86</v>
+        <v>226.55</v>
       </c>
       <c r="C5" t="n">
-        <v>6.79</v>
+        <v>7.3</v>
       </c>
       <c r="D5" t="n">
-        <v>212.07</v>
+        <v>224.95</v>
       </c>
       <c r="E5" t="n">
-        <v>239.24</v>
+        <v>248.45</v>
       </c>
       <c r="F5" t="n">
-        <v>1188.56</v>
+        <v>279.65</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44.90999984741211</v>
+        <v>48.2400016784668</v>
       </c>
       <c r="F5" t="n">
-        <v>24790.31991577148</v>
+        <v>26628.48092651367</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>24790.31991577148</v>
+        <v>26628.48092651367</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>218.8600006103516</v>
+        <v>226.5500030517578</v>
       </c>
       <c r="F6" t="n">
-        <v>38300.50010681152</v>
+        <v>39646.25053405762</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>38300.50010681152</v>
+        <v>39646.25053405762</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.39000034332275</v>
+        <v>16.54000091552734</v>
       </c>
       <c r="F7" t="n">
-        <v>38905.92086791992</v>
+        <v>41813.12231445312</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>38905.92086791992</v>
+        <v>41813.12231445312</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4133.7001953125</v>
+        <v>4307.60009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02453720111501001</v>
+        <v>0.0506085205379776</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.002798255837100916</v>
+        <v>0.05814444004781949</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59.70999908447266</v>
+        <v>62.22999954223633</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03192022804193817</v>
+        <v>0.05806343611774789</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.02003907167581476</v>
+        <v>0.06990574883074707</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.72</v>
+        <v>-0.79</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>91874.67570877075</v>
+        <v>90998.17717666626</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.3%</t>
+          <t>+52.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-55465.94608306885</v>
+        <v>-56256.93199615479</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.7%</t>
+          <t>+32.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-36408.7296257019</v>
+        <v>-34741.24518051148</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.24</v>
+        <v>48.05</v>
       </c>
       <c r="C2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="D2" t="n">
-        <v>46.36</v>
+        <v>46.17</v>
       </c>
       <c r="E2" t="n">
-        <v>53.88</v>
+        <v>53.67</v>
       </c>
       <c r="F2" t="n">
-        <v>1038.15</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.54</v>
+        <v>15.86</v>
       </c>
       <c r="C3" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="D3" t="n">
-        <v>15.67</v>
+        <v>14.97</v>
       </c>
       <c r="E3" t="n">
-        <v>19.15</v>
+        <v>18.51</v>
       </c>
       <c r="F3" t="n">
-        <v>2199.36</v>
+        <v>2237.28</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>226.55</v>
+        <v>231.08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.3</v>
+        <v>7.42</v>
       </c>
       <c r="D5" t="n">
-        <v>224.95</v>
+        <v>224.66</v>
       </c>
       <c r="E5" t="n">
-        <v>248.45</v>
+        <v>253.33</v>
       </c>
       <c r="F5" t="n">
-        <v>279.65</v>
+        <v>1122.95</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>48.2400016784668</v>
+        <v>48.04999923706055</v>
       </c>
       <c r="F5" t="n">
-        <v>26628.48092651367</v>
+        <v>26523.59957885742</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>26628.48092651367</v>
+        <v>26523.59957885742</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>226.5500030517578</v>
+        <v>231.0800018310547</v>
       </c>
       <c r="F6" t="n">
-        <v>39646.25053405762</v>
+        <v>40439.00032043457</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>39646.25053405762</v>
+        <v>40439.00032043457</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.54000091552734</v>
+        <v>15.85999965667725</v>
       </c>
       <c r="F7" t="n">
-        <v>41813.12231445312</v>
+        <v>40094.07913208008</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>41813.12231445312</v>
+        <v>40094.07913208008</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4307.60009765625</v>
+        <v>4302.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0506085205379776</v>
+        <v>0.06255706171208719</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05814444004781949</v>
+        <v>0.04159197226208877</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>62.22999954223633</v>
+        <v>61.90499877929688</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05806343611774789</v>
+        <v>0.07490752384475607</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06990574883074707</v>
+        <v>0.0252906765531129</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.79</v>
+        <v>-1.74</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CERRAR ARBITRAJE (Media alcanzada)</t>
+          <t>MANTENER</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>90998.17717666626</v>
+        <v>95738.8919845581</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+52.5%</t>
+          <t>+52.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-56256.93199615479</v>
+        <v>-58773.79054870606</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+32.5%</t>
+          <t>+32.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-34741.24518051148</v>
+        <v>-36965.10143585205</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.05</v>
+        <v>51.22</v>
       </c>
       <c r="C2" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="D2" t="n">
-        <v>46.17</v>
+        <v>49.16</v>
       </c>
       <c r="E2" t="n">
-        <v>53.67</v>
+        <v>57.39</v>
       </c>
       <c r="F2" t="n">
-        <v>1035</v>
+        <v>1135.54</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.86</v>
+        <v>16.85</v>
       </c>
       <c r="C3" t="n">
-        <v>0.89</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>14.97</v>
+        <v>15.91</v>
       </c>
       <c r="E3" t="n">
-        <v>18.51</v>
+        <v>19.66</v>
       </c>
       <c r="F3" t="n">
-        <v>2237.28</v>
+        <v>2370.9</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>231.08</v>
+        <v>238.65</v>
       </c>
       <c r="C5" t="n">
-        <v>7.42</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>224.66</v>
+        <v>225.09</v>
       </c>
       <c r="E5" t="n">
-        <v>253.33</v>
+        <v>263.49</v>
       </c>
       <c r="F5" t="n">
-        <v>1122.95</v>
+        <v>2372.38</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>48.04999923706055</v>
+        <v>51.22000122070312</v>
       </c>
       <c r="F5" t="n">
-        <v>26523.59957885742</v>
+        <v>28273.44067382812</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>26523.59957885742</v>
+        <v>28273.44067382812</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>231.0800018310547</v>
+        <v>238.6499938964844</v>
       </c>
       <c r="F6" t="n">
-        <v>40439.00032043457</v>
+        <v>41763.74893188477</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>40439.00032043457</v>
+        <v>41763.74893188477</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.85999965667725</v>
+        <v>16.85000038146973</v>
       </c>
       <c r="F7" t="n">
-        <v>40094.07913208008</v>
+        <v>42596.80096435547</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>40094.07913208008</v>
+        <v>42596.80096435547</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4302.39990234375</v>
+        <v>4401.2998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06255706171208719</v>
+        <v>0.08698221790938554</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04159197226208877</v>
+        <v>0.06553520085007691</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>61.90499877929688</v>
+        <v>63.79999923706055</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07490752384475607</v>
+        <v>0.1078119788953336</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0252906765531129</v>
+        <v>0.05667628901933508</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.74</v>
+        <v>-1.53</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HOLD / CASH (Sin Tendencia)</t>
+          <t>LIGERAMENTE ALCISTA (Parcial)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>95738.8919845581</v>
+        <v>97849.87209472655</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+52.2%</t>
+          <t>+51.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-58773.79054870606</v>
+        <v>-59239.34885253907</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+32.8%</t>
+          <t>+33.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-36965.10143585205</v>
+        <v>-38610.5232421875</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51.22</v>
+        <v>51.8</v>
       </c>
       <c r="C2" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="D2" t="n">
-        <v>49.16</v>
+        <v>49.78</v>
       </c>
       <c r="E2" t="n">
-        <v>57.39</v>
+        <v>57.87</v>
       </c>
       <c r="F2" t="n">
-        <v>1135.54</v>
+        <v>1117.41</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.85</v>
+        <v>17.55</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="D3" t="n">
-        <v>15.91</v>
+        <v>16.63</v>
       </c>
       <c r="E3" t="n">
-        <v>19.66</v>
+        <v>20.32</v>
       </c>
       <c r="F3" t="n">
-        <v>2370.9</v>
+        <v>2336.59</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>238.65</v>
+        <v>240.9</v>
       </c>
       <c r="C5" t="n">
-        <v>8.279999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>225.09</v>
+        <v>225.5</v>
       </c>
       <c r="E5" t="n">
-        <v>263.49</v>
+        <v>265.24</v>
       </c>
       <c r="F5" t="n">
-        <v>2372.38</v>
+        <v>2694.56</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>51.22000122070312</v>
+        <v>51.79999923706055</v>
       </c>
       <c r="F5" t="n">
-        <v>28273.44067382812</v>
+        <v>28593.59957885742</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28273.44067382812</v>
+        <v>28593.59957885742</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>238.6499938964844</v>
+        <v>240.8999938964844</v>
       </c>
       <c r="F6" t="n">
-        <v>41763.74893188477</v>
+        <v>42157.49893188477</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>41763.74893188477</v>
+        <v>42157.49893188477</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16.85000038146973</v>
+        <v>17.54999923706055</v>
       </c>
       <c r="F7" t="n">
-        <v>42596.80096435547</v>
+        <v>44366.39807128906</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>42596.80096435547</v>
+        <v>44366.39807128906</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4401.2998046875</v>
+        <v>4452.7001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08698221790938554</v>
+        <v>0.1038749161347254</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06553520085007691</v>
+        <v>0.08493947256679402</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63.79999923706055</v>
+        <v>65.91500091552734</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1078119788953336</v>
+        <v>0.1430280944876974</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05667628901933508</v>
+        <v>0.1020917086188344</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.53</v>
+        <v>-1.55</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>97849.87209472655</v>
+        <v>98272.63273849487</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.5%</t>
+          <t>+51.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-59239.34885253907</v>
+        <v>-59156.095262146</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.5%</t>
+          <t>+33.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-38610.5232421875</v>
+        <v>-39116.53747634888</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51.8</v>
+        <v>51.79</v>
       </c>
       <c r="C2" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="D2" t="n">
-        <v>49.78</v>
+        <v>49.83</v>
       </c>
       <c r="E2" t="n">
-        <v>57.87</v>
+        <v>57.66</v>
       </c>
       <c r="F2" t="n">
-        <v>1117.41</v>
+        <v>1080.93</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.55</v>
+        <v>17.76</v>
       </c>
       <c r="C3" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>16.63</v>
+        <v>16.86</v>
       </c>
       <c r="E3" t="n">
-        <v>20.32</v>
+        <v>20.45</v>
       </c>
       <c r="F3" t="n">
-        <v>2336.59</v>
+        <v>2268.95</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>240.9</v>
+        <v>240.74</v>
       </c>
       <c r="C5" t="n">
-        <v>8.119999999999999</v>
+        <v>7.76</v>
       </c>
       <c r="D5" t="n">
-        <v>225.5</v>
+        <v>226.4</v>
       </c>
       <c r="E5" t="n">
-        <v>265.24</v>
+        <v>264.01</v>
       </c>
       <c r="F5" t="n">
-        <v>2694.56</v>
+        <v>2509.38</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>51.79999923706055</v>
+        <v>51.79000091552734</v>
       </c>
       <c r="F5" t="n">
-        <v>28593.59957885742</v>
+        <v>28588.08050537109</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28593.59957885742</v>
+        <v>28588.08050537109</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>240.8999938964844</v>
+        <v>240.7400054931641</v>
       </c>
       <c r="F6" t="n">
-        <v>42157.49893188477</v>
+        <v>42129.50096130371</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>42157.49893188477</v>
+        <v>42129.50096130371</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.54999923706055</v>
+        <v>17.76000022888184</v>
       </c>
       <c r="F7" t="n">
-        <v>44366.39807128906</v>
+        <v>44897.28057861328</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>44366.39807128906</v>
+        <v>44897.28057861328</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4452.7001953125</v>
+        <v>4434.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1038749161347254</v>
+        <v>0.0827757992097411</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08493947256679402</v>
+        <v>0.1094320496231549</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.91500091552734</v>
+        <v>65.00499725341797</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1430280944876974</v>
+        <v>0.08240637934057116</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1020917086188344</v>
+        <v>0.1278932318940045</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Módulos Quant" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ajuste Barbell Strategy" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Control de Riesgo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Posiciones Ledger" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Rendimientos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Módulos Quant" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ajuste Barbell Strategy" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de Riesgo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Posiciones Ledger" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rendimientos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.55</v>
+        <v>-1.18</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>98272.63273849487</v>
+        <v>94737.42124786376</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+51.2%</t>
+          <t>+49.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-59156.095262146</v>
+        <v>-55488.77189025879</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+33.8%</t>
+          <t>+35.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-39116.53747634888</v>
+        <v>-39248.64935760498</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51.79</v>
+        <v>47.3</v>
       </c>
       <c r="C2" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="D2" t="n">
-        <v>49.83</v>
+        <v>45.04</v>
       </c>
       <c r="E2" t="n">
-        <v>57.66</v>
+        <v>54.08</v>
       </c>
       <c r="F2" t="n">
-        <v>1080.93</v>
+        <v>1247.43</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.76</v>
+        <v>17.73</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="D3" t="n">
-        <v>16.86</v>
+        <v>16.81</v>
       </c>
       <c r="E3" t="n">
-        <v>20.45</v>
+        <v>20.48</v>
       </c>
       <c r="F3" t="n">
-        <v>2268.95</v>
+        <v>2313.12</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>240.74</v>
+        <v>231.57</v>
       </c>
       <c r="C5" t="n">
-        <v>7.76</v>
+        <v>8.25</v>
       </c>
       <c r="D5" t="n">
-        <v>226.4</v>
+        <v>225.16</v>
       </c>
       <c r="E5" t="n">
-        <v>264.01</v>
+        <v>256.32</v>
       </c>
       <c r="F5" t="n">
-        <v>2509.38</v>
+        <v>1121.5</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>51.79000091552734</v>
+        <v>47.29999923706055</v>
       </c>
       <c r="F5" t="n">
-        <v>28588.08050537109</v>
+        <v>26109.59957885742</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28588.08050537109</v>
+        <v>26109.59957885742</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>240.7400054931641</v>
+        <v>231.5700073242188</v>
       </c>
       <c r="F6" t="n">
-        <v>42129.50096130371</v>
+        <v>40524.75128173828</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>42129.50096130371</v>
+        <v>40524.75128173828</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.76000022888184</v>
+        <v>17.72999954223633</v>
       </c>
       <c r="F7" t="n">
-        <v>44897.28057861328</v>
+        <v>44821.43884277344</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>44897.28057861328</v>
+        <v>44821.43884277344</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4434.39990234375</v>
+        <v>4417.7001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0827757992097411</v>
+        <v>0.04141918795674204</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1094320496231549</v>
+        <v>0.09240855472613752</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.00499725341797</v>
+        <v>64.71499633789062</v>
       </c>
       <c r="C3" t="n">
-        <v>0.08240637934057116</v>
+        <v>0.05332113487850543</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1278932318940045</v>
+        <v>0.1331639931056243</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.18</v>
+        <v>-1.43</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>94737.42124786376</v>
+        <v>96561.65944290161</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+49.8%</t>
+          <t>+49.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-55488.77189025879</v>
+        <v>-55802.39493560791</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+35.2%</t>
+          <t>+35.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-39248.64935760498</v>
+        <v>-40759.2645072937</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47.3</v>
+        <v>47.42</v>
       </c>
       <c r="C2" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="D2" t="n">
-        <v>45.04</v>
+        <v>45.17</v>
       </c>
       <c r="E2" t="n">
-        <v>54.08</v>
+        <v>54.18</v>
       </c>
       <c r="F2" t="n">
-        <v>1247.43</v>
+        <v>1244.37</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.73</v>
+        <v>18.37</v>
       </c>
       <c r="C3" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="D3" t="n">
-        <v>16.81</v>
+        <v>16.46</v>
       </c>
       <c r="E3" t="n">
-        <v>20.48</v>
+        <v>21.21</v>
       </c>
       <c r="F3" t="n">
-        <v>2313.12</v>
+        <v>4818.55</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>231.57</v>
+        <v>234.21</v>
       </c>
       <c r="C5" t="n">
-        <v>8.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>225.16</v>
+        <v>225.29</v>
       </c>
       <c r="E5" t="n">
-        <v>256.32</v>
+        <v>258.82</v>
       </c>
       <c r="F5" t="n">
-        <v>1121.5</v>
+        <v>1561.78</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>47.29999923706055</v>
+        <v>47.41999816894531</v>
       </c>
       <c r="F5" t="n">
-        <v>26109.59957885742</v>
+        <v>26175.83898925781</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>26109.59957885742</v>
+        <v>26175.83898925781</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>231.5700073242188</v>
+        <v>234.2100067138672</v>
       </c>
       <c r="F6" t="n">
-        <v>40524.75128173828</v>
+        <v>40986.75117492676</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>40524.75128173828</v>
+        <v>40986.75117492676</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.72999954223633</v>
+        <v>18.3700008392334</v>
       </c>
       <c r="F7" t="n">
-        <v>44821.43884277344</v>
+        <v>46439.36212158203</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>44821.43884277344</v>
+        <v>46439.36212158203</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4417.7001953125</v>
+        <v>4432</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04141918795674204</v>
+        <v>0.01609431850518628</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09240855472613752</v>
+        <v>0.1044932474220186</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64.71499633789062</v>
+        <v>64.82499694824219</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05332113487850543</v>
+        <v>-0.004316128271694808</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1331639931056243</v>
+        <v>0.1568042940702961</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.43</v>
+        <v>-1.61</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>96561.65944290161</v>
+        <v>98499.42726745605</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+49.1%</t>
+          <t>+48.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-55802.39493560791</v>
+        <v>-56716.55199584962</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+35.9%</t>
+          <t>+36.1%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-40759.2645072937</v>
+        <v>-41782.87527160645</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47.42</v>
+        <v>48.11</v>
       </c>
       <c r="C2" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="D2" t="n">
-        <v>45.17</v>
+        <v>45.88</v>
       </c>
       <c r="E2" t="n">
-        <v>54.18</v>
+        <v>54.81</v>
       </c>
       <c r="F2" t="n">
-        <v>1244.37</v>
+        <v>1233.72</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.37</v>
+        <v>18.82</v>
       </c>
       <c r="C3" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="D3" t="n">
-        <v>16.46</v>
+        <v>16.73</v>
       </c>
       <c r="E3" t="n">
-        <v>21.21</v>
+        <v>21.62</v>
       </c>
       <c r="F3" t="n">
-        <v>4818.55</v>
+        <v>5284.42</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>234.21</v>
+        <v>238.56</v>
       </c>
       <c r="C5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>225.29</v>
+        <v>225.08</v>
       </c>
       <c r="E5" t="n">
-        <v>258.82</v>
+        <v>263.41</v>
       </c>
       <c r="F5" t="n">
-        <v>1561.78</v>
+        <v>2359.06</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>47.41999816894531</v>
+        <v>48.11000061035156</v>
       </c>
       <c r="F5" t="n">
-        <v>26175.83898925781</v>
+        <v>26556.72033691406</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>26175.83898925781</v>
+        <v>26556.72033691406</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>234.2100067138672</v>
+        <v>238.5599975585938</v>
       </c>
       <c r="F6" t="n">
-        <v>40986.75117492676</v>
+        <v>41747.99957275391</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>40986.75117492676</v>
+        <v>41747.99957275391</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.3700008392334</v>
+        <v>18.81999969482422</v>
       </c>
       <c r="F7" t="n">
-        <v>46439.36212158203</v>
+        <v>47576.95922851562</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>46439.36212158203</v>
+        <v>47576.95922851562</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4432</v>
+        <v>4471.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01609431850518628</v>
+        <v>0.02524189614065464</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1044932474220186</v>
+        <v>0.1144366528172058</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64.82499694824219</v>
+        <v>65.875</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.004316128271694808</v>
+        <v>0.01181146375481124</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1568042940702961</v>
+        <v>0.1755416345445293</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.61</v>
+        <v>-1.39</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>98499.42726745605</v>
+        <v>95088.48192214966</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+48.9%</t>
+          <t>+49.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-56716.55199584962</v>
+        <v>-55304.32010650635</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+36.1%</t>
+          <t>+35.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-41782.87527160645</v>
+        <v>-39784.16181564331</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48.11</v>
+        <v>46.6</v>
       </c>
       <c r="C2" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="D2" t="n">
-        <v>45.88</v>
+        <v>44.4</v>
       </c>
       <c r="E2" t="n">
-        <v>54.81</v>
+        <v>53.2</v>
       </c>
       <c r="F2" t="n">
-        <v>1233.72</v>
+        <v>1213.93</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.82</v>
+        <v>17.95</v>
       </c>
       <c r="C3" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>16.73</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="n">
-        <v>21.62</v>
+        <v>20.78</v>
       </c>
       <c r="F3" t="n">
-        <v>5284.42</v>
+        <v>3152.78</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>238.56</v>
+        <v>232.96</v>
       </c>
       <c r="C5" t="n">
-        <v>8.279999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="D5" t="n">
-        <v>225.08</v>
+        <v>226.1</v>
       </c>
       <c r="E5" t="n">
-        <v>263.41</v>
+        <v>256.59</v>
       </c>
       <c r="F5" t="n">
-        <v>2359.06</v>
+        <v>1201.32</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>48.11000061035156</v>
+        <v>46.59999847412109</v>
       </c>
       <c r="F5" t="n">
-        <v>26556.72033691406</v>
+        <v>25723.19915771484</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>26556.72033691406</v>
+        <v>25723.19915771484</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>238.5599975585938</v>
+        <v>232.9600067138672</v>
       </c>
       <c r="F6" t="n">
-        <v>41747.99957275391</v>
+        <v>40768.00117492676</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>41747.99957275391</v>
+        <v>40768.00117492676</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18.81999969482422</v>
+        <v>17.95000076293945</v>
       </c>
       <c r="F7" t="n">
-        <v>47576.95922851562</v>
+        <v>45377.60192871094</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>47576.95922851562</v>
+        <v>45377.60192871094</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4471.89990234375</v>
+        <v>4391.7998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02524189614065464</v>
+        <v>0.00200771268252331</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1144366528172058</v>
+        <v>0.09512997810995594</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.875</v>
+        <v>63.47499847412109</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01181146375481124</v>
+        <v>-0.0199786745874444</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1755416345445293</v>
+        <v>0.1174782675678259</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,11 +460,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1.39</v>
+        <v>-2.86</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MANTENER</t>
+          <t>COMPRAR SPREAD (Largo GLD / Corto GDX)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>95088.48192214966</v>
+        <v>107497.2056640625</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+49.4%</t>
+          <t>+48.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-55304.32010650635</v>
+        <v>-61187.61147460937</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+35.6%</t>
+          <t>+36.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-39784.16181564331</v>
+        <v>-46309.59418945313</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46.6</v>
+        <v>51.92</v>
       </c>
       <c r="C2" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="D2" t="n">
-        <v>44.4</v>
+        <v>51.02</v>
       </c>
       <c r="E2" t="n">
-        <v>53.2</v>
+        <v>59.16</v>
       </c>
       <c r="F2" t="n">
-        <v>1213.93</v>
+        <v>494.43</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.95</v>
+        <v>20.82</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.51</v>
       </c>
       <c r="E3" t="n">
-        <v>20.78</v>
+        <v>24.03</v>
       </c>
       <c r="F3" t="n">
-        <v>3152.78</v>
+        <v>5843.5</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>232.96</v>
+        <v>258.14</v>
       </c>
       <c r="C5" t="n">
-        <v>7.88</v>
+        <v>9.1</v>
       </c>
       <c r="D5" t="n">
-        <v>226.1</v>
+        <v>236</v>
       </c>
       <c r="E5" t="n">
-        <v>256.59</v>
+        <v>285.44</v>
       </c>
       <c r="F5" t="n">
-        <v>1201.32</v>
+        <v>3874.66</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>46.59999847412109</v>
+        <v>51.91999816894531</v>
       </c>
       <c r="F5" t="n">
-        <v>25723.19915771484</v>
+        <v>28659.83898925781</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>25723.19915771484</v>
+        <v>28659.83898925781</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>232.9600067138672</v>
+        <v>258.1400146484375</v>
       </c>
       <c r="F6" t="n">
-        <v>40768.00117492676</v>
+        <v>45174.50256347656</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>40768.00117492676</v>
+        <v>45174.50256347656</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>17.95000076293945</v>
+        <v>20.81999969482422</v>
       </c>
       <c r="F7" t="n">
-        <v>45377.60192871094</v>
+        <v>52632.95922851562</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>45377.60192871094</v>
+        <v>52632.95922851562</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4391.7998046875</v>
+        <v>4574.39990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00200771268252331</v>
+        <v>0.04830869006550897</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09512997810995594</v>
+        <v>0.1030890569020932</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63.47499847412109</v>
+        <v>68.14499664306641</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0199786745874444</v>
+        <v>0.05043693815642736</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1174782675678259</v>
+        <v>0.135390384705466</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.86</v>
+        <v>-2.88</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>107497.2056640625</v>
+        <v>108952.4019287109</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+48.4%</t>
+          <t>+49.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-61187.61147460937</v>
+        <v>-62981.20848388672</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+36.6%</t>
+          <t>+35.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-46309.59418945313</v>
+        <v>-45971.19344482422</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51.92</v>
+        <v>53.07</v>
       </c>
       <c r="C2" t="n">
         <v>2.41</v>
       </c>
       <c r="D2" t="n">
-        <v>51.02</v>
+        <v>51.05</v>
       </c>
       <c r="E2" t="n">
-        <v>59.16</v>
+        <v>60.29</v>
       </c>
       <c r="F2" t="n">
-        <v>494.43</v>
+        <v>1117.42</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.82</v>
+        <v>20.72</v>
       </c>
       <c r="C3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="D3" t="n">
-        <v>18.51</v>
+        <v>18.74</v>
       </c>
       <c r="E3" t="n">
-        <v>24.03</v>
+        <v>23.97</v>
       </c>
       <c r="F3" t="n">
-        <v>5843.5</v>
+        <v>5009.5</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>258.14</v>
+        <v>265.74</v>
       </c>
       <c r="C5" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>236</v>
+        <v>245.09</v>
       </c>
       <c r="E5" t="n">
-        <v>285.44</v>
+        <v>292.74</v>
       </c>
       <c r="F5" t="n">
-        <v>3874.66</v>
+        <v>3613.14</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>51.91999816894531</v>
+        <v>53.06999969482422</v>
       </c>
       <c r="F5" t="n">
-        <v>28659.83898925781</v>
+        <v>29294.63983154297</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28659.83898925781</v>
+        <v>29294.63983154297</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>258.1400146484375</v>
+        <v>265.739990234375</v>
       </c>
       <c r="F6" t="n">
-        <v>45174.50256347656</v>
+        <v>46504.49829101562</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>45174.50256347656</v>
+        <v>46504.49829101562</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20.81999969482422</v>
+        <v>20.71999931335449</v>
       </c>
       <c r="F7" t="n">
-        <v>52632.95922851562</v>
+        <v>52380.15826416016</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>52632.95922851562</v>
+        <v>52380.15826416016</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4574.39990234375</v>
+        <v>4661.60009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04830869006550897</v>
+        <v>0.06419509669928591</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1030890569020932</v>
+        <v>0.151979435861775</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>68.14499664306641</v>
+        <v>69.01000213623047</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05043693815642736</v>
+        <v>0.06188839844345706</v>
       </c>
       <c r="D3" t="n">
-        <v>0.135390384705466</v>
+        <v>0.193985981096531</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.88</v>
+        <v>-2.7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>108952.4019287109</v>
+        <v>109180.5539077759</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+49.1%</t>
+          <t>+49.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-62981.20848388672</v>
+        <v>-64031.74039611818</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+35.9%</t>
+          <t>+35.1%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-45971.19344482422</v>
+        <v>-45148.81351165772</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53.07</v>
+        <v>53.63</v>
       </c>
       <c r="C2" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="D2" t="n">
-        <v>51.05</v>
+        <v>51.13</v>
       </c>
       <c r="E2" t="n">
-        <v>60.29</v>
+        <v>60.74</v>
       </c>
       <c r="F2" t="n">
-        <v>1117.42</v>
+        <v>1377.73</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.72</v>
+        <v>20.4</v>
       </c>
       <c r="C3" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="D3" t="n">
-        <v>18.74</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="n">
-        <v>23.97</v>
+        <v>23.58</v>
       </c>
       <c r="F3" t="n">
-        <v>5009.5</v>
+        <v>4053.83</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>265.74</v>
+        <v>270.13</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>245.09</v>
+        <v>248.02</v>
       </c>
       <c r="E5" t="n">
-        <v>292.74</v>
+        <v>296.71</v>
       </c>
       <c r="F5" t="n">
-        <v>3613.14</v>
+        <v>3869.72</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53.06999969482422</v>
+        <v>53.63000106811523</v>
       </c>
       <c r="F5" t="n">
-        <v>29294.63983154297</v>
+        <v>29603.76058959961</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>29294.63983154297</v>
+        <v>29603.76058959961</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>265.739990234375</v>
+        <v>270.1300048828125</v>
       </c>
       <c r="F6" t="n">
-        <v>46504.49829101562</v>
+        <v>47272.75085449219</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>46504.49829101562</v>
+        <v>47272.75085449219</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20.71999931335449</v>
+        <v>20.39999961853027</v>
       </c>
       <c r="F7" t="n">
-        <v>52380.15826416016</v>
+        <v>51571.19903564453</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>52380.15826416016</v>
+        <v>51571.19903564453</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4661.60009765625</v>
+        <v>4715.2998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06419509669928591</v>
+        <v>0.06734121353446976</v>
       </c>
       <c r="D2" t="n">
-        <v>0.151979435861775</v>
+        <v>0.1592338704595013</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69.01000213623047</v>
+        <v>69.01999664306641</v>
       </c>
       <c r="C3" t="n">
-        <v>0.06188839844345706</v>
+        <v>0.04384377655305216</v>
       </c>
       <c r="D3" t="n">
-        <v>0.193985981096531</v>
+        <v>0.176691194862125</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.7</v>
+        <v>-3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>109180.5539077759</v>
+        <v>110814.0136001587</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+49.9%</t>
+          <t>+49.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-64031.74039611818</v>
+        <v>-64446.72479553223</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+35.1%</t>
+          <t>+35.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-45148.81351165772</v>
+        <v>-46367.28880462646</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53.63</v>
+        <v>54.21</v>
       </c>
       <c r="C2" t="n">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="D2" t="n">
-        <v>51.13</v>
+        <v>51.29</v>
       </c>
       <c r="E2" t="n">
-        <v>60.74</v>
+        <v>60.9</v>
       </c>
       <c r="F2" t="n">
-        <v>1377.73</v>
+        <v>1613.67</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.4</v>
+        <v>20.92</v>
       </c>
       <c r="C3" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>18.89</v>
       </c>
       <c r="E3" t="n">
-        <v>23.58</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
-        <v>4053.83</v>
+        <v>5138.16</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>270.13</v>
+        <v>271.77</v>
       </c>
       <c r="C5" t="n">
-        <v>8.859999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>248.02</v>
+        <v>251.62</v>
       </c>
       <c r="E5" t="n">
-        <v>296.71</v>
+        <v>297.14</v>
       </c>
       <c r="F5" t="n">
-        <v>3869.72</v>
+        <v>3526.23</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53.63000106811523</v>
+        <v>54.20999908447266</v>
       </c>
       <c r="F5" t="n">
-        <v>29603.76058959961</v>
+        <v>29923.91949462891</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>29603.76058959961</v>
+        <v>29923.91949462891</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>270.1300048828125</v>
+        <v>271.7699890136719</v>
       </c>
       <c r="F6" t="n">
-        <v>47272.75085449219</v>
+        <v>47559.74807739258</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47272.75085449219</v>
+        <v>47559.74807739258</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20.39999961853027</v>
+        <v>20.92000007629395</v>
       </c>
       <c r="F7" t="n">
-        <v>51571.19903564453</v>
+        <v>52885.76019287109</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>51571.19903564453</v>
+        <v>52885.76019287109</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4715.2998046875</v>
+        <v>4723.7998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06734121353446976</v>
+        <v>0.08195139823350894</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1592338704595013</v>
+        <v>0.159356928380783</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69.01999664306641</v>
+        <v>68.87999725341797</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04384377655305216</v>
+        <v>0.07724300863573319</v>
       </c>
       <c r="D3" t="n">
-        <v>0.176691194862125</v>
+        <v>0.1779996769328769</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-3</v>
+        <v>-2.7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>110814.0136001587</v>
+        <v>108945.4449142456</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+49.4%</t>
+          <t>+49.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-64446.72479553223</v>
+        <v>-63024.39856872558</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+35.6%</t>
+          <t>+35.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-46367.28880462646</v>
+        <v>-45921.04634552002</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54.21</v>
+        <v>52.63</v>
       </c>
       <c r="C2" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="D2" t="n">
-        <v>51.29</v>
+        <v>51.23</v>
       </c>
       <c r="E2" t="n">
-        <v>60.9</v>
+        <v>59.39</v>
       </c>
       <c r="F2" t="n">
-        <v>1613.67</v>
+        <v>772.0599999999999</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.92</v>
+        <v>20.7</v>
       </c>
       <c r="C3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="D3" t="n">
-        <v>18.89</v>
+        <v>18.92</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>23.73</v>
       </c>
       <c r="F3" t="n">
-        <v>5138.16</v>
+        <v>4504.26</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>271.77</v>
+        <v>267.37</v>
       </c>
       <c r="C5" t="n">
-        <v>8.460000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>251.62</v>
+        <v>251.4</v>
       </c>
       <c r="E5" t="n">
-        <v>297.14</v>
+        <v>293</v>
       </c>
       <c r="F5" t="n">
-        <v>3526.23</v>
+        <v>2794.24</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54.20999908447266</v>
+        <v>52.63000106811523</v>
       </c>
       <c r="F5" t="n">
-        <v>29923.91949462891</v>
+        <v>29051.76058959961</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>29923.91949462891</v>
+        <v>29051.76058959961</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>271.7699890136719</v>
+        <v>267.3699951171875</v>
       </c>
       <c r="F6" t="n">
-        <v>47559.74807739258</v>
+        <v>46789.74914550781</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47559.74807739258</v>
+        <v>46789.74914550781</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20.92000007629395</v>
+        <v>20.70000076293945</v>
       </c>
       <c r="F7" t="n">
-        <v>52885.76019287109</v>
+        <v>52329.60192871094</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>52885.76019287109</v>
+        <v>52329.60192871094</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4723.7998046875</v>
+        <v>4682.7998046875</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08195139823350894</v>
+        <v>0.04307923253679924</v>
       </c>
       <c r="D2" t="n">
-        <v>0.159356928380783</v>
+        <v>0.160171381720513</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>68.87999725341797</v>
+        <v>69.22499847412109</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07724300863573319</v>
+        <v>0.05310793885760101</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1779996769328769</v>
+        <v>0.208199468395158</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.7</v>
+        <v>-2.75</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>108945.4449142456</v>
+        <v>112160.5345062256</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+49.2%</t>
+          <t>+48.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-63024.39856872558</v>
+        <v>-64583.17223510742</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+35.8%</t>
+          <t>+36.1%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-45921.04634552002</v>
+        <v>-47577.36227111817</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.63</v>
+        <v>54.89</v>
       </c>
       <c r="C2" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="D2" t="n">
-        <v>51.23</v>
+        <v>51.42</v>
       </c>
       <c r="E2" t="n">
-        <v>59.39</v>
+        <v>61.42</v>
       </c>
       <c r="F2" t="n">
-        <v>772.0599999999999</v>
+        <v>1913.85</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.7</v>
+        <v>21.43</v>
       </c>
       <c r="C3" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
       <c r="D3" t="n">
-        <v>18.92</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>23.73</v>
+        <v>24.41</v>
       </c>
       <c r="F3" t="n">
-        <v>4504.26</v>
+        <v>6147.39</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>267.37</v>
+        <v>271.31</v>
       </c>
       <c r="C5" t="n">
-        <v>8.539999999999999</v>
+        <v>7.96</v>
       </c>
       <c r="D5" t="n">
-        <v>251.4</v>
+        <v>252.85</v>
       </c>
       <c r="E5" t="n">
-        <v>293</v>
+        <v>295.2</v>
       </c>
       <c r="F5" t="n">
-        <v>2794.24</v>
+        <v>3230.62</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.63000106811523</v>
+        <v>54.88999938964844</v>
       </c>
       <c r="F5" t="n">
-        <v>29051.76058959961</v>
+        <v>30299.27966308594</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>29051.76058959961</v>
+        <v>30299.27966308594</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>267.3699951171875</v>
+        <v>271.3099975585938</v>
       </c>
       <c r="F6" t="n">
-        <v>46789.74914550781</v>
+        <v>47479.24957275391</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>46789.74914550781</v>
+        <v>47479.24957275391</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20.70000076293945</v>
+        <v>21.43000030517578</v>
       </c>
       <c r="F7" t="n">
-        <v>52329.60192871094</v>
+        <v>54175.04077148438</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>52329.60192871094</v>
+        <v>54175.04077148438</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4682.7998046875</v>
+        <v>4626.7001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04307923253679924</v>
+        <v>0.000562292684271215</v>
       </c>
       <c r="D2" t="n">
-        <v>0.160171381720513</v>
+        <v>0.1284359125664449</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69.22499847412109</v>
+        <v>69.54000091552734</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05310793885760101</v>
+        <v>0.001065233264009091</v>
       </c>
       <c r="D3" t="n">
-        <v>0.208199468395158</v>
+        <v>0.1823514841322795</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.75</v>
+        <v>-2.88</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sí (Posible Onda de Impulso)</t>
+          <t>No Convencente / Correctivo</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>112160.5345062256</v>
+        <v>108190.4462402344</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+48.9%</t>
+          <t>+49.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-64583.17223510742</v>
+        <v>-63033.95225830078</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+36.1%</t>
+          <t>+35.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-47577.36227111817</v>
+        <v>-45156.49398193359</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54.89</v>
+        <v>52.87</v>
       </c>
       <c r="C2" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="D2" t="n">
-        <v>51.42</v>
+        <v>50.48</v>
       </c>
       <c r="E2" t="n">
-        <v>61.42</v>
+        <v>59.81</v>
       </c>
       <c r="F2" t="n">
-        <v>1913.85</v>
+        <v>1319.77</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.43</v>
+        <v>20.38</v>
       </c>
       <c r="C3" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="E3" t="n">
-        <v>24.41</v>
+        <v>23.49</v>
       </c>
       <c r="F3" t="n">
-        <v>6147.39</v>
+        <v>3242.07</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>271.31</v>
+        <v>266.16</v>
       </c>
       <c r="C5" t="n">
-        <v>7.96</v>
+        <v>8.24</v>
       </c>
       <c r="D5" t="n">
-        <v>252.85</v>
+        <v>253.18</v>
       </c>
       <c r="E5" t="n">
-        <v>295.2</v>
+        <v>290.88</v>
       </c>
       <c r="F5" t="n">
-        <v>3230.62</v>
+        <v>2271.5</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54.88999938964844</v>
+        <v>52.86999893188477</v>
       </c>
       <c r="F5" t="n">
-        <v>30299.27966308594</v>
+        <v>29184.23941040039</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>30299.27966308594</v>
+        <v>29184.23941040039</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>271.3099975585938</v>
+        <v>266.1600036621094</v>
       </c>
       <c r="F6" t="n">
-        <v>47479.24957275391</v>
+        <v>46578.00064086914</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47479.24957275391</v>
+        <v>46578.00064086914</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>21.43000030517578</v>
+        <v>20.3799991607666</v>
       </c>
       <c r="F7" t="n">
-        <v>54175.04077148438</v>
+        <v>51520.63787841797</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>54175.04077148438</v>
+        <v>51520.63787841797</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4626.7001953125</v>
+        <v>4504.10009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000562292684271215</v>
+        <v>-0.0259509953214081</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1284359125664449</v>
+        <v>0.09853417974623091</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69.54000091552734</v>
+        <v>67.08999633789062</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001065233264009091</v>
+        <v>-0.03420388338425018</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1823514841322795</v>
+        <v>0.1406953652027088</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.88</v>
+        <v>-2.54</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>108190.4462402344</v>
+        <v>106201.0825363159</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+49.5%</t>
+          <t>+49.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-63033.95225830078</v>
+        <v>-62216.84291687013</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+35.5%</t>
+          <t>+35.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-45156.49398193359</v>
+        <v>-43984.23961944581</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.87</v>
+        <v>51.92</v>
       </c>
       <c r="C2" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="D2" t="n">
-        <v>50.48</v>
+        <v>50.25</v>
       </c>
       <c r="E2" t="n">
-        <v>59.81</v>
+        <v>59.02</v>
       </c>
       <c r="F2" t="n">
-        <v>1319.77</v>
+        <v>923.64</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.38</v>
+        <v>19.87</v>
       </c>
       <c r="C3" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="D3" t="n">
-        <v>19.1</v>
+        <v>19.03</v>
       </c>
       <c r="E3" t="n">
-        <v>23.49</v>
+        <v>23.06</v>
       </c>
       <c r="F3" t="n">
-        <v>3242.07</v>
+        <v>2122.13</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>266.16</v>
+        <v>263.15</v>
       </c>
       <c r="C5" t="n">
-        <v>8.24</v>
+        <v>8.44</v>
       </c>
       <c r="D5" t="n">
-        <v>253.18</v>
+        <v>252.88</v>
       </c>
       <c r="E5" t="n">
-        <v>290.88</v>
+        <v>288.47</v>
       </c>
       <c r="F5" t="n">
-        <v>2271.5</v>
+        <v>1796.78</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.86999893188477</v>
+        <v>51.91999816894531</v>
       </c>
       <c r="F5" t="n">
-        <v>29184.23941040039</v>
+        <v>28659.83898925781</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>29184.23941040039</v>
+        <v>28659.83898925781</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>266.1600036621094</v>
+        <v>263.1499938964844</v>
       </c>
       <c r="F6" t="n">
-        <v>46578.00064086914</v>
+        <v>46051.24893188477</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>46578.00064086914</v>
+        <v>46051.24893188477</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20.3799991607666</v>
+        <v>19.8700008392334</v>
       </c>
       <c r="F7" t="n">
-        <v>51520.63787841797</v>
+        <v>50231.36212158203</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>51520.63787841797</v>
+        <v>50231.36212158203</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4504.10009765625</v>
+        <v>4499.10009765625</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0259509953214081</v>
+        <v>-0.02996916777847036</v>
       </c>
       <c r="D2" t="n">
-        <v>0.09853417974623091</v>
+        <v>0.1153779785601472</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67.08999633789062</v>
+        <v>67.43499755859375</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03420388338425018</v>
+        <v>-0.01749816423673045</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1406953652027088</v>
+        <v>0.1693862655021896</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.54</v>
+        <v>-2.53</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106201.0825363159</v>
+        <v>102517.294039154</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+49.8%</t>
+          <t>+49.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-62216.84291687013</v>
+        <v>-60237.64155731202</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+35.2%</t>
+          <t>+35.1%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-43984.23961944581</v>
+        <v>-42279.65248184204</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51.92</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="D2" t="n">
-        <v>50.25</v>
+        <v>49.97</v>
       </c>
       <c r="E2" t="n">
-        <v>59.02</v>
+        <v>57.24</v>
       </c>
       <c r="F2" t="n">
-        <v>923.64</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.87</v>
+        <v>19.11</v>
       </c>
       <c r="C3" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="D3" t="n">
-        <v>19.03</v>
+        <v>18.96</v>
       </c>
       <c r="E3" t="n">
-        <v>23.06</v>
+        <v>22.39</v>
       </c>
       <c r="F3" t="n">
-        <v>2122.13</v>
+        <v>390.52</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>263.15</v>
+        <v>255.42</v>
       </c>
       <c r="C5" t="n">
-        <v>8.44</v>
+        <v>8.43</v>
       </c>
       <c r="D5" t="n">
-        <v>252.88</v>
+        <v>252.91</v>
       </c>
       <c r="E5" t="n">
-        <v>288.47</v>
+        <v>280.71</v>
       </c>
       <c r="F5" t="n">
-        <v>1796.78</v>
+        <v>439.49</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>51.91999816894531</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>28659.83898925781</v>
+        <v>27600</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28659.83898925781</v>
+        <v>27600</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>263.1499938964844</v>
+        <v>255.4199981689453</v>
       </c>
       <c r="F6" t="n">
-        <v>46051.24893188477</v>
+        <v>44698.49967956543</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>46051.24893188477</v>
+        <v>44698.49967956543</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>19.8700008392334</v>
+        <v>19.11000061035156</v>
       </c>
       <c r="F7" t="n">
-        <v>50231.36212158203</v>
+        <v>48310.08154296875</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>50231.36212158203</v>
+        <v>48310.08154296875</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4499.10009765625</v>
+        <v>4378</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.02996916777847036</v>
+        <v>-0.04788834456076463</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1153779785601472</v>
+        <v>0.06900427416002075</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67.43499755859375</v>
+        <v>64.78500366210938</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.01749816423673045</v>
+        <v>-0.04713920138785632</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1693862655021896</v>
+        <v>0.07874323840206521</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.53</v>
+        <v>-2.68</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bajista</t>
+          <t>Alcista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102517.294039154</v>
+        <v>107445.0066421509</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+49.9%</t>
+          <t>+48.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-60237.64155731202</v>
+        <v>-61258.73999328614</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+35.1%</t>
+          <t>+36.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-42279.65248184204</v>
+        <v>-46186.26664886474</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>51.54</v>
       </c>
       <c r="C2" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="D2" t="n">
-        <v>49.97</v>
+        <v>48.81</v>
       </c>
       <c r="E2" t="n">
-        <v>57.24</v>
+        <v>58.96</v>
       </c>
       <c r="F2" t="n">
-        <v>16.35</v>
+        <v>1507.31</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.11</v>
+        <v>20.77</v>
       </c>
       <c r="C3" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="D3" t="n">
-        <v>18.96</v>
+        <v>18.54</v>
       </c>
       <c r="E3" t="n">
-        <v>22.39</v>
+        <v>24.29</v>
       </c>
       <c r="F3" t="n">
-        <v>390.52</v>
+        <v>5628</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>255.42</v>
+        <v>259.71</v>
       </c>
       <c r="C5" t="n">
-        <v>8.43</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>252.91</v>
+        <v>251.63</v>
       </c>
       <c r="E5" t="n">
-        <v>280.71</v>
+        <v>285.06</v>
       </c>
       <c r="F5" t="n">
-        <v>439.49</v>
+        <v>1413.59</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>51.54000091552734</v>
       </c>
       <c r="F5" t="n">
-        <v>27600</v>
+        <v>28450.08050537109</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>27600</v>
+        <v>28450.08050537109</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>255.4199981689453</v>
+        <v>259.7099914550781</v>
       </c>
       <c r="F6" t="n">
-        <v>44698.49967956543</v>
+        <v>45449.24850463867</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>44698.49967956543</v>
+        <v>45449.24850463867</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>19.11000061035156</v>
+        <v>20.77000045776367</v>
       </c>
       <c r="F7" t="n">
-        <v>48310.08154296875</v>
+        <v>52506.56115722656</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>48310.08154296875</v>
+        <v>52506.56115722656</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4378</v>
+        <v>4432.89990234375</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.04788834456076463</v>
+        <v>-0.03835396782388023</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06900427416002075</v>
+        <v>0.04406710308142303</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>64.78500366210938</v>
+        <v>65.97000122070312</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.04713920138785632</v>
+        <v>-0.04982067423148373</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07874323840206521</v>
+        <v>0.06233598380232541</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.68</v>
+        <v>-2.88</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -530,7 +530,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>No Convencente / Correctivo</t>
+          <t>Sí (Posible Onda de Impulso)</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>107445.0066421509</v>
+        <v>110464.5774536133</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+48.5%</t>
+          <t>+48.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-61258.73999328614</v>
+        <v>-63343.61608886719</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+36.5%</t>
+          <t>+36.3%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-46186.26664886474</v>
+        <v>-47120.96136474609</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51.54</v>
+        <v>52.6</v>
       </c>
       <c r="C2" t="n">
-        <v>2.47</v>
+        <v>2.22</v>
       </c>
       <c r="D2" t="n">
-        <v>48.81</v>
+        <v>50.46</v>
       </c>
       <c r="E2" t="n">
-        <v>58.96</v>
+        <v>59.25</v>
       </c>
       <c r="F2" t="n">
-        <v>1507.31</v>
+        <v>1180.95</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.77</v>
+        <v>21.21</v>
       </c>
       <c r="C3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="D3" t="n">
-        <v>18.54</v>
+        <v>18.78</v>
       </c>
       <c r="E3" t="n">
-        <v>24.29</v>
+        <v>24.7</v>
       </c>
       <c r="F3" t="n">
-        <v>5628</v>
+        <v>6130.59</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>259.71</v>
+        <v>270.31</v>
       </c>
       <c r="C5" t="n">
-        <v>8.449999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>251.63</v>
+        <v>251.61</v>
       </c>
       <c r="E5" t="n">
-        <v>285.06</v>
+        <v>297.15</v>
       </c>
       <c r="F5" t="n">
-        <v>1413.59</v>
+        <v>3272.51</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>51.54000091552734</v>
+        <v>52.59999847412109</v>
       </c>
       <c r="F5" t="n">
-        <v>28450.08050537109</v>
+        <v>29035.19915771484</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28450.08050537109</v>
+        <v>29035.19915771484</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>259.7099914550781</v>
+        <v>270.3099975585938</v>
       </c>
       <c r="F6" t="n">
-        <v>45449.24850463867</v>
+        <v>47304.24957275391</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>45449.24850463867</v>
+        <v>47304.24957275391</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20.77000045776367</v>
+        <v>21.20999908447266</v>
       </c>
       <c r="F7" t="n">
-        <v>52506.56115722656</v>
+        <v>53618.87768554688</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>52506.56115722656</v>
+        <v>53618.87768554688</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4432.89990234375</v>
+        <v>4524</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.03835396782388023</v>
+        <v>0.01024986073173606</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04406710308142303</v>
+        <v>0.06647807637906644</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65.97000122070312</v>
+        <v>67.58000183105469</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.04982067423148373</v>
+        <v>0.008731980901403924</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06233598380232541</v>
+        <v>0.09995284326548126</v>
       </c>
     </row>
   </sheetData>

--- a/public/reporte_semanal.xlsx
+++ b/public/reporte_semanal.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-2.88</v>
+        <v>-2.67</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alcista</t>
+          <t>Bajista</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sí (Posible Onda de Impulso)</t>
+          <t>No Convencente / Correctivo</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>110464.5774536133</v>
+        <v>108120.1866378784</v>
       </c>
     </row>
     <row r="3">
@@ -615,7 +615,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,11 +625,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+48.7%</t>
+          <t>+48.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>-63343.61608886719</v>
+        <v>-62201.15684509277</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+36.3%</t>
+          <t>+36.1%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-47120.96136474609</v>
+        <v>-45919.02979278565</v>
       </c>
     </row>
   </sheetData>
@@ -718,19 +718,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.6</v>
+        <v>51.34</v>
       </c>
       <c r="C2" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="D2" t="n">
-        <v>50.46</v>
+        <v>50.36</v>
       </c>
       <c r="E2" t="n">
-        <v>59.25</v>
+        <v>58.11</v>
       </c>
       <c r="F2" t="n">
-        <v>1180.95</v>
+        <v>543.09</v>
       </c>
     </row>
     <row r="3">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.21</v>
+        <v>20.68</v>
       </c>
       <c r="C3" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="D3" t="n">
-        <v>18.78</v>
+        <v>18.75</v>
       </c>
       <c r="E3" t="n">
-        <v>24.7</v>
+        <v>24.21</v>
       </c>
       <c r="F3" t="n">
-        <v>6130.59</v>
+        <v>4881.1</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>270.31</v>
+        <v>266.18</v>
       </c>
       <c r="C5" t="n">
-        <v>8.949999999999999</v>
+        <v>9.01</v>
       </c>
       <c r="D5" t="n">
-        <v>251.61</v>
+        <v>251.46</v>
       </c>
       <c r="E5" t="n">
-        <v>297.15</v>
+        <v>293.21</v>
       </c>
       <c r="F5" t="n">
-        <v>3272.51</v>
+        <v>2576.87</v>
       </c>
     </row>
     <row r="6">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>52.59999847412109</v>
+        <v>51.34000015258789</v>
       </c>
       <c r="F5" t="n">
-        <v>29035.19915771484</v>
+        <v>28339.68008422852</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>29035.19915771484</v>
+        <v>28339.68008422852</v>
       </c>
     </row>
     <row r="6">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>270.3099975585938</v>
+        <v>266.1799926757812</v>
       </c>
       <c r="F6" t="n">
-        <v>47304.24957275391</v>
+        <v>46581.49871826172</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47304.24957275391</v>
+        <v>46581.49871826172</v>
       </c>
     </row>
     <row r="7">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>21.20999908447266</v>
+        <v>20.68000030517578</v>
       </c>
       <c r="F7" t="n">
-        <v>53618.87768554688</v>
+        <v>52279.04077148438</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>53618.87768554688</v>
+        <v>52279.04077148438</v>
       </c>
     </row>
   </sheetData>
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4524</v>
+        <v>4477.2001953125</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01024986073173606</v>
+        <v>-0.0002009562814866417</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06647807637906644</v>
+        <v>0.05544559059700616</v>
       </c>
     </row>
     <row r="3">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67.58000183105469</v>
+        <v>66.81999969482422</v>
       </c>
       <c r="C3" t="n">
-        <v>0.008731980901403924</v>
+        <v>-0.002612180678905007</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09995284326548126</v>
+        <v>0.08758281532845325</v>
       </c>
     </row>
   </sheetData>
